--- a/activity/M01A07/M01A07_Pendiente.xlsx
+++ b/activity/M01A07/M01A07_Pendiente.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.HCMC\activity\M01A07\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C8EEA69-EB73-45A6-B79B-C4CDA22EADEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AB8F18C-BF28-4421-9683-DB3E56804C1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" tabRatio="762" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="44">
   <si>
     <t>Observaciones</t>
   </si>
@@ -120,9 +120,6 @@
   </si>
   <si>
     <t>M01A07</t>
-  </si>
-  <si>
-    <t>https://github.com/rcfdtools/R.HCMC/blob/main/activity/M01A07/Readme.md</t>
   </si>
   <si>
     <t>Grupo 6</t>
@@ -252,12 +249,6 @@
     </font>
     <font>
       <sz val="8"/>
-      <color theme="10"/>
-      <name val="Segoe UI Light"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -265,6 +256,12 @@
     <font>
       <sz val="8"/>
       <color theme="1"/>
+      <name val="Segoe UI Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF0070C0"/>
       <name val="Segoe UI Light"/>
       <family val="2"/>
     </font>
@@ -283,7 +280,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -462,15 +459,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color theme="0" tint="-4.9989318521683403E-2"/>
       </left>
@@ -629,31 +617,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -668,17 +632,11 @@
     <xf numFmtId="2" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -688,15 +646,15 @@
     <xf numFmtId="2" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -710,6 +668,36 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -2113,25 +2101,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="F1" s="36" t="s">
+      <c r="F1" s="28" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="2" spans="2:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="44" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B3" s="29"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
     </row>
     <row r="4" spans="2:6" ht="30.75" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="22" t="s">
@@ -2154,14 +2142,14 @@
       <c r="B5" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="37">
+      <c r="C5" s="29">
         <v>5</v>
       </c>
       <c r="D5" s="23">
         <f>Detalle!C27*C5/5</f>
         <v>0</v>
       </c>
-      <c r="E5" s="39"/>
+      <c r="E5" s="31"/>
       <c r="F5" s="25">
         <f>AVERAGE(D5:E5)</f>
         <v>0</v>
@@ -2171,14 +2159,14 @@
       <c r="B6" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="37">
+      <c r="C6" s="29">
         <v>5</v>
       </c>
       <c r="D6" s="23">
         <f>Detalle!F27*C6/5</f>
         <v>0</v>
       </c>
-      <c r="E6" s="39"/>
+      <c r="E6" s="31"/>
       <c r="F6" s="25">
         <f t="shared" ref="F6:F18" si="0">AVERAGE(D6:E6)</f>
         <v>0</v>
@@ -2188,14 +2176,14 @@
       <c r="B7" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="37">
+      <c r="C7" s="29">
         <v>5</v>
       </c>
       <c r="D7" s="23">
         <f>Detalle!I27*C7/5</f>
         <v>0</v>
       </c>
-      <c r="E7" s="39"/>
+      <c r="E7" s="31"/>
       <c r="F7" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2205,14 +2193,14 @@
       <c r="B8" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="37">
+      <c r="C8" s="29">
         <v>5</v>
       </c>
       <c r="D8" s="23">
         <f>Detalle!L27*C8/5</f>
         <v>0</v>
       </c>
-      <c r="E8" s="39"/>
+      <c r="E8" s="31"/>
       <c r="F8" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2222,14 +2210,14 @@
       <c r="B9" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="37">
+      <c r="C9" s="29">
         <v>5</v>
       </c>
       <c r="D9" s="23">
         <f>Detalle!O27*C9/5</f>
         <v>0</v>
       </c>
-      <c r="E9" s="39"/>
+      <c r="E9" s="31"/>
       <c r="F9" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2237,16 +2225,16 @@
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B10" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="37">
+        <v>27</v>
+      </c>
+      <c r="C10" s="29">
         <v>5</v>
       </c>
       <c r="D10" s="23">
         <f>Detalle!R27*C10/5</f>
         <v>0</v>
       </c>
-      <c r="E10" s="39"/>
+      <c r="E10" s="31"/>
       <c r="F10" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2254,16 +2242,16 @@
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B11" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="37">
+        <v>28</v>
+      </c>
+      <c r="C11" s="29">
         <v>5</v>
       </c>
       <c r="D11" s="23">
         <f>Detalle!U27*C11/5</f>
         <v>0</v>
       </c>
-      <c r="E11" s="39"/>
+      <c r="E11" s="31"/>
       <c r="F11" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2271,16 +2259,16 @@
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B12" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="37">
+        <v>29</v>
+      </c>
+      <c r="C12" s="29">
         <v>5</v>
       </c>
       <c r="D12" s="23">
         <f>Detalle!X27*C12/5</f>
         <v>0</v>
       </c>
-      <c r="E12" s="39"/>
+      <c r="E12" s="31"/>
       <c r="F12" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2288,16 +2276,16 @@
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B13" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" s="37">
+        <v>30</v>
+      </c>
+      <c r="C13" s="29">
         <v>5</v>
       </c>
       <c r="D13" s="23">
         <f>Detalle!AA27*C13/5</f>
         <v>0</v>
       </c>
-      <c r="E13" s="39"/>
+      <c r="E13" s="31"/>
       <c r="F13" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2305,16 +2293,16 @@
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B14" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" s="37">
+        <v>31</v>
+      </c>
+      <c r="C14" s="29">
         <v>5</v>
       </c>
       <c r="D14" s="23">
         <f>Detalle!AD27*C14/5</f>
         <v>0</v>
       </c>
-      <c r="E14" s="39"/>
+      <c r="E14" s="31"/>
       <c r="F14" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2322,16 +2310,16 @@
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B15" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C15" s="37">
+        <v>32</v>
+      </c>
+      <c r="C15" s="29">
         <v>5</v>
       </c>
       <c r="D15" s="23">
         <f>Detalle!AG27*C15/5</f>
         <v>0</v>
       </c>
-      <c r="E15" s="39"/>
+      <c r="E15" s="31"/>
       <c r="F15" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2339,16 +2327,16 @@
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B16" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C16" s="37">
+        <v>33</v>
+      </c>
+      <c r="C16" s="29">
         <v>5</v>
       </c>
       <c r="D16" s="23">
         <f>Detalle!AJ27*C16/5</f>
         <v>0</v>
       </c>
-      <c r="E16" s="39"/>
+      <c r="E16" s="31"/>
       <c r="F16" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2356,16 +2344,16 @@
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B17" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C17" s="37">
+        <v>34</v>
+      </c>
+      <c r="C17" s="29">
         <v>5</v>
       </c>
       <c r="D17" s="23">
         <f>Detalle!AM27*C17/5</f>
         <v>0</v>
       </c>
-      <c r="E17" s="39"/>
+      <c r="E17" s="31"/>
       <c r="F17" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2373,36 +2361,37 @@
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B18" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C18" s="38">
+        <v>35</v>
+      </c>
+      <c r="C18" s="30">
         <v>5</v>
       </c>
       <c r="D18" s="24">
         <f>Detalle!AP27*C18/5</f>
         <v>0</v>
       </c>
-      <c r="E18" s="40"/>
+      <c r="E18" s="32"/>
       <c r="F18" s="26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B19" s="30" t="s">
-        <v>27</v>
-      </c>
-      <c r="C19" s="30"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="30"/>
+    <row r="19" spans="2:6" ht="15.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B19" s="53" t="str">
+        <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.HCMC/blob/main/activity/",F1,"/Readme.md"),_xlfn.CONCAT("Ir a actividad ",F1," en GitHub."))</f>
+        <v>Ir a actividad M01A07 en GitHub.</v>
+      </c>
+      <c r="C19" s="53"/>
+      <c r="D19" s="53"/>
+      <c r="E19" s="53"/>
+      <c r="F19" s="53"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B20" s="27"/>
-      <c r="C20" s="27"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="27"/>
-      <c r="F20" s="27"/>
+      <c r="B20" s="53"/>
+      <c r="C20" s="53"/>
+      <c r="D20" s="53"/>
+      <c r="E20" s="53"/>
+      <c r="F20" s="53"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B21" s="27"/>
@@ -2412,17 +2401,15 @@
       <c r="F21" s="27"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="B2:F3"/>
     <mergeCell ref="B19:F19"/>
+    <mergeCell ref="B20:F20"/>
   </mergeCells>
-  <phoneticPr fontId="11" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="B19" r:id="rId1" xr:uid="{F2D00288-2115-4A63-9C69-2228ADA9789D}"/>
-  </hyperlinks>
+  <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
-  <drawing r:id="rId3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -2500,98 +2487,98 @@
       <c r="AP1" s="15"/>
       <c r="AQ1" s="15"/>
     </row>
-    <row r="2" spans="1:44" s="53" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="52"/>
-      <c r="B2" s="34" t="s">
+    <row r="2" spans="1:44" s="43" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="42"/>
+      <c r="B2" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="31" t="str">
+      <c r="C2" s="48" t="str">
         <f>Calificacion!B5</f>
         <v>Grupo 1</v>
       </c>
-      <c r="D2" s="32"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="31" t="str">
+      <c r="D2" s="49"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="48" t="str">
         <f>Calificacion!B6</f>
         <v>Grupo 2</v>
       </c>
-      <c r="G2" s="32"/>
-      <c r="H2" s="33"/>
-      <c r="I2" s="31" t="str">
+      <c r="G2" s="49"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="48" t="str">
         <f>Calificacion!B7</f>
         <v>Grupo 3</v>
       </c>
-      <c r="J2" s="32"/>
-      <c r="K2" s="33"/>
-      <c r="L2" s="31" t="str">
+      <c r="J2" s="49"/>
+      <c r="K2" s="50"/>
+      <c r="L2" s="48" t="str">
         <f>Calificacion!B8</f>
         <v>Grupo 4</v>
       </c>
-      <c r="M2" s="32"/>
-      <c r="N2" s="33"/>
-      <c r="O2" s="31" t="str">
+      <c r="M2" s="49"/>
+      <c r="N2" s="50"/>
+      <c r="O2" s="48" t="str">
         <f>Calificacion!B9</f>
         <v>Grupo 5</v>
       </c>
-      <c r="P2" s="32"/>
-      <c r="Q2" s="33"/>
-      <c r="R2" s="31" t="str">
+      <c r="P2" s="49"/>
+      <c r="Q2" s="50"/>
+      <c r="R2" s="48" t="str">
         <f>Calificacion!B10</f>
         <v>Grupo 6</v>
       </c>
-      <c r="S2" s="32"/>
-      <c r="T2" s="33"/>
-      <c r="U2" s="31" t="str">
+      <c r="S2" s="49"/>
+      <c r="T2" s="50"/>
+      <c r="U2" s="48" t="str">
         <f>Calificacion!B11</f>
         <v>Grupo 7</v>
       </c>
-      <c r="V2" s="32"/>
-      <c r="W2" s="33"/>
-      <c r="X2" s="31" t="str">
+      <c r="V2" s="49"/>
+      <c r="W2" s="50"/>
+      <c r="X2" s="48" t="str">
         <f>Calificacion!B12</f>
         <v>Grupo 8</v>
       </c>
-      <c r="Y2" s="32"/>
-      <c r="Z2" s="33"/>
-      <c r="AA2" s="31" t="str">
+      <c r="Y2" s="49"/>
+      <c r="Z2" s="50"/>
+      <c r="AA2" s="48" t="str">
         <f>Calificacion!B13</f>
         <v>Grupo 9</v>
       </c>
-      <c r="AB2" s="32"/>
-      <c r="AC2" s="33"/>
-      <c r="AD2" s="31" t="str">
+      <c r="AB2" s="49"/>
+      <c r="AC2" s="50"/>
+      <c r="AD2" s="48" t="str">
         <f>Calificacion!B14</f>
         <v>Grupo 10</v>
       </c>
-      <c r="AE2" s="32"/>
-      <c r="AF2" s="33"/>
-      <c r="AG2" s="31" t="str">
+      <c r="AE2" s="49"/>
+      <c r="AF2" s="50"/>
+      <c r="AG2" s="48" t="str">
         <f>Calificacion!B15</f>
         <v>Grupo 11</v>
       </c>
-      <c r="AH2" s="32"/>
-      <c r="AI2" s="33"/>
-      <c r="AJ2" s="31" t="str">
+      <c r="AH2" s="49"/>
+      <c r="AI2" s="50"/>
+      <c r="AJ2" s="48" t="str">
         <f>Calificacion!B16</f>
         <v>Grupo 12</v>
       </c>
-      <c r="AK2" s="32"/>
-      <c r="AL2" s="33"/>
-      <c r="AM2" s="31" t="str">
+      <c r="AK2" s="49"/>
+      <c r="AL2" s="50"/>
+      <c r="AM2" s="48" t="str">
         <f>Calificacion!B17</f>
         <v>Grupo 13</v>
       </c>
-      <c r="AN2" s="32"/>
-      <c r="AO2" s="33"/>
-      <c r="AP2" s="31" t="str">
+      <c r="AN2" s="49"/>
+      <c r="AO2" s="50"/>
+      <c r="AP2" s="48" t="str">
         <f>Calificacion!B18</f>
         <v>Grupo 14</v>
       </c>
-      <c r="AQ2" s="32"/>
-      <c r="AR2" s="33"/>
+      <c r="AQ2" s="49"/>
+      <c r="AR2" s="50"/>
     </row>
     <row r="3" spans="1:44" x14ac:dyDescent="0.45">
-      <c r="B3" s="35"/>
+      <c r="B3" s="47"/>
       <c r="C3" s="12" t="s">
         <v>1</v>
       </c>
@@ -2723,1324 +2710,1324 @@
       <c r="B4" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="45"/>
+      <c r="C4" s="35"/>
       <c r="D4" s="18"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="45"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="35"/>
       <c r="G4" s="18"/>
-      <c r="H4" s="46"/>
-      <c r="I4" s="45"/>
+      <c r="H4" s="36"/>
+      <c r="I4" s="35"/>
       <c r="J4" s="18"/>
-      <c r="K4" s="46"/>
-      <c r="L4" s="45"/>
+      <c r="K4" s="36"/>
+      <c r="L4" s="35"/>
       <c r="M4" s="18"/>
-      <c r="N4" s="46"/>
-      <c r="O4" s="45"/>
+      <c r="N4" s="36"/>
+      <c r="O4" s="35"/>
       <c r="P4" s="18"/>
-      <c r="Q4" s="46"/>
-      <c r="R4" s="45"/>
+      <c r="Q4" s="36"/>
+      <c r="R4" s="35"/>
       <c r="S4" s="18"/>
-      <c r="T4" s="46"/>
-      <c r="U4" s="45"/>
+      <c r="T4" s="36"/>
+      <c r="U4" s="35"/>
       <c r="V4" s="18"/>
-      <c r="W4" s="46"/>
-      <c r="X4" s="45"/>
+      <c r="W4" s="36"/>
+      <c r="X4" s="35"/>
       <c r="Y4" s="18"/>
-      <c r="Z4" s="46"/>
-      <c r="AA4" s="45"/>
+      <c r="Z4" s="36"/>
+      <c r="AA4" s="35"/>
       <c r="AB4" s="18"/>
-      <c r="AC4" s="46"/>
-      <c r="AD4" s="45"/>
+      <c r="AC4" s="36"/>
+      <c r="AD4" s="35"/>
       <c r="AE4" s="18"/>
-      <c r="AF4" s="46"/>
-      <c r="AG4" s="45"/>
+      <c r="AF4" s="36"/>
+      <c r="AG4" s="35"/>
       <c r="AH4" s="18"/>
-      <c r="AI4" s="46"/>
-      <c r="AJ4" s="45"/>
+      <c r="AI4" s="36"/>
+      <c r="AJ4" s="35"/>
       <c r="AK4" s="18"/>
-      <c r="AL4" s="46"/>
-      <c r="AM4" s="45"/>
+      <c r="AL4" s="36"/>
+      <c r="AM4" s="35"/>
       <c r="AN4" s="18"/>
-      <c r="AO4" s="46"/>
-      <c r="AP4" s="45"/>
+      <c r="AO4" s="36"/>
+      <c r="AP4" s="35"/>
       <c r="AQ4" s="18"/>
-      <c r="AR4" s="46"/>
+      <c r="AR4" s="36"/>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B5" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="C5" s="45">
+        <v>38</v>
+      </c>
+      <c r="C5" s="35">
         <v>0</v>
       </c>
       <c r="D5" s="18"/>
-      <c r="E5" s="46"/>
-      <c r="F5" s="45">
+      <c r="E5" s="36"/>
+      <c r="F5" s="35">
         <v>0</v>
       </c>
       <c r="G5" s="18"/>
-      <c r="H5" s="46"/>
-      <c r="I5" s="45">
+      <c r="H5" s="36"/>
+      <c r="I5" s="35">
         <v>0</v>
       </c>
       <c r="J5" s="18"/>
-      <c r="K5" s="46"/>
-      <c r="L5" s="45">
+      <c r="K5" s="36"/>
+      <c r="L5" s="35">
         <v>0</v>
       </c>
       <c r="M5" s="18"/>
-      <c r="N5" s="46"/>
-      <c r="O5" s="45">
+      <c r="N5" s="36"/>
+      <c r="O5" s="35">
         <v>0</v>
       </c>
       <c r="P5" s="18"/>
-      <c r="Q5" s="46"/>
-      <c r="R5" s="45">
+      <c r="Q5" s="36"/>
+      <c r="R5" s="35">
         <v>0</v>
       </c>
       <c r="S5" s="18"/>
-      <c r="T5" s="46"/>
-      <c r="U5" s="45">
+      <c r="T5" s="36"/>
+      <c r="U5" s="35">
         <v>0</v>
       </c>
       <c r="V5" s="18"/>
-      <c r="W5" s="46"/>
-      <c r="X5" s="45">
+      <c r="W5" s="36"/>
+      <c r="X5" s="35">
         <v>0</v>
       </c>
       <c r="Y5" s="18"/>
-      <c r="Z5" s="46"/>
-      <c r="AA5" s="45">
+      <c r="Z5" s="36"/>
+      <c r="AA5" s="35">
         <v>0</v>
       </c>
       <c r="AB5" s="18"/>
-      <c r="AC5" s="46"/>
-      <c r="AD5" s="45">
+      <c r="AC5" s="36"/>
+      <c r="AD5" s="35">
         <v>0</v>
       </c>
       <c r="AE5" s="18"/>
-      <c r="AF5" s="46"/>
-      <c r="AG5" s="45">
+      <c r="AF5" s="36"/>
+      <c r="AG5" s="35">
         <v>0</v>
       </c>
       <c r="AH5" s="18"/>
-      <c r="AI5" s="46"/>
-      <c r="AJ5" s="45">
+      <c r="AI5" s="36"/>
+      <c r="AJ5" s="35">
         <v>0</v>
       </c>
       <c r="AK5" s="18"/>
-      <c r="AL5" s="46"/>
-      <c r="AM5" s="45">
+      <c r="AL5" s="36"/>
+      <c r="AM5" s="35">
         <v>0</v>
       </c>
       <c r="AN5" s="18"/>
-      <c r="AO5" s="46"/>
-      <c r="AP5" s="45">
+      <c r="AO5" s="36"/>
+      <c r="AP5" s="35">
         <v>0</v>
       </c>
       <c r="AQ5" s="18"/>
-      <c r="AR5" s="46"/>
+      <c r="AR5" s="36"/>
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B6" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="C6" s="45"/>
+        <v>39</v>
+      </c>
+      <c r="C6" s="35"/>
       <c r="D6" s="18"/>
-      <c r="E6" s="46"/>
-      <c r="F6" s="45"/>
+      <c r="E6" s="36"/>
+      <c r="F6" s="35"/>
       <c r="G6" s="18"/>
-      <c r="H6" s="46"/>
-      <c r="I6" s="45"/>
+      <c r="H6" s="36"/>
+      <c r="I6" s="35"/>
       <c r="J6" s="18"/>
-      <c r="K6" s="46"/>
-      <c r="L6" s="45"/>
+      <c r="K6" s="36"/>
+      <c r="L6" s="35"/>
       <c r="M6" s="18"/>
-      <c r="N6" s="46"/>
-      <c r="O6" s="45"/>
+      <c r="N6" s="36"/>
+      <c r="O6" s="35"/>
       <c r="P6" s="18"/>
-      <c r="Q6" s="46"/>
-      <c r="R6" s="45"/>
+      <c r="Q6" s="36"/>
+      <c r="R6" s="35"/>
       <c r="S6" s="18"/>
-      <c r="T6" s="46"/>
-      <c r="U6" s="45"/>
+      <c r="T6" s="36"/>
+      <c r="U6" s="35"/>
       <c r="V6" s="18"/>
-      <c r="W6" s="46"/>
-      <c r="X6" s="45"/>
+      <c r="W6" s="36"/>
+      <c r="X6" s="35"/>
       <c r="Y6" s="18"/>
-      <c r="Z6" s="46"/>
-      <c r="AA6" s="45"/>
+      <c r="Z6" s="36"/>
+      <c r="AA6" s="35"/>
       <c r="AB6" s="18"/>
-      <c r="AC6" s="46"/>
-      <c r="AD6" s="45"/>
+      <c r="AC6" s="36"/>
+      <c r="AD6" s="35"/>
       <c r="AE6" s="18"/>
-      <c r="AF6" s="46"/>
-      <c r="AG6" s="45"/>
+      <c r="AF6" s="36"/>
+      <c r="AG6" s="35"/>
       <c r="AH6" s="18"/>
-      <c r="AI6" s="46"/>
-      <c r="AJ6" s="45"/>
+      <c r="AI6" s="36"/>
+      <c r="AJ6" s="35"/>
       <c r="AK6" s="18"/>
-      <c r="AL6" s="46"/>
-      <c r="AM6" s="45"/>
+      <c r="AL6" s="36"/>
+      <c r="AM6" s="35"/>
       <c r="AN6" s="18"/>
-      <c r="AO6" s="46"/>
-      <c r="AP6" s="45"/>
+      <c r="AO6" s="36"/>
+      <c r="AP6" s="35"/>
       <c r="AQ6" s="18"/>
-      <c r="AR6" s="46"/>
+      <c r="AR6" s="36"/>
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B7" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="C7" s="45"/>
+        <v>40</v>
+      </c>
+      <c r="C7" s="35"/>
       <c r="D7" s="18"/>
-      <c r="E7" s="46"/>
-      <c r="F7" s="45"/>
+      <c r="E7" s="36"/>
+      <c r="F7" s="35"/>
       <c r="G7" s="18"/>
-      <c r="H7" s="46"/>
-      <c r="I7" s="45"/>
+      <c r="H7" s="36"/>
+      <c r="I7" s="35"/>
       <c r="J7" s="18"/>
-      <c r="K7" s="46"/>
-      <c r="L7" s="45"/>
+      <c r="K7" s="36"/>
+      <c r="L7" s="35"/>
       <c r="M7" s="18"/>
-      <c r="N7" s="46"/>
-      <c r="O7" s="45"/>
+      <c r="N7" s="36"/>
+      <c r="O7" s="35"/>
       <c r="P7" s="18"/>
-      <c r="Q7" s="46"/>
-      <c r="R7" s="45"/>
+      <c r="Q7" s="36"/>
+      <c r="R7" s="35"/>
       <c r="S7" s="18"/>
-      <c r="T7" s="46"/>
-      <c r="U7" s="45"/>
+      <c r="T7" s="36"/>
+      <c r="U7" s="35"/>
       <c r="V7" s="18"/>
-      <c r="W7" s="46"/>
-      <c r="X7" s="45"/>
+      <c r="W7" s="36"/>
+      <c r="X7" s="35"/>
       <c r="Y7" s="18"/>
-      <c r="Z7" s="46"/>
-      <c r="AA7" s="45"/>
+      <c r="Z7" s="36"/>
+      <c r="AA7" s="35"/>
       <c r="AB7" s="18"/>
-      <c r="AC7" s="46"/>
-      <c r="AD7" s="45"/>
+      <c r="AC7" s="36"/>
+      <c r="AD7" s="35"/>
       <c r="AE7" s="18"/>
-      <c r="AF7" s="46"/>
-      <c r="AG7" s="45"/>
+      <c r="AF7" s="36"/>
+      <c r="AG7" s="35"/>
       <c r="AH7" s="18"/>
-      <c r="AI7" s="46"/>
-      <c r="AJ7" s="45"/>
+      <c r="AI7" s="36"/>
+      <c r="AJ7" s="35"/>
       <c r="AK7" s="18"/>
-      <c r="AL7" s="46"/>
-      <c r="AM7" s="45"/>
+      <c r="AL7" s="36"/>
+      <c r="AM7" s="35"/>
       <c r="AN7" s="18"/>
-      <c r="AO7" s="46"/>
-      <c r="AP7" s="45"/>
+      <c r="AO7" s="36"/>
+      <c r="AP7" s="35"/>
       <c r="AQ7" s="18"/>
-      <c r="AR7" s="46"/>
+      <c r="AR7" s="36"/>
     </row>
     <row r="8" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B8" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="C8" s="45"/>
-      <c r="D8" s="51">
+        <v>41</v>
+      </c>
+      <c r="C8" s="35"/>
+      <c r="D8" s="41">
         <f>D5-D6</f>
         <v>0</v>
       </c>
-      <c r="E8" s="46"/>
-      <c r="F8" s="45"/>
-      <c r="G8" s="51">
+      <c r="E8" s="36"/>
+      <c r="F8" s="35"/>
+      <c r="G8" s="41">
         <f>G5-G6</f>
         <v>0</v>
       </c>
-      <c r="H8" s="46"/>
-      <c r="I8" s="45"/>
-      <c r="J8" s="51">
+      <c r="H8" s="36"/>
+      <c r="I8" s="35"/>
+      <c r="J8" s="41">
         <f>J5-J6</f>
         <v>0</v>
       </c>
-      <c r="K8" s="46"/>
-      <c r="L8" s="45"/>
-      <c r="M8" s="51">
+      <c r="K8" s="36"/>
+      <c r="L8" s="35"/>
+      <c r="M8" s="41">
         <f>M5-M6</f>
         <v>0</v>
       </c>
-      <c r="N8" s="46"/>
-      <c r="O8" s="45"/>
-      <c r="P8" s="51">
+      <c r="N8" s="36"/>
+      <c r="O8" s="35"/>
+      <c r="P8" s="41">
         <f>P5-P6</f>
         <v>0</v>
       </c>
-      <c r="Q8" s="46"/>
-      <c r="R8" s="45"/>
-      <c r="S8" s="51">
+      <c r="Q8" s="36"/>
+      <c r="R8" s="35"/>
+      <c r="S8" s="41">
         <f>S5-S6</f>
         <v>0</v>
       </c>
-      <c r="T8" s="46"/>
-      <c r="U8" s="45"/>
-      <c r="V8" s="51">
+      <c r="T8" s="36"/>
+      <c r="U8" s="35"/>
+      <c r="V8" s="41">
         <f>V5-V6</f>
         <v>0</v>
       </c>
-      <c r="W8" s="46"/>
-      <c r="X8" s="45"/>
-      <c r="Y8" s="51">
+      <c r="W8" s="36"/>
+      <c r="X8" s="35"/>
+      <c r="Y8" s="41">
         <f>Y5-Y6</f>
         <v>0</v>
       </c>
-      <c r="Z8" s="46"/>
-      <c r="AA8" s="45"/>
-      <c r="AB8" s="51">
+      <c r="Z8" s="36"/>
+      <c r="AA8" s="35"/>
+      <c r="AB8" s="41">
         <f>AB5-AB6</f>
         <v>0</v>
       </c>
-      <c r="AC8" s="46"/>
-      <c r="AD8" s="45"/>
-      <c r="AE8" s="51">
+      <c r="AC8" s="36"/>
+      <c r="AD8" s="35"/>
+      <c r="AE8" s="41">
         <f>AE5-AE6</f>
         <v>0</v>
       </c>
-      <c r="AF8" s="46"/>
-      <c r="AG8" s="45"/>
-      <c r="AH8" s="51">
+      <c r="AF8" s="36"/>
+      <c r="AG8" s="35"/>
+      <c r="AH8" s="41">
         <f>AH5-AH6</f>
         <v>0</v>
       </c>
-      <c r="AI8" s="46"/>
-      <c r="AJ8" s="45"/>
-      <c r="AK8" s="51">
+      <c r="AI8" s="36"/>
+      <c r="AJ8" s="35"/>
+      <c r="AK8" s="41">
         <f>AK5-AK6</f>
         <v>0</v>
       </c>
-      <c r="AL8" s="46"/>
-      <c r="AM8" s="45"/>
-      <c r="AN8" s="51">
+      <c r="AL8" s="36"/>
+      <c r="AM8" s="35"/>
+      <c r="AN8" s="41">
         <f>AN5-AN6</f>
         <v>0</v>
       </c>
-      <c r="AO8" s="46"/>
-      <c r="AP8" s="45"/>
-      <c r="AQ8" s="51">
+      <c r="AO8" s="36"/>
+      <c r="AP8" s="35"/>
+      <c r="AQ8" s="41">
         <f>AQ5-AQ6</f>
         <v>0</v>
       </c>
-      <c r="AR8" s="46"/>
+      <c r="AR8" s="36"/>
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B9" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="C9" s="45"/>
+        <v>41</v>
+      </c>
+      <c r="C9" s="35"/>
       <c r="D9" s="18"/>
-      <c r="E9" s="46"/>
-      <c r="F9" s="45"/>
+      <c r="E9" s="36"/>
+      <c r="F9" s="35"/>
       <c r="G9" s="18"/>
-      <c r="H9" s="46"/>
-      <c r="I9" s="45"/>
+      <c r="H9" s="36"/>
+      <c r="I9" s="35"/>
       <c r="J9" s="18"/>
-      <c r="K9" s="46"/>
-      <c r="L9" s="45"/>
+      <c r="K9" s="36"/>
+      <c r="L9" s="35"/>
       <c r="M9" s="18"/>
-      <c r="N9" s="46"/>
-      <c r="O9" s="45"/>
+      <c r="N9" s="36"/>
+      <c r="O9" s="35"/>
       <c r="P9" s="18"/>
-      <c r="Q9" s="46"/>
-      <c r="R9" s="45"/>
+      <c r="Q9" s="36"/>
+      <c r="R9" s="35"/>
       <c r="S9" s="18"/>
-      <c r="T9" s="46"/>
-      <c r="U9" s="45"/>
+      <c r="T9" s="36"/>
+      <c r="U9" s="35"/>
       <c r="V9" s="18"/>
-      <c r="W9" s="46"/>
-      <c r="X9" s="45"/>
+      <c r="W9" s="36"/>
+      <c r="X9" s="35"/>
       <c r="Y9" s="18"/>
-      <c r="Z9" s="46"/>
-      <c r="AA9" s="45"/>
+      <c r="Z9" s="36"/>
+      <c r="AA9" s="35"/>
       <c r="AB9" s="18"/>
-      <c r="AC9" s="46"/>
-      <c r="AD9" s="45"/>
+      <c r="AC9" s="36"/>
+      <c r="AD9" s="35"/>
       <c r="AE9" s="18"/>
-      <c r="AF9" s="46"/>
-      <c r="AG9" s="45"/>
+      <c r="AF9" s="36"/>
+      <c r="AG9" s="35"/>
       <c r="AH9" s="18"/>
-      <c r="AI9" s="46"/>
-      <c r="AJ9" s="45"/>
+      <c r="AI9" s="36"/>
+      <c r="AJ9" s="35"/>
       <c r="AK9" s="18"/>
-      <c r="AL9" s="46"/>
-      <c r="AM9" s="45"/>
+      <c r="AL9" s="36"/>
+      <c r="AM9" s="35"/>
       <c r="AN9" s="18"/>
-      <c r="AO9" s="46"/>
-      <c r="AP9" s="45"/>
+      <c r="AO9" s="36"/>
+      <c r="AP9" s="35"/>
       <c r="AQ9" s="18"/>
-      <c r="AR9" s="46"/>
+      <c r="AR9" s="36"/>
     </row>
     <row r="10" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B10" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="45"/>
+      <c r="C10" s="35"/>
       <c r="D10" s="18"/>
-      <c r="E10" s="46"/>
-      <c r="F10" s="45"/>
+      <c r="E10" s="36"/>
+      <c r="F10" s="35"/>
       <c r="G10" s="18"/>
-      <c r="H10" s="46"/>
-      <c r="I10" s="45"/>
+      <c r="H10" s="36"/>
+      <c r="I10" s="35"/>
       <c r="J10" s="18"/>
-      <c r="K10" s="46"/>
-      <c r="L10" s="45"/>
+      <c r="K10" s="36"/>
+      <c r="L10" s="35"/>
       <c r="M10" s="18"/>
-      <c r="N10" s="46"/>
-      <c r="O10" s="45"/>
+      <c r="N10" s="36"/>
+      <c r="O10" s="35"/>
       <c r="P10" s="18"/>
-      <c r="Q10" s="46"/>
-      <c r="R10" s="45"/>
+      <c r="Q10" s="36"/>
+      <c r="R10" s="35"/>
       <c r="S10" s="18"/>
-      <c r="T10" s="46"/>
-      <c r="U10" s="45"/>
+      <c r="T10" s="36"/>
+      <c r="U10" s="35"/>
       <c r="V10" s="18"/>
-      <c r="W10" s="46"/>
-      <c r="X10" s="45"/>
+      <c r="W10" s="36"/>
+      <c r="X10" s="35"/>
       <c r="Y10" s="18"/>
-      <c r="Z10" s="46"/>
-      <c r="AA10" s="45"/>
+      <c r="Z10" s="36"/>
+      <c r="AA10" s="35"/>
       <c r="AB10" s="18"/>
-      <c r="AC10" s="46"/>
-      <c r="AD10" s="45"/>
+      <c r="AC10" s="36"/>
+      <c r="AD10" s="35"/>
       <c r="AE10" s="18"/>
-      <c r="AF10" s="46"/>
-      <c r="AG10" s="45"/>
+      <c r="AF10" s="36"/>
+      <c r="AG10" s="35"/>
       <c r="AH10" s="18"/>
-      <c r="AI10" s="46"/>
-      <c r="AJ10" s="45"/>
+      <c r="AI10" s="36"/>
+      <c r="AJ10" s="35"/>
       <c r="AK10" s="18"/>
-      <c r="AL10" s="46"/>
-      <c r="AM10" s="45"/>
+      <c r="AL10" s="36"/>
+      <c r="AM10" s="35"/>
       <c r="AN10" s="18"/>
-      <c r="AO10" s="46"/>
-      <c r="AP10" s="45"/>
+      <c r="AO10" s="36"/>
+      <c r="AP10" s="35"/>
       <c r="AQ10" s="18"/>
-      <c r="AR10" s="46"/>
+      <c r="AR10" s="36"/>
     </row>
     <row r="11" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B11" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="45"/>
-      <c r="D11" s="50" t="e">
+      <c r="C11" s="35"/>
+      <c r="D11" s="40" t="e">
         <f>D9/D10</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E11" s="46"/>
-      <c r="F11" s="45"/>
-      <c r="G11" s="50" t="e">
+      <c r="E11" s="36"/>
+      <c r="F11" s="35"/>
+      <c r="G11" s="40" t="e">
         <f>G9/G10</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H11" s="46"/>
-      <c r="I11" s="45"/>
-      <c r="J11" s="50" t="e">
+      <c r="H11" s="36"/>
+      <c r="I11" s="35"/>
+      <c r="J11" s="40" t="e">
         <f>J9/J10</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K11" s="46"/>
-      <c r="L11" s="45"/>
-      <c r="M11" s="50" t="e">
+      <c r="K11" s="36"/>
+      <c r="L11" s="35"/>
+      <c r="M11" s="40" t="e">
         <f>M9/M10</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="N11" s="46"/>
-      <c r="O11" s="45"/>
-      <c r="P11" s="50" t="e">
+      <c r="N11" s="36"/>
+      <c r="O11" s="35"/>
+      <c r="P11" s="40" t="e">
         <f>P9/P10</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q11" s="46"/>
-      <c r="R11" s="45"/>
-      <c r="S11" s="50" t="e">
+      <c r="Q11" s="36"/>
+      <c r="R11" s="35"/>
+      <c r="S11" s="40" t="e">
         <f>S9/S10</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="T11" s="46"/>
-      <c r="U11" s="45"/>
-      <c r="V11" s="50" t="e">
+      <c r="T11" s="36"/>
+      <c r="U11" s="35"/>
+      <c r="V11" s="40" t="e">
         <f>V9/V10</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="W11" s="46"/>
-      <c r="X11" s="45"/>
-      <c r="Y11" s="50" t="e">
+      <c r="W11" s="36"/>
+      <c r="X11" s="35"/>
+      <c r="Y11" s="40" t="e">
         <f>Y9/Y10</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z11" s="46"/>
-      <c r="AA11" s="45"/>
-      <c r="AB11" s="50" t="e">
+      <c r="Z11" s="36"/>
+      <c r="AA11" s="35"/>
+      <c r="AB11" s="40" t="e">
         <f>AB9/AB10</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC11" s="46"/>
-      <c r="AD11" s="45"/>
-      <c r="AE11" s="50" t="e">
+      <c r="AC11" s="36"/>
+      <c r="AD11" s="35"/>
+      <c r="AE11" s="40" t="e">
         <f>AE9/AE10</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF11" s="46"/>
-      <c r="AG11" s="45"/>
-      <c r="AH11" s="50" t="e">
+      <c r="AF11" s="36"/>
+      <c r="AG11" s="35"/>
+      <c r="AH11" s="40" t="e">
         <f>AH9/AH10</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AI11" s="46"/>
-      <c r="AJ11" s="45"/>
-      <c r="AK11" s="50" t="e">
+      <c r="AI11" s="36"/>
+      <c r="AJ11" s="35"/>
+      <c r="AK11" s="40" t="e">
         <f>AK9/AK10</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AL11" s="46"/>
-      <c r="AM11" s="45"/>
-      <c r="AN11" s="50" t="e">
+      <c r="AL11" s="36"/>
+      <c r="AM11" s="35"/>
+      <c r="AN11" s="40" t="e">
         <f>AN9/AN10</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AO11" s="46"/>
-      <c r="AP11" s="45"/>
-      <c r="AQ11" s="50" t="e">
+      <c r="AO11" s="36"/>
+      <c r="AP11" s="35"/>
+      <c r="AQ11" s="40" t="e">
         <f>AQ9/AQ10</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AR11" s="46"/>
+      <c r="AR11" s="36"/>
     </row>
     <row r="12" spans="1:44" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B12" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="45"/>
+      <c r="C12" s="35"/>
       <c r="D12" s="18"/>
-      <c r="E12" s="46"/>
-      <c r="F12" s="45"/>
+      <c r="E12" s="36"/>
+      <c r="F12" s="35"/>
       <c r="G12" s="18"/>
-      <c r="H12" s="46"/>
-      <c r="I12" s="45"/>
+      <c r="H12" s="36"/>
+      <c r="I12" s="35"/>
       <c r="J12" s="18"/>
-      <c r="K12" s="46"/>
-      <c r="L12" s="45"/>
+      <c r="K12" s="36"/>
+      <c r="L12" s="35"/>
       <c r="M12" s="18"/>
-      <c r="N12" s="46"/>
-      <c r="O12" s="45"/>
+      <c r="N12" s="36"/>
+      <c r="O12" s="35"/>
       <c r="P12" s="18"/>
-      <c r="Q12" s="46"/>
-      <c r="R12" s="45"/>
+      <c r="Q12" s="36"/>
+      <c r="R12" s="35"/>
       <c r="S12" s="18"/>
-      <c r="T12" s="46"/>
-      <c r="U12" s="45"/>
+      <c r="T12" s="36"/>
+      <c r="U12" s="35"/>
       <c r="V12" s="18"/>
-      <c r="W12" s="46"/>
-      <c r="X12" s="45"/>
+      <c r="W12" s="36"/>
+      <c r="X12" s="35"/>
       <c r="Y12" s="18"/>
-      <c r="Z12" s="46"/>
-      <c r="AA12" s="45"/>
+      <c r="Z12" s="36"/>
+      <c r="AA12" s="35"/>
       <c r="AB12" s="18"/>
-      <c r="AC12" s="46"/>
-      <c r="AD12" s="45"/>
+      <c r="AC12" s="36"/>
+      <c r="AD12" s="35"/>
       <c r="AE12" s="18"/>
-      <c r="AF12" s="46"/>
-      <c r="AG12" s="45"/>
+      <c r="AF12" s="36"/>
+      <c r="AG12" s="35"/>
       <c r="AH12" s="18"/>
-      <c r="AI12" s="46"/>
-      <c r="AJ12" s="45"/>
+      <c r="AI12" s="36"/>
+      <c r="AJ12" s="35"/>
       <c r="AK12" s="18"/>
-      <c r="AL12" s="46"/>
-      <c r="AM12" s="45"/>
+      <c r="AL12" s="36"/>
+      <c r="AM12" s="35"/>
       <c r="AN12" s="18"/>
-      <c r="AO12" s="46"/>
-      <c r="AP12" s="45"/>
+      <c r="AO12" s="36"/>
+      <c r="AP12" s="35"/>
       <c r="AQ12" s="18"/>
-      <c r="AR12" s="46"/>
+      <c r="AR12" s="36"/>
     </row>
     <row r="13" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B13" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="45"/>
+      <c r="C13" s="35"/>
       <c r="D13" s="18"/>
-      <c r="E13" s="46"/>
-      <c r="F13" s="45"/>
+      <c r="E13" s="36"/>
+      <c r="F13" s="35"/>
       <c r="G13" s="18"/>
-      <c r="H13" s="46"/>
-      <c r="I13" s="45"/>
+      <c r="H13" s="36"/>
+      <c r="I13" s="35"/>
       <c r="J13" s="18"/>
-      <c r="K13" s="46"/>
-      <c r="L13" s="45"/>
+      <c r="K13" s="36"/>
+      <c r="L13" s="35"/>
       <c r="M13" s="18"/>
-      <c r="N13" s="46"/>
-      <c r="O13" s="45"/>
+      <c r="N13" s="36"/>
+      <c r="O13" s="35"/>
       <c r="P13" s="18"/>
-      <c r="Q13" s="46"/>
-      <c r="R13" s="45"/>
+      <c r="Q13" s="36"/>
+      <c r="R13" s="35"/>
       <c r="S13" s="18"/>
-      <c r="T13" s="46"/>
-      <c r="U13" s="45"/>
+      <c r="T13" s="36"/>
+      <c r="U13" s="35"/>
       <c r="V13" s="18"/>
-      <c r="W13" s="46"/>
-      <c r="X13" s="45"/>
+      <c r="W13" s="36"/>
+      <c r="X13" s="35"/>
       <c r="Y13" s="18"/>
-      <c r="Z13" s="46"/>
-      <c r="AA13" s="45"/>
+      <c r="Z13" s="36"/>
+      <c r="AA13" s="35"/>
       <c r="AB13" s="18"/>
-      <c r="AC13" s="46"/>
-      <c r="AD13" s="45"/>
+      <c r="AC13" s="36"/>
+      <c r="AD13" s="35"/>
       <c r="AE13" s="18"/>
-      <c r="AF13" s="46"/>
-      <c r="AG13" s="45"/>
+      <c r="AF13" s="36"/>
+      <c r="AG13" s="35"/>
       <c r="AH13" s="18"/>
-      <c r="AI13" s="46"/>
-      <c r="AJ13" s="45"/>
+      <c r="AI13" s="36"/>
+      <c r="AJ13" s="35"/>
       <c r="AK13" s="18"/>
-      <c r="AL13" s="46"/>
-      <c r="AM13" s="45"/>
+      <c r="AL13" s="36"/>
+      <c r="AM13" s="35"/>
       <c r="AN13" s="18"/>
-      <c r="AO13" s="46"/>
-      <c r="AP13" s="45"/>
+      <c r="AO13" s="36"/>
+      <c r="AP13" s="35"/>
       <c r="AQ13" s="18"/>
-      <c r="AR13" s="46"/>
+      <c r="AR13" s="36"/>
     </row>
     <row r="14" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B14" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="45"/>
+      <c r="C14" s="35"/>
       <c r="D14" s="18"/>
-      <c r="E14" s="46"/>
-      <c r="F14" s="45"/>
+      <c r="E14" s="36"/>
+      <c r="F14" s="35"/>
       <c r="G14" s="18"/>
-      <c r="H14" s="46"/>
-      <c r="I14" s="45"/>
+      <c r="H14" s="36"/>
+      <c r="I14" s="35"/>
       <c r="J14" s="18"/>
-      <c r="K14" s="46"/>
-      <c r="L14" s="45"/>
+      <c r="K14" s="36"/>
+      <c r="L14" s="35"/>
       <c r="M14" s="18"/>
-      <c r="N14" s="46"/>
-      <c r="O14" s="45"/>
+      <c r="N14" s="36"/>
+      <c r="O14" s="35"/>
       <c r="P14" s="18"/>
-      <c r="Q14" s="46"/>
-      <c r="R14" s="45"/>
+      <c r="Q14" s="36"/>
+      <c r="R14" s="35"/>
       <c r="S14" s="18"/>
-      <c r="T14" s="46"/>
-      <c r="U14" s="45"/>
+      <c r="T14" s="36"/>
+      <c r="U14" s="35"/>
       <c r="V14" s="18"/>
-      <c r="W14" s="46"/>
-      <c r="X14" s="45"/>
+      <c r="W14" s="36"/>
+      <c r="X14" s="35"/>
       <c r="Y14" s="18"/>
-      <c r="Z14" s="46"/>
-      <c r="AA14" s="45"/>
+      <c r="Z14" s="36"/>
+      <c r="AA14" s="35"/>
       <c r="AB14" s="18"/>
-      <c r="AC14" s="46"/>
-      <c r="AD14" s="45"/>
+      <c r="AC14" s="36"/>
+      <c r="AD14" s="35"/>
       <c r="AE14" s="18"/>
-      <c r="AF14" s="46"/>
-      <c r="AG14" s="45"/>
+      <c r="AF14" s="36"/>
+      <c r="AG14" s="35"/>
       <c r="AH14" s="18"/>
-      <c r="AI14" s="46"/>
-      <c r="AJ14" s="45"/>
+      <c r="AI14" s="36"/>
+      <c r="AJ14" s="35"/>
       <c r="AK14" s="18"/>
-      <c r="AL14" s="46"/>
-      <c r="AM14" s="45"/>
+      <c r="AL14" s="36"/>
+      <c r="AM14" s="35"/>
       <c r="AN14" s="18"/>
-      <c r="AO14" s="46"/>
-      <c r="AP14" s="45"/>
+      <c r="AO14" s="36"/>
+      <c r="AP14" s="35"/>
       <c r="AQ14" s="18"/>
-      <c r="AR14" s="46"/>
+      <c r="AR14" s="36"/>
     </row>
     <row r="15" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B15" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="45"/>
+      <c r="C15" s="35"/>
       <c r="D15" s="19"/>
-      <c r="E15" s="46"/>
-      <c r="F15" s="45"/>
+      <c r="E15" s="36"/>
+      <c r="F15" s="35"/>
       <c r="G15" s="19"/>
-      <c r="H15" s="46"/>
-      <c r="I15" s="45"/>
+      <c r="H15" s="36"/>
+      <c r="I15" s="35"/>
       <c r="J15" s="19"/>
-      <c r="K15" s="46"/>
-      <c r="L15" s="45"/>
+      <c r="K15" s="36"/>
+      <c r="L15" s="35"/>
       <c r="M15" s="19"/>
-      <c r="N15" s="46"/>
-      <c r="O15" s="45"/>
+      <c r="N15" s="36"/>
+      <c r="O15" s="35"/>
       <c r="P15" s="19"/>
-      <c r="Q15" s="46"/>
-      <c r="R15" s="45"/>
+      <c r="Q15" s="36"/>
+      <c r="R15" s="35"/>
       <c r="S15" s="19"/>
-      <c r="T15" s="46"/>
-      <c r="U15" s="45"/>
+      <c r="T15" s="36"/>
+      <c r="U15" s="35"/>
       <c r="V15" s="19"/>
-      <c r="W15" s="46"/>
-      <c r="X15" s="45"/>
+      <c r="W15" s="36"/>
+      <c r="X15" s="35"/>
       <c r="Y15" s="19"/>
-      <c r="Z15" s="46"/>
-      <c r="AA15" s="45"/>
+      <c r="Z15" s="36"/>
+      <c r="AA15" s="35"/>
       <c r="AB15" s="19"/>
-      <c r="AC15" s="46"/>
-      <c r="AD15" s="45"/>
+      <c r="AC15" s="36"/>
+      <c r="AD15" s="35"/>
       <c r="AE15" s="19"/>
-      <c r="AF15" s="46"/>
-      <c r="AG15" s="45"/>
+      <c r="AF15" s="36"/>
+      <c r="AG15" s="35"/>
       <c r="AH15" s="19"/>
-      <c r="AI15" s="46"/>
-      <c r="AJ15" s="45"/>
+      <c r="AI15" s="36"/>
+      <c r="AJ15" s="35"/>
       <c r="AK15" s="19"/>
-      <c r="AL15" s="46"/>
-      <c r="AM15" s="45"/>
+      <c r="AL15" s="36"/>
+      <c r="AM15" s="35"/>
       <c r="AN15" s="19"/>
-      <c r="AO15" s="46"/>
-      <c r="AP15" s="45"/>
+      <c r="AO15" s="36"/>
+      <c r="AP15" s="35"/>
       <c r="AQ15" s="19"/>
-      <c r="AR15" s="46"/>
+      <c r="AR15" s="36"/>
     </row>
     <row r="16" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B16" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="45"/>
+      <c r="C16" s="35"/>
       <c r="D16" s="18"/>
-      <c r="E16" s="46"/>
-      <c r="F16" s="45"/>
+      <c r="E16" s="36"/>
+      <c r="F16" s="35"/>
       <c r="G16" s="18"/>
-      <c r="H16" s="46"/>
-      <c r="I16" s="45"/>
+      <c r="H16" s="36"/>
+      <c r="I16" s="35"/>
       <c r="J16" s="18"/>
-      <c r="K16" s="46"/>
-      <c r="L16" s="45"/>
+      <c r="K16" s="36"/>
+      <c r="L16" s="35"/>
       <c r="M16" s="18"/>
-      <c r="N16" s="46"/>
-      <c r="O16" s="45"/>
+      <c r="N16" s="36"/>
+      <c r="O16" s="35"/>
       <c r="P16" s="18"/>
-      <c r="Q16" s="46"/>
-      <c r="R16" s="45"/>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="35"/>
       <c r="S16" s="18"/>
-      <c r="T16" s="46"/>
-      <c r="U16" s="45"/>
+      <c r="T16" s="36"/>
+      <c r="U16" s="35"/>
       <c r="V16" s="18"/>
-      <c r="W16" s="46"/>
-      <c r="X16" s="45"/>
+      <c r="W16" s="36"/>
+      <c r="X16" s="35"/>
       <c r="Y16" s="18"/>
-      <c r="Z16" s="46"/>
-      <c r="AA16" s="45"/>
+      <c r="Z16" s="36"/>
+      <c r="AA16" s="35"/>
       <c r="AB16" s="18"/>
-      <c r="AC16" s="46"/>
-      <c r="AD16" s="45"/>
+      <c r="AC16" s="36"/>
+      <c r="AD16" s="35"/>
       <c r="AE16" s="18"/>
-      <c r="AF16" s="46"/>
-      <c r="AG16" s="45"/>
+      <c r="AF16" s="36"/>
+      <c r="AG16" s="35"/>
       <c r="AH16" s="18"/>
-      <c r="AI16" s="46"/>
-      <c r="AJ16" s="45"/>
+      <c r="AI16" s="36"/>
+      <c r="AJ16" s="35"/>
       <c r="AK16" s="18"/>
-      <c r="AL16" s="46"/>
-      <c r="AM16" s="45"/>
+      <c r="AL16" s="36"/>
+      <c r="AM16" s="35"/>
       <c r="AN16" s="18"/>
-      <c r="AO16" s="46"/>
-      <c r="AP16" s="45"/>
+      <c r="AO16" s="36"/>
+      <c r="AP16" s="35"/>
       <c r="AQ16" s="18"/>
-      <c r="AR16" s="46"/>
+      <c r="AR16" s="36"/>
     </row>
     <row r="17" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B17" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="C17" s="45"/>
+        <v>42</v>
+      </c>
+      <c r="C17" s="35"/>
       <c r="D17" s="18"/>
-      <c r="E17" s="46"/>
-      <c r="F17" s="45"/>
+      <c r="E17" s="36"/>
+      <c r="F17" s="35"/>
       <c r="G17" s="18"/>
-      <c r="H17" s="46"/>
-      <c r="I17" s="45"/>
+      <c r="H17" s="36"/>
+      <c r="I17" s="35"/>
       <c r="J17" s="18"/>
-      <c r="K17" s="46"/>
-      <c r="L17" s="45"/>
+      <c r="K17" s="36"/>
+      <c r="L17" s="35"/>
       <c r="M17" s="18"/>
-      <c r="N17" s="46"/>
-      <c r="O17" s="45"/>
+      <c r="N17" s="36"/>
+      <c r="O17" s="35"/>
       <c r="P17" s="18"/>
-      <c r="Q17" s="46"/>
-      <c r="R17" s="45"/>
+      <c r="Q17" s="36"/>
+      <c r="R17" s="35"/>
       <c r="S17" s="18"/>
-      <c r="T17" s="46"/>
-      <c r="U17" s="45"/>
+      <c r="T17" s="36"/>
+      <c r="U17" s="35"/>
       <c r="V17" s="18"/>
-      <c r="W17" s="46"/>
-      <c r="X17" s="45"/>
+      <c r="W17" s="36"/>
+      <c r="X17" s="35"/>
       <c r="Y17" s="18"/>
-      <c r="Z17" s="46"/>
-      <c r="AA17" s="45"/>
+      <c r="Z17" s="36"/>
+      <c r="AA17" s="35"/>
       <c r="AB17" s="18"/>
-      <c r="AC17" s="46"/>
-      <c r="AD17" s="45"/>
+      <c r="AC17" s="36"/>
+      <c r="AD17" s="35"/>
       <c r="AE17" s="18"/>
-      <c r="AF17" s="46"/>
-      <c r="AG17" s="45"/>
+      <c r="AF17" s="36"/>
+      <c r="AG17" s="35"/>
       <c r="AH17" s="18"/>
-      <c r="AI17" s="46"/>
-      <c r="AJ17" s="45"/>
+      <c r="AI17" s="36"/>
+      <c r="AJ17" s="35"/>
       <c r="AK17" s="18"/>
-      <c r="AL17" s="46"/>
-      <c r="AM17" s="45"/>
+      <c r="AL17" s="36"/>
+      <c r="AM17" s="35"/>
       <c r="AN17" s="18"/>
-      <c r="AO17" s="46"/>
-      <c r="AP17" s="45"/>
+      <c r="AO17" s="36"/>
+      <c r="AP17" s="35"/>
       <c r="AQ17" s="18"/>
-      <c r="AR17" s="46"/>
+      <c r="AR17" s="36"/>
     </row>
     <row r="18" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B18" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="C18" s="45"/>
+        <v>43</v>
+      </c>
+      <c r="C18" s="35"/>
       <c r="D18" s="18"/>
-      <c r="E18" s="46"/>
-      <c r="F18" s="45"/>
+      <c r="E18" s="36"/>
+      <c r="F18" s="35"/>
       <c r="G18" s="18"/>
-      <c r="H18" s="46"/>
-      <c r="I18" s="45"/>
+      <c r="H18" s="36"/>
+      <c r="I18" s="35"/>
       <c r="J18" s="18"/>
-      <c r="K18" s="46"/>
-      <c r="L18" s="45"/>
+      <c r="K18" s="36"/>
+      <c r="L18" s="35"/>
       <c r="M18" s="18"/>
-      <c r="N18" s="46"/>
-      <c r="O18" s="45"/>
+      <c r="N18" s="36"/>
+      <c r="O18" s="35"/>
       <c r="P18" s="18"/>
-      <c r="Q18" s="46"/>
-      <c r="R18" s="45"/>
+      <c r="Q18" s="36"/>
+      <c r="R18" s="35"/>
       <c r="S18" s="18"/>
-      <c r="T18" s="46"/>
-      <c r="U18" s="45"/>
+      <c r="T18" s="36"/>
+      <c r="U18" s="35"/>
       <c r="V18" s="18"/>
-      <c r="W18" s="46"/>
-      <c r="X18" s="45"/>
+      <c r="W18" s="36"/>
+      <c r="X18" s="35"/>
       <c r="Y18" s="18"/>
-      <c r="Z18" s="46"/>
-      <c r="AA18" s="45"/>
+      <c r="Z18" s="36"/>
+      <c r="AA18" s="35"/>
       <c r="AB18" s="18"/>
-      <c r="AC18" s="46"/>
-      <c r="AD18" s="45"/>
+      <c r="AC18" s="36"/>
+      <c r="AD18" s="35"/>
       <c r="AE18" s="18"/>
-      <c r="AF18" s="46"/>
-      <c r="AG18" s="45"/>
+      <c r="AF18" s="36"/>
+      <c r="AG18" s="35"/>
       <c r="AH18" s="18"/>
-      <c r="AI18" s="46"/>
-      <c r="AJ18" s="45"/>
+      <c r="AI18" s="36"/>
+      <c r="AJ18" s="35"/>
       <c r="AK18" s="18"/>
-      <c r="AL18" s="46"/>
-      <c r="AM18" s="45"/>
+      <c r="AL18" s="36"/>
+      <c r="AM18" s="35"/>
       <c r="AN18" s="18"/>
-      <c r="AO18" s="46"/>
-      <c r="AP18" s="45"/>
+      <c r="AO18" s="36"/>
+      <c r="AP18" s="35"/>
       <c r="AQ18" s="18"/>
-      <c r="AR18" s="46"/>
+      <c r="AR18" s="36"/>
     </row>
     <row r="19" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B19" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="45"/>
+      <c r="C19" s="35"/>
       <c r="D19" s="18"/>
-      <c r="E19" s="46"/>
-      <c r="F19" s="45"/>
+      <c r="E19" s="36"/>
+      <c r="F19" s="35"/>
       <c r="G19" s="18"/>
-      <c r="H19" s="46"/>
-      <c r="I19" s="45"/>
+      <c r="H19" s="36"/>
+      <c r="I19" s="35"/>
       <c r="J19" s="18"/>
-      <c r="K19" s="46"/>
-      <c r="L19" s="45"/>
+      <c r="K19" s="36"/>
+      <c r="L19" s="35"/>
       <c r="M19" s="18"/>
-      <c r="N19" s="46"/>
-      <c r="O19" s="45"/>
+      <c r="N19" s="36"/>
+      <c r="O19" s="35"/>
       <c r="P19" s="18"/>
-      <c r="Q19" s="46"/>
-      <c r="R19" s="45"/>
+      <c r="Q19" s="36"/>
+      <c r="R19" s="35"/>
       <c r="S19" s="18"/>
-      <c r="T19" s="46"/>
-      <c r="U19" s="45"/>
+      <c r="T19" s="36"/>
+      <c r="U19" s="35"/>
       <c r="V19" s="18"/>
-      <c r="W19" s="46"/>
-      <c r="X19" s="45"/>
+      <c r="W19" s="36"/>
+      <c r="X19" s="35"/>
       <c r="Y19" s="18"/>
-      <c r="Z19" s="46"/>
-      <c r="AA19" s="45"/>
+      <c r="Z19" s="36"/>
+      <c r="AA19" s="35"/>
       <c r="AB19" s="18"/>
-      <c r="AC19" s="46"/>
-      <c r="AD19" s="45"/>
+      <c r="AC19" s="36"/>
+      <c r="AD19" s="35"/>
       <c r="AE19" s="18"/>
-      <c r="AF19" s="46"/>
-      <c r="AG19" s="45"/>
+      <c r="AF19" s="36"/>
+      <c r="AG19" s="35"/>
       <c r="AH19" s="18"/>
-      <c r="AI19" s="46"/>
-      <c r="AJ19" s="45"/>
+      <c r="AI19" s="36"/>
+      <c r="AJ19" s="35"/>
       <c r="AK19" s="18"/>
-      <c r="AL19" s="46"/>
-      <c r="AM19" s="45"/>
+      <c r="AL19" s="36"/>
+      <c r="AM19" s="35"/>
       <c r="AN19" s="18"/>
-      <c r="AO19" s="46"/>
-      <c r="AP19" s="45"/>
+      <c r="AO19" s="36"/>
+      <c r="AP19" s="35"/>
       <c r="AQ19" s="18"/>
-      <c r="AR19" s="46"/>
+      <c r="AR19" s="36"/>
     </row>
     <row r="20" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B20" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="C20" s="45"/>
-      <c r="D20" s="50" t="e">
+      <c r="C20" s="35"/>
+      <c r="D20" s="40" t="e">
         <f>D17/D19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E20" s="46"/>
-      <c r="F20" s="45"/>
-      <c r="G20" s="50" t="e">
+      <c r="E20" s="36"/>
+      <c r="F20" s="35"/>
+      <c r="G20" s="40" t="e">
         <f>G17/G19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H20" s="46"/>
-      <c r="I20" s="45"/>
-      <c r="J20" s="50" t="e">
+      <c r="H20" s="36"/>
+      <c r="I20" s="35"/>
+      <c r="J20" s="40" t="e">
         <f>J17/J19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K20" s="46"/>
-      <c r="L20" s="45"/>
-      <c r="M20" s="50" t="e">
+      <c r="K20" s="36"/>
+      <c r="L20" s="35"/>
+      <c r="M20" s="40" t="e">
         <f>M17/M19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="N20" s="46"/>
-      <c r="O20" s="45"/>
-      <c r="P20" s="50" t="e">
+      <c r="N20" s="36"/>
+      <c r="O20" s="35"/>
+      <c r="P20" s="40" t="e">
         <f>P17/P19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q20" s="46"/>
-      <c r="R20" s="45"/>
-      <c r="S20" s="50" t="e">
+      <c r="Q20" s="36"/>
+      <c r="R20" s="35"/>
+      <c r="S20" s="40" t="e">
         <f>S17/S19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="T20" s="46"/>
-      <c r="U20" s="45"/>
-      <c r="V20" s="50" t="e">
+      <c r="T20" s="36"/>
+      <c r="U20" s="35"/>
+      <c r="V20" s="40" t="e">
         <f>V17/V19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="W20" s="46"/>
-      <c r="X20" s="45"/>
-      <c r="Y20" s="50" t="e">
+      <c r="W20" s="36"/>
+      <c r="X20" s="35"/>
+      <c r="Y20" s="40" t="e">
         <f>Y17/Y19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z20" s="46"/>
-      <c r="AA20" s="45"/>
-      <c r="AB20" s="50" t="e">
+      <c r="Z20" s="36"/>
+      <c r="AA20" s="35"/>
+      <c r="AB20" s="40" t="e">
         <f>AB17/AB19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC20" s="46"/>
-      <c r="AD20" s="45"/>
-      <c r="AE20" s="50" t="e">
+      <c r="AC20" s="36"/>
+      <c r="AD20" s="35"/>
+      <c r="AE20" s="40" t="e">
         <f>AE17/AE19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF20" s="46"/>
-      <c r="AG20" s="45"/>
-      <c r="AH20" s="50" t="e">
+      <c r="AF20" s="36"/>
+      <c r="AG20" s="35"/>
+      <c r="AH20" s="40" t="e">
         <f>AH17/AH19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AI20" s="46"/>
-      <c r="AJ20" s="45"/>
-      <c r="AK20" s="50" t="e">
+      <c r="AI20" s="36"/>
+      <c r="AJ20" s="35"/>
+      <c r="AK20" s="40" t="e">
         <f>AK17/AK19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AL20" s="46"/>
-      <c r="AM20" s="45"/>
-      <c r="AN20" s="50" t="e">
+      <c r="AL20" s="36"/>
+      <c r="AM20" s="35"/>
+      <c r="AN20" s="40" t="e">
         <f>AN17/AN19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AO20" s="46"/>
-      <c r="AP20" s="45"/>
-      <c r="AQ20" s="50" t="e">
+      <c r="AO20" s="36"/>
+      <c r="AP20" s="35"/>
+      <c r="AQ20" s="40" t="e">
         <f>AQ17/AQ19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AR20" s="46"/>
+      <c r="AR20" s="36"/>
     </row>
     <row r="21" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B21" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="C21" s="45"/>
+      <c r="C21" s="35"/>
       <c r="D21" s="18"/>
-      <c r="E21" s="46"/>
-      <c r="F21" s="45"/>
+      <c r="E21" s="36"/>
+      <c r="F21" s="35"/>
       <c r="G21" s="18"/>
-      <c r="H21" s="46"/>
-      <c r="I21" s="45"/>
+      <c r="H21" s="36"/>
+      <c r="I21" s="35"/>
       <c r="J21" s="18"/>
-      <c r="K21" s="46"/>
-      <c r="L21" s="45"/>
+      <c r="K21" s="36"/>
+      <c r="L21" s="35"/>
       <c r="M21" s="18"/>
-      <c r="N21" s="46"/>
-      <c r="O21" s="45"/>
+      <c r="N21" s="36"/>
+      <c r="O21" s="35"/>
       <c r="P21" s="18"/>
-      <c r="Q21" s="46"/>
-      <c r="R21" s="45"/>
+      <c r="Q21" s="36"/>
+      <c r="R21" s="35"/>
       <c r="S21" s="18"/>
-      <c r="T21" s="46"/>
-      <c r="U21" s="45"/>
+      <c r="T21" s="36"/>
+      <c r="U21" s="35"/>
       <c r="V21" s="18"/>
-      <c r="W21" s="46"/>
-      <c r="X21" s="45"/>
+      <c r="W21" s="36"/>
+      <c r="X21" s="35"/>
       <c r="Y21" s="18"/>
-      <c r="Z21" s="46"/>
-      <c r="AA21" s="45"/>
+      <c r="Z21" s="36"/>
+      <c r="AA21" s="35"/>
       <c r="AB21" s="18"/>
-      <c r="AC21" s="46"/>
-      <c r="AD21" s="45"/>
+      <c r="AC21" s="36"/>
+      <c r="AD21" s="35"/>
       <c r="AE21" s="18"/>
-      <c r="AF21" s="46"/>
-      <c r="AG21" s="45"/>
+      <c r="AF21" s="36"/>
+      <c r="AG21" s="35"/>
       <c r="AH21" s="18"/>
-      <c r="AI21" s="46"/>
-      <c r="AJ21" s="45"/>
+      <c r="AI21" s="36"/>
+      <c r="AJ21" s="35"/>
       <c r="AK21" s="18"/>
-      <c r="AL21" s="46"/>
-      <c r="AM21" s="45"/>
+      <c r="AL21" s="36"/>
+      <c r="AM21" s="35"/>
       <c r="AN21" s="18"/>
-      <c r="AO21" s="46"/>
-      <c r="AP21" s="45"/>
+      <c r="AO21" s="36"/>
+      <c r="AP21" s="35"/>
       <c r="AQ21" s="18"/>
-      <c r="AR21" s="46"/>
+      <c r="AR21" s="36"/>
     </row>
     <row r="22" spans="1:44" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B22" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="45"/>
+      <c r="C22" s="35"/>
       <c r="D22" s="18"/>
-      <c r="E22" s="46"/>
-      <c r="F22" s="45"/>
+      <c r="E22" s="36"/>
+      <c r="F22" s="35"/>
       <c r="G22" s="18"/>
-      <c r="H22" s="46"/>
-      <c r="I22" s="45"/>
+      <c r="H22" s="36"/>
+      <c r="I22" s="35"/>
       <c r="J22" s="18"/>
-      <c r="K22" s="46"/>
-      <c r="L22" s="45"/>
+      <c r="K22" s="36"/>
+      <c r="L22" s="35"/>
       <c r="M22" s="18"/>
-      <c r="N22" s="46"/>
-      <c r="O22" s="45"/>
+      <c r="N22" s="36"/>
+      <c r="O22" s="35"/>
       <c r="P22" s="18"/>
-      <c r="Q22" s="46"/>
-      <c r="R22" s="45"/>
+      <c r="Q22" s="36"/>
+      <c r="R22" s="35"/>
       <c r="S22" s="18"/>
-      <c r="T22" s="46"/>
-      <c r="U22" s="45"/>
+      <c r="T22" s="36"/>
+      <c r="U22" s="35"/>
       <c r="V22" s="18"/>
-      <c r="W22" s="46"/>
-      <c r="X22" s="45"/>
+      <c r="W22" s="36"/>
+      <c r="X22" s="35"/>
       <c r="Y22" s="18"/>
-      <c r="Z22" s="46"/>
-      <c r="AA22" s="45"/>
+      <c r="Z22" s="36"/>
+      <c r="AA22" s="35"/>
       <c r="AB22" s="18"/>
-      <c r="AC22" s="46"/>
-      <c r="AD22" s="45"/>
+      <c r="AC22" s="36"/>
+      <c r="AD22" s="35"/>
       <c r="AE22" s="18"/>
-      <c r="AF22" s="46"/>
-      <c r="AG22" s="45"/>
+      <c r="AF22" s="36"/>
+      <c r="AG22" s="35"/>
       <c r="AH22" s="18"/>
-      <c r="AI22" s="46"/>
-      <c r="AJ22" s="45"/>
+      <c r="AI22" s="36"/>
+      <c r="AJ22" s="35"/>
       <c r="AK22" s="18"/>
-      <c r="AL22" s="46"/>
-      <c r="AM22" s="45"/>
+      <c r="AL22" s="36"/>
+      <c r="AM22" s="35"/>
       <c r="AN22" s="18"/>
-      <c r="AO22" s="46"/>
-      <c r="AP22" s="45"/>
+      <c r="AO22" s="36"/>
+      <c r="AP22" s="35"/>
       <c r="AQ22" s="18"/>
-      <c r="AR22" s="46"/>
+      <c r="AR22" s="36"/>
     </row>
     <row r="23" spans="1:44" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B23" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C23" s="45"/>
+      <c r="C23" s="35"/>
       <c r="D23" s="18"/>
-      <c r="E23" s="46"/>
-      <c r="F23" s="45"/>
+      <c r="E23" s="36"/>
+      <c r="F23" s="35"/>
       <c r="G23" s="18"/>
-      <c r="H23" s="46"/>
-      <c r="I23" s="45"/>
+      <c r="H23" s="36"/>
+      <c r="I23" s="35"/>
       <c r="J23" s="18"/>
-      <c r="K23" s="46"/>
-      <c r="L23" s="45"/>
+      <c r="K23" s="36"/>
+      <c r="L23" s="35"/>
       <c r="M23" s="18"/>
-      <c r="N23" s="46"/>
-      <c r="O23" s="45"/>
+      <c r="N23" s="36"/>
+      <c r="O23" s="35"/>
       <c r="P23" s="18"/>
-      <c r="Q23" s="46"/>
-      <c r="R23" s="45"/>
+      <c r="Q23" s="36"/>
+      <c r="R23" s="35"/>
       <c r="S23" s="18"/>
-      <c r="T23" s="46"/>
-      <c r="U23" s="45"/>
+      <c r="T23" s="36"/>
+      <c r="U23" s="35"/>
       <c r="V23" s="18"/>
-      <c r="W23" s="46"/>
-      <c r="X23" s="45"/>
+      <c r="W23" s="36"/>
+      <c r="X23" s="35"/>
       <c r="Y23" s="18"/>
-      <c r="Z23" s="46"/>
-      <c r="AA23" s="45"/>
+      <c r="Z23" s="36"/>
+      <c r="AA23" s="35"/>
       <c r="AB23" s="18"/>
-      <c r="AC23" s="46"/>
-      <c r="AD23" s="45"/>
+      <c r="AC23" s="36"/>
+      <c r="AD23" s="35"/>
       <c r="AE23" s="18"/>
-      <c r="AF23" s="46"/>
-      <c r="AG23" s="45"/>
+      <c r="AF23" s="36"/>
+      <c r="AG23" s="35"/>
       <c r="AH23" s="18"/>
-      <c r="AI23" s="46"/>
-      <c r="AJ23" s="45"/>
+      <c r="AI23" s="36"/>
+      <c r="AJ23" s="35"/>
       <c r="AK23" s="18"/>
-      <c r="AL23" s="46"/>
-      <c r="AM23" s="45"/>
+      <c r="AL23" s="36"/>
+      <c r="AM23" s="35"/>
       <c r="AN23" s="18"/>
-      <c r="AO23" s="46"/>
-      <c r="AP23" s="45"/>
+      <c r="AO23" s="36"/>
+      <c r="AP23" s="35"/>
       <c r="AQ23" s="18"/>
-      <c r="AR23" s="46"/>
+      <c r="AR23" s="36"/>
     </row>
     <row r="24" spans="1:44" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B24" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="C24" s="45"/>
+        <v>37</v>
+      </c>
+      <c r="C24" s="35"/>
       <c r="D24" s="18"/>
-      <c r="E24" s="46"/>
-      <c r="F24" s="45"/>
+      <c r="E24" s="36"/>
+      <c r="F24" s="35"/>
       <c r="G24" s="18"/>
-      <c r="H24" s="46"/>
-      <c r="I24" s="45"/>
+      <c r="H24" s="36"/>
+      <c r="I24" s="35"/>
       <c r="J24" s="18"/>
-      <c r="K24" s="46"/>
-      <c r="L24" s="45"/>
+      <c r="K24" s="36"/>
+      <c r="L24" s="35"/>
       <c r="M24" s="18"/>
-      <c r="N24" s="46"/>
-      <c r="O24" s="45"/>
+      <c r="N24" s="36"/>
+      <c r="O24" s="35"/>
       <c r="P24" s="18"/>
-      <c r="Q24" s="46"/>
-      <c r="R24" s="45"/>
+      <c r="Q24" s="36"/>
+      <c r="R24" s="35"/>
       <c r="S24" s="18"/>
-      <c r="T24" s="46"/>
-      <c r="U24" s="45"/>
+      <c r="T24" s="36"/>
+      <c r="U24" s="35"/>
       <c r="V24" s="18"/>
-      <c r="W24" s="46"/>
-      <c r="X24" s="45"/>
+      <c r="W24" s="36"/>
+      <c r="X24" s="35"/>
       <c r="Y24" s="18"/>
-      <c r="Z24" s="46"/>
-      <c r="AA24" s="45"/>
+      <c r="Z24" s="36"/>
+      <c r="AA24" s="35"/>
       <c r="AB24" s="18"/>
-      <c r="AC24" s="46"/>
-      <c r="AD24" s="45"/>
+      <c r="AC24" s="36"/>
+      <c r="AD24" s="35"/>
       <c r="AE24" s="18"/>
-      <c r="AF24" s="46"/>
-      <c r="AG24" s="45"/>
+      <c r="AF24" s="36"/>
+      <c r="AG24" s="35"/>
       <c r="AH24" s="18"/>
-      <c r="AI24" s="46"/>
-      <c r="AJ24" s="45"/>
+      <c r="AI24" s="36"/>
+      <c r="AJ24" s="35"/>
       <c r="AK24" s="18"/>
-      <c r="AL24" s="46"/>
-      <c r="AM24" s="45"/>
+      <c r="AL24" s="36"/>
+      <c r="AM24" s="35"/>
       <c r="AN24" s="18"/>
-      <c r="AO24" s="46"/>
-      <c r="AP24" s="45"/>
+      <c r="AO24" s="36"/>
+      <c r="AP24" s="35"/>
       <c r="AQ24" s="18"/>
-      <c r="AR24" s="46"/>
+      <c r="AR24" s="36"/>
     </row>
     <row r="25" spans="1:44" ht="76.900000000000006" x14ac:dyDescent="0.45">
       <c r="B25" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="C25" s="45"/>
+        <v>36</v>
+      </c>
+      <c r="C25" s="35"/>
       <c r="D25" s="18"/>
-      <c r="E25" s="46"/>
-      <c r="F25" s="45"/>
+      <c r="E25" s="36"/>
+      <c r="F25" s="35"/>
       <c r="G25" s="18"/>
-      <c r="H25" s="46"/>
-      <c r="I25" s="45"/>
+      <c r="H25" s="36"/>
+      <c r="I25" s="35"/>
       <c r="J25" s="18"/>
-      <c r="K25" s="46"/>
-      <c r="L25" s="45"/>
+      <c r="K25" s="36"/>
+      <c r="L25" s="35"/>
       <c r="M25" s="18"/>
-      <c r="N25" s="46"/>
-      <c r="O25" s="45"/>
+      <c r="N25" s="36"/>
+      <c r="O25" s="35"/>
       <c r="P25" s="18"/>
-      <c r="Q25" s="46"/>
-      <c r="R25" s="45"/>
+      <c r="Q25" s="36"/>
+      <c r="R25" s="35"/>
       <c r="S25" s="18"/>
-      <c r="T25" s="46"/>
-      <c r="U25" s="45"/>
+      <c r="T25" s="36"/>
+      <c r="U25" s="35"/>
       <c r="V25" s="18"/>
-      <c r="W25" s="46"/>
-      <c r="X25" s="45"/>
+      <c r="W25" s="36"/>
+      <c r="X25" s="35"/>
       <c r="Y25" s="18"/>
-      <c r="Z25" s="46"/>
-      <c r="AA25" s="45"/>
+      <c r="Z25" s="36"/>
+      <c r="AA25" s="35"/>
       <c r="AB25" s="18"/>
-      <c r="AC25" s="46"/>
-      <c r="AD25" s="45"/>
+      <c r="AC25" s="36"/>
+      <c r="AD25" s="35"/>
       <c r="AE25" s="18"/>
-      <c r="AF25" s="46"/>
-      <c r="AG25" s="45"/>
+      <c r="AF25" s="36"/>
+      <c r="AG25" s="35"/>
       <c r="AH25" s="18"/>
-      <c r="AI25" s="46"/>
-      <c r="AJ25" s="45"/>
+      <c r="AI25" s="36"/>
+      <c r="AJ25" s="35"/>
       <c r="AK25" s="18"/>
-      <c r="AL25" s="46"/>
-      <c r="AM25" s="45"/>
+      <c r="AL25" s="36"/>
+      <c r="AM25" s="35"/>
       <c r="AN25" s="18"/>
-      <c r="AO25" s="46"/>
-      <c r="AP25" s="45"/>
+      <c r="AO25" s="36"/>
+      <c r="AP25" s="35"/>
       <c r="AQ25" s="18"/>
-      <c r="AR25" s="46"/>
+      <c r="AR25" s="36"/>
     </row>
     <row r="26" spans="1:44" x14ac:dyDescent="0.45">
-      <c r="B26" s="41"/>
-      <c r="C26" s="47"/>
-      <c r="D26" s="48"/>
-      <c r="E26" s="49"/>
-      <c r="F26" s="47"/>
-      <c r="G26" s="48"/>
-      <c r="H26" s="49"/>
-      <c r="I26" s="47"/>
-      <c r="J26" s="48"/>
-      <c r="K26" s="49"/>
-      <c r="L26" s="47"/>
-      <c r="M26" s="48"/>
-      <c r="N26" s="49"/>
-      <c r="O26" s="47"/>
-      <c r="P26" s="48"/>
-      <c r="Q26" s="49"/>
-      <c r="R26" s="47"/>
-      <c r="S26" s="48"/>
-      <c r="T26" s="49"/>
-      <c r="U26" s="47"/>
-      <c r="V26" s="48"/>
-      <c r="W26" s="49"/>
-      <c r="X26" s="47"/>
-      <c r="Y26" s="48"/>
-      <c r="Z26" s="49"/>
-      <c r="AA26" s="47"/>
-      <c r="AB26" s="48"/>
-      <c r="AC26" s="49"/>
-      <c r="AD26" s="47"/>
-      <c r="AE26" s="48"/>
-      <c r="AF26" s="49"/>
-      <c r="AG26" s="47"/>
-      <c r="AH26" s="48"/>
-      <c r="AI26" s="49"/>
-      <c r="AJ26" s="47"/>
-      <c r="AK26" s="48"/>
-      <c r="AL26" s="49"/>
-      <c r="AM26" s="47"/>
-      <c r="AN26" s="48"/>
-      <c r="AO26" s="49"/>
-      <c r="AP26" s="47"/>
-      <c r="AQ26" s="48"/>
-      <c r="AR26" s="49"/>
+      <c r="B26" s="33"/>
+      <c r="C26" s="37"/>
+      <c r="D26" s="38"/>
+      <c r="E26" s="39"/>
+      <c r="F26" s="37"/>
+      <c r="G26" s="38"/>
+      <c r="H26" s="39"/>
+      <c r="I26" s="37"/>
+      <c r="J26" s="38"/>
+      <c r="K26" s="39"/>
+      <c r="L26" s="37"/>
+      <c r="M26" s="38"/>
+      <c r="N26" s="39"/>
+      <c r="O26" s="37"/>
+      <c r="P26" s="38"/>
+      <c r="Q26" s="39"/>
+      <c r="R26" s="37"/>
+      <c r="S26" s="38"/>
+      <c r="T26" s="39"/>
+      <c r="U26" s="37"/>
+      <c r="V26" s="38"/>
+      <c r="W26" s="39"/>
+      <c r="X26" s="37"/>
+      <c r="Y26" s="38"/>
+      <c r="Z26" s="39"/>
+      <c r="AA26" s="37"/>
+      <c r="AB26" s="38"/>
+      <c r="AC26" s="39"/>
+      <c r="AD26" s="37"/>
+      <c r="AE26" s="38"/>
+      <c r="AF26" s="39"/>
+      <c r="AG26" s="37"/>
+      <c r="AH26" s="38"/>
+      <c r="AI26" s="39"/>
+      <c r="AJ26" s="37"/>
+      <c r="AK26" s="38"/>
+      <c r="AL26" s="39"/>
+      <c r="AM26" s="37"/>
+      <c r="AN26" s="38"/>
+      <c r="AO26" s="39"/>
+      <c r="AP26" s="37"/>
+      <c r="AQ26" s="38"/>
+      <c r="AR26" s="39"/>
     </row>
     <row r="27" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A27" s="1"/>
-      <c r="B27" s="44" t="s">
+      <c r="B27" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="C27" s="42">
+      <c r="C27" s="51">
         <f>AVERAGE(C4:C26)</f>
         <v>0</v>
       </c>
-      <c r="D27" s="42"/>
-      <c r="E27" s="43"/>
-      <c r="F27" s="42">
+      <c r="D27" s="51"/>
+      <c r="E27" s="52"/>
+      <c r="F27" s="51">
         <f>AVERAGE(F4:F26)</f>
         <v>0</v>
       </c>
-      <c r="G27" s="42"/>
-      <c r="H27" s="43"/>
-      <c r="I27" s="42">
+      <c r="G27" s="51"/>
+      <c r="H27" s="52"/>
+      <c r="I27" s="51">
         <f>AVERAGE(I4:I26)</f>
         <v>0</v>
       </c>
-      <c r="J27" s="42"/>
-      <c r="K27" s="43"/>
-      <c r="L27" s="42">
+      <c r="J27" s="51"/>
+      <c r="K27" s="52"/>
+      <c r="L27" s="51">
         <f>AVERAGE(L4:L26)</f>
         <v>0</v>
       </c>
-      <c r="M27" s="42"/>
-      <c r="N27" s="43"/>
-      <c r="O27" s="42">
+      <c r="M27" s="51"/>
+      <c r="N27" s="52"/>
+      <c r="O27" s="51">
         <f>AVERAGE(O4:O26)</f>
         <v>0</v>
       </c>
-      <c r="P27" s="42"/>
-      <c r="Q27" s="43"/>
-      <c r="R27" s="42">
+      <c r="P27" s="51"/>
+      <c r="Q27" s="52"/>
+      <c r="R27" s="51">
         <f>AVERAGE(R4:R26)</f>
         <v>0</v>
       </c>
-      <c r="S27" s="42"/>
-      <c r="T27" s="43"/>
-      <c r="U27" s="42">
+      <c r="S27" s="51"/>
+      <c r="T27" s="52"/>
+      <c r="U27" s="51">
         <f>AVERAGE(U4:U26)</f>
         <v>0</v>
       </c>
-      <c r="V27" s="42"/>
-      <c r="W27" s="43"/>
-      <c r="X27" s="42">
+      <c r="V27" s="51"/>
+      <c r="W27" s="52"/>
+      <c r="X27" s="51">
         <f>AVERAGE(X4:X26)</f>
         <v>0</v>
       </c>
-      <c r="Y27" s="42"/>
-      <c r="Z27" s="43"/>
-      <c r="AA27" s="42">
+      <c r="Y27" s="51"/>
+      <c r="Z27" s="52"/>
+      <c r="AA27" s="51">
         <f>AVERAGE(AA4:AA26)</f>
         <v>0</v>
       </c>
-      <c r="AB27" s="42"/>
-      <c r="AC27" s="43"/>
-      <c r="AD27" s="42">
+      <c r="AB27" s="51"/>
+      <c r="AC27" s="52"/>
+      <c r="AD27" s="51">
         <f>AVERAGE(AD4:AD26)</f>
         <v>0</v>
       </c>
-      <c r="AE27" s="42"/>
-      <c r="AF27" s="43"/>
-      <c r="AG27" s="42">
+      <c r="AE27" s="51"/>
+      <c r="AF27" s="52"/>
+      <c r="AG27" s="51">
         <f>AVERAGE(AG4:AG26)</f>
         <v>0</v>
       </c>
-      <c r="AH27" s="42"/>
-      <c r="AI27" s="43"/>
-      <c r="AJ27" s="42">
+      <c r="AH27" s="51"/>
+      <c r="AI27" s="52"/>
+      <c r="AJ27" s="51">
         <f>AVERAGE(AJ4:AJ26)</f>
         <v>0</v>
       </c>
-      <c r="AK27" s="42"/>
-      <c r="AL27" s="43"/>
-      <c r="AM27" s="42">
+      <c r="AK27" s="51"/>
+      <c r="AL27" s="52"/>
+      <c r="AM27" s="51">
         <f>AVERAGE(AM4:AM26)</f>
         <v>0</v>
       </c>
-      <c r="AN27" s="42"/>
-      <c r="AO27" s="43"/>
-      <c r="AP27" s="42">
+      <c r="AN27" s="51"/>
+      <c r="AO27" s="52"/>
+      <c r="AP27" s="51">
         <f>AVERAGE(AP4:AP26)</f>
         <v>0</v>
       </c>
-      <c r="AQ27" s="42"/>
-      <c r="AR27" s="43"/>
+      <c r="AQ27" s="51"/>
+      <c r="AR27" s="52"/>
     </row>
     <row r="28" spans="1:44" s="9" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B28" s="16"/>
@@ -5664,6 +5651,19 @@
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="R27:T27"/>
+    <mergeCell ref="U27:W27"/>
+    <mergeCell ref="AM27:AO27"/>
+    <mergeCell ref="X27:Z27"/>
+    <mergeCell ref="AA27:AC27"/>
+    <mergeCell ref="AD27:AF27"/>
+    <mergeCell ref="AG27:AI27"/>
+    <mergeCell ref="AJ27:AL27"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="O27:Q27"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="AP2:AR2"/>
     <mergeCell ref="AP27:AR27"/>
@@ -5680,19 +5680,6 @@
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="U2:W2"/>
     <mergeCell ref="R2:T2"/>
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="I27:K27"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="R27:T27"/>
-    <mergeCell ref="U27:W27"/>
-    <mergeCell ref="AM27:AO27"/>
-    <mergeCell ref="X27:Z27"/>
-    <mergeCell ref="AA27:AC27"/>
-    <mergeCell ref="AD27:AF27"/>
-    <mergeCell ref="AG27:AI27"/>
-    <mergeCell ref="AJ27:AL27"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/activity/M01A07/M01A07_Pendiente.xlsx
+++ b/activity/M01A07/M01A07_Pendiente.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.HCMC\activity\M01A07\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AB8F18C-BF28-4421-9683-DB3E56804C1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B57FBC16-9B45-48AF-8D6F-735B27E3384F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" tabRatio="762" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
   </bookViews>
@@ -532,7 +532,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -620,12 +620,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -675,6 +669,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -696,8 +693,8 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -814,7 +811,9 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="bg2"/>
+              <a:schemeClr val="bg1">
+                <a:lumMod val="85000"/>
+              </a:schemeClr>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -2106,20 +2105,20 @@
       </c>
     </row>
     <row r="2" spans="2:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B2" s="44" t="s">
+      <c r="B2" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B3" s="45"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="45"/>
+      <c r="B3" s="43"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43"/>
     </row>
     <row r="4" spans="2:6" ht="30.75" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="22" t="s">
@@ -2142,14 +2141,14 @@
       <c r="B5" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="29">
+      <c r="C5" s="52">
         <v>5</v>
       </c>
       <c r="D5" s="23">
         <f>Detalle!C27*C5/5</f>
         <v>0</v>
       </c>
-      <c r="E5" s="31"/>
+      <c r="E5" s="29"/>
       <c r="F5" s="25">
         <f>AVERAGE(D5:E5)</f>
         <v>0</v>
@@ -2159,14 +2158,14 @@
       <c r="B6" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="29">
+      <c r="C6" s="52">
         <v>5</v>
       </c>
       <c r="D6" s="23">
         <f>Detalle!F27*C6/5</f>
         <v>0</v>
       </c>
-      <c r="E6" s="31"/>
+      <c r="E6" s="29"/>
       <c r="F6" s="25">
         <f t="shared" ref="F6:F18" si="0">AVERAGE(D6:E6)</f>
         <v>0</v>
@@ -2176,14 +2175,14 @@
       <c r="B7" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="29">
+      <c r="C7" s="52">
         <v>5</v>
       </c>
       <c r="D7" s="23">
         <f>Detalle!I27*C7/5</f>
         <v>0</v>
       </c>
-      <c r="E7" s="31"/>
+      <c r="E7" s="29"/>
       <c r="F7" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2193,14 +2192,14 @@
       <c r="B8" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="29">
+      <c r="C8" s="52">
         <v>5</v>
       </c>
       <c r="D8" s="23">
         <f>Detalle!L27*C8/5</f>
         <v>0</v>
       </c>
-      <c r="E8" s="31"/>
+      <c r="E8" s="29"/>
       <c r="F8" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2210,14 +2209,14 @@
       <c r="B9" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="29">
+      <c r="C9" s="52">
         <v>5</v>
       </c>
       <c r="D9" s="23">
         <f>Detalle!O27*C9/5</f>
         <v>0</v>
       </c>
-      <c r="E9" s="31"/>
+      <c r="E9" s="29"/>
       <c r="F9" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2227,14 +2226,14 @@
       <c r="B10" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="29">
+      <c r="C10" s="52">
         <v>5</v>
       </c>
       <c r="D10" s="23">
         <f>Detalle!R27*C10/5</f>
         <v>0</v>
       </c>
-      <c r="E10" s="31"/>
+      <c r="E10" s="29"/>
       <c r="F10" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2244,14 +2243,14 @@
       <c r="B11" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="29">
+      <c r="C11" s="52">
         <v>5</v>
       </c>
       <c r="D11" s="23">
         <f>Detalle!U27*C11/5</f>
         <v>0</v>
       </c>
-      <c r="E11" s="31"/>
+      <c r="E11" s="29"/>
       <c r="F11" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2261,14 +2260,14 @@
       <c r="B12" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="29">
+      <c r="C12" s="52">
         <v>5</v>
       </c>
       <c r="D12" s="23">
         <f>Detalle!X27*C12/5</f>
         <v>0</v>
       </c>
-      <c r="E12" s="31"/>
+      <c r="E12" s="29"/>
       <c r="F12" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2278,14 +2277,14 @@
       <c r="B13" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="29">
+      <c r="C13" s="52">
         <v>5</v>
       </c>
       <c r="D13" s="23">
         <f>Detalle!AA27*C13/5</f>
         <v>0</v>
       </c>
-      <c r="E13" s="31"/>
+      <c r="E13" s="29"/>
       <c r="F13" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2295,14 +2294,14 @@
       <c r="B14" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="29">
+      <c r="C14" s="52">
         <v>5</v>
       </c>
       <c r="D14" s="23">
         <f>Detalle!AD27*C14/5</f>
         <v>0</v>
       </c>
-      <c r="E14" s="31"/>
+      <c r="E14" s="29"/>
       <c r="F14" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2312,14 +2311,14 @@
       <c r="B15" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C15" s="52">
         <v>5</v>
       </c>
       <c r="D15" s="23">
         <f>Detalle!AG27*C15/5</f>
         <v>0</v>
       </c>
-      <c r="E15" s="31"/>
+      <c r="E15" s="29"/>
       <c r="F15" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2329,14 +2328,14 @@
       <c r="B16" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="29">
+      <c r="C16" s="52">
         <v>5</v>
       </c>
       <c r="D16" s="23">
         <f>Detalle!AJ27*C16/5</f>
         <v>0</v>
       </c>
-      <c r="E16" s="31"/>
+      <c r="E16" s="29"/>
       <c r="F16" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2346,14 +2345,14 @@
       <c r="B17" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="29">
+      <c r="C17" s="52">
         <v>5</v>
       </c>
       <c r="D17" s="23">
         <f>Detalle!AM27*C17/5</f>
         <v>0</v>
       </c>
-      <c r="E17" s="31"/>
+      <c r="E17" s="29"/>
       <c r="F17" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2370,28 +2369,28 @@
         <f>Detalle!AP27*C18/5</f>
         <v>0</v>
       </c>
-      <c r="E18" s="32"/>
+      <c r="E18" s="30"/>
       <c r="F18" s="26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="2:6" ht="15.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B19" s="53" t="str">
+      <c r="B19" s="44" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.HCMC/blob/main/activity/",F1,"/Readme.md"),_xlfn.CONCAT("Ir a actividad ",F1," en GitHub."))</f>
         <v>Ir a actividad M01A07 en GitHub.</v>
       </c>
-      <c r="C19" s="53"/>
-      <c r="D19" s="53"/>
-      <c r="E19" s="53"/>
-      <c r="F19" s="53"/>
+      <c r="C19" s="44"/>
+      <c r="D19" s="44"/>
+      <c r="E19" s="44"/>
+      <c r="F19" s="44"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B20" s="53"/>
-      <c r="C20" s="53"/>
-      <c r="D20" s="53"/>
-      <c r="E20" s="53"/>
-      <c r="F20" s="53"/>
+      <c r="B20" s="44"/>
+      <c r="C20" s="44"/>
+      <c r="D20" s="44"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="44"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B21" s="27"/>
@@ -2487,98 +2486,98 @@
       <c r="AP1" s="15"/>
       <c r="AQ1" s="15"/>
     </row>
-    <row r="2" spans="1:44" s="43" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="42"/>
-      <c r="B2" s="46" t="s">
+    <row r="2" spans="1:44" s="41" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="40"/>
+      <c r="B2" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="48" t="str">
+      <c r="C2" s="47" t="str">
         <f>Calificacion!B5</f>
         <v>Grupo 1</v>
       </c>
-      <c r="D2" s="49"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="48" t="str">
+      <c r="D2" s="48"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="47" t="str">
         <f>Calificacion!B6</f>
         <v>Grupo 2</v>
       </c>
-      <c r="G2" s="49"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="48" t="str">
+      <c r="G2" s="48"/>
+      <c r="H2" s="49"/>
+      <c r="I2" s="47" t="str">
         <f>Calificacion!B7</f>
         <v>Grupo 3</v>
       </c>
-      <c r="J2" s="49"/>
-      <c r="K2" s="50"/>
-      <c r="L2" s="48" t="str">
+      <c r="J2" s="48"/>
+      <c r="K2" s="49"/>
+      <c r="L2" s="47" t="str">
         <f>Calificacion!B8</f>
         <v>Grupo 4</v>
       </c>
-      <c r="M2" s="49"/>
-      <c r="N2" s="50"/>
-      <c r="O2" s="48" t="str">
+      <c r="M2" s="48"/>
+      <c r="N2" s="49"/>
+      <c r="O2" s="47" t="str">
         <f>Calificacion!B9</f>
         <v>Grupo 5</v>
       </c>
-      <c r="P2" s="49"/>
-      <c r="Q2" s="50"/>
-      <c r="R2" s="48" t="str">
+      <c r="P2" s="48"/>
+      <c r="Q2" s="49"/>
+      <c r="R2" s="47" t="str">
         <f>Calificacion!B10</f>
         <v>Grupo 6</v>
       </c>
-      <c r="S2" s="49"/>
-      <c r="T2" s="50"/>
-      <c r="U2" s="48" t="str">
+      <c r="S2" s="48"/>
+      <c r="T2" s="49"/>
+      <c r="U2" s="47" t="str">
         <f>Calificacion!B11</f>
         <v>Grupo 7</v>
       </c>
-      <c r="V2" s="49"/>
-      <c r="W2" s="50"/>
-      <c r="X2" s="48" t="str">
+      <c r="V2" s="48"/>
+      <c r="W2" s="49"/>
+      <c r="X2" s="47" t="str">
         <f>Calificacion!B12</f>
         <v>Grupo 8</v>
       </c>
-      <c r="Y2" s="49"/>
-      <c r="Z2" s="50"/>
-      <c r="AA2" s="48" t="str">
+      <c r="Y2" s="48"/>
+      <c r="Z2" s="49"/>
+      <c r="AA2" s="47" t="str">
         <f>Calificacion!B13</f>
         <v>Grupo 9</v>
       </c>
-      <c r="AB2" s="49"/>
-      <c r="AC2" s="50"/>
-      <c r="AD2" s="48" t="str">
+      <c r="AB2" s="48"/>
+      <c r="AC2" s="49"/>
+      <c r="AD2" s="47" t="str">
         <f>Calificacion!B14</f>
         <v>Grupo 10</v>
       </c>
-      <c r="AE2" s="49"/>
-      <c r="AF2" s="50"/>
-      <c r="AG2" s="48" t="str">
+      <c r="AE2" s="48"/>
+      <c r="AF2" s="49"/>
+      <c r="AG2" s="47" t="str">
         <f>Calificacion!B15</f>
         <v>Grupo 11</v>
       </c>
-      <c r="AH2" s="49"/>
-      <c r="AI2" s="50"/>
-      <c r="AJ2" s="48" t="str">
+      <c r="AH2" s="48"/>
+      <c r="AI2" s="49"/>
+      <c r="AJ2" s="47" t="str">
         <f>Calificacion!B16</f>
         <v>Grupo 12</v>
       </c>
-      <c r="AK2" s="49"/>
-      <c r="AL2" s="50"/>
-      <c r="AM2" s="48" t="str">
+      <c r="AK2" s="48"/>
+      <c r="AL2" s="49"/>
+      <c r="AM2" s="47" t="str">
         <f>Calificacion!B17</f>
         <v>Grupo 13</v>
       </c>
-      <c r="AN2" s="49"/>
-      <c r="AO2" s="50"/>
-      <c r="AP2" s="48" t="str">
+      <c r="AN2" s="48"/>
+      <c r="AO2" s="49"/>
+      <c r="AP2" s="47" t="str">
         <f>Calificacion!B18</f>
         <v>Grupo 14</v>
       </c>
-      <c r="AQ2" s="49"/>
-      <c r="AR2" s="50"/>
+      <c r="AQ2" s="48"/>
+      <c r="AR2" s="49"/>
     </row>
     <row r="3" spans="1:44" x14ac:dyDescent="0.45">
-      <c r="B3" s="47"/>
+      <c r="B3" s="46"/>
       <c r="C3" s="12" t="s">
         <v>1</v>
       </c>
@@ -2710,1324 +2709,1324 @@
       <c r="B4" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="35"/>
+      <c r="C4" s="33"/>
       <c r="D4" s="18"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="35"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="33"/>
       <c r="G4" s="18"/>
-      <c r="H4" s="36"/>
-      <c r="I4" s="35"/>
+      <c r="H4" s="34"/>
+      <c r="I4" s="33"/>
       <c r="J4" s="18"/>
-      <c r="K4" s="36"/>
-      <c r="L4" s="35"/>
+      <c r="K4" s="34"/>
+      <c r="L4" s="33"/>
       <c r="M4" s="18"/>
-      <c r="N4" s="36"/>
-      <c r="O4" s="35"/>
+      <c r="N4" s="34"/>
+      <c r="O4" s="33"/>
       <c r="P4" s="18"/>
-      <c r="Q4" s="36"/>
-      <c r="R4" s="35"/>
+      <c r="Q4" s="34"/>
+      <c r="R4" s="33"/>
       <c r="S4" s="18"/>
-      <c r="T4" s="36"/>
-      <c r="U4" s="35"/>
+      <c r="T4" s="34"/>
+      <c r="U4" s="33"/>
       <c r="V4" s="18"/>
-      <c r="W4" s="36"/>
-      <c r="X4" s="35"/>
+      <c r="W4" s="34"/>
+      <c r="X4" s="33"/>
       <c r="Y4" s="18"/>
-      <c r="Z4" s="36"/>
-      <c r="AA4" s="35"/>
+      <c r="Z4" s="34"/>
+      <c r="AA4" s="33"/>
       <c r="AB4" s="18"/>
-      <c r="AC4" s="36"/>
-      <c r="AD4" s="35"/>
+      <c r="AC4" s="34"/>
+      <c r="AD4" s="33"/>
       <c r="AE4" s="18"/>
-      <c r="AF4" s="36"/>
-      <c r="AG4" s="35"/>
+      <c r="AF4" s="34"/>
+      <c r="AG4" s="33"/>
       <c r="AH4" s="18"/>
-      <c r="AI4" s="36"/>
-      <c r="AJ4" s="35"/>
+      <c r="AI4" s="34"/>
+      <c r="AJ4" s="33"/>
       <c r="AK4" s="18"/>
-      <c r="AL4" s="36"/>
-      <c r="AM4" s="35"/>
+      <c r="AL4" s="34"/>
+      <c r="AM4" s="33"/>
       <c r="AN4" s="18"/>
-      <c r="AO4" s="36"/>
-      <c r="AP4" s="35"/>
+      <c r="AO4" s="34"/>
+      <c r="AP4" s="33"/>
       <c r="AQ4" s="18"/>
-      <c r="AR4" s="36"/>
+      <c r="AR4" s="34"/>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B5" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="35">
+      <c r="C5" s="33">
         <v>0</v>
       </c>
       <c r="D5" s="18"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="35">
+      <c r="E5" s="34"/>
+      <c r="F5" s="33">
         <v>0</v>
       </c>
       <c r="G5" s="18"/>
-      <c r="H5" s="36"/>
-      <c r="I5" s="35">
+      <c r="H5" s="34"/>
+      <c r="I5" s="33">
         <v>0</v>
       </c>
       <c r="J5" s="18"/>
-      <c r="K5" s="36"/>
-      <c r="L5" s="35">
+      <c r="K5" s="34"/>
+      <c r="L5" s="33">
         <v>0</v>
       </c>
       <c r="M5" s="18"/>
-      <c r="N5" s="36"/>
-      <c r="O5" s="35">
+      <c r="N5" s="34"/>
+      <c r="O5" s="33">
         <v>0</v>
       </c>
       <c r="P5" s="18"/>
-      <c r="Q5" s="36"/>
-      <c r="R5" s="35">
+      <c r="Q5" s="34"/>
+      <c r="R5" s="33">
         <v>0</v>
       </c>
       <c r="S5" s="18"/>
-      <c r="T5" s="36"/>
-      <c r="U5" s="35">
+      <c r="T5" s="34"/>
+      <c r="U5" s="33">
         <v>0</v>
       </c>
       <c r="V5" s="18"/>
-      <c r="W5" s="36"/>
-      <c r="X5" s="35">
+      <c r="W5" s="34"/>
+      <c r="X5" s="33">
         <v>0</v>
       </c>
       <c r="Y5" s="18"/>
-      <c r="Z5" s="36"/>
-      <c r="AA5" s="35">
+      <c r="Z5" s="34"/>
+      <c r="AA5" s="33">
         <v>0</v>
       </c>
       <c r="AB5" s="18"/>
-      <c r="AC5" s="36"/>
-      <c r="AD5" s="35">
+      <c r="AC5" s="34"/>
+      <c r="AD5" s="33">
         <v>0</v>
       </c>
       <c r="AE5" s="18"/>
-      <c r="AF5" s="36"/>
-      <c r="AG5" s="35">
+      <c r="AF5" s="34"/>
+      <c r="AG5" s="33">
         <v>0</v>
       </c>
       <c r="AH5" s="18"/>
-      <c r="AI5" s="36"/>
-      <c r="AJ5" s="35">
+      <c r="AI5" s="34"/>
+      <c r="AJ5" s="33">
         <v>0</v>
       </c>
       <c r="AK5" s="18"/>
-      <c r="AL5" s="36"/>
-      <c r="AM5" s="35">
+      <c r="AL5" s="34"/>
+      <c r="AM5" s="33">
         <v>0</v>
       </c>
       <c r="AN5" s="18"/>
-      <c r="AO5" s="36"/>
-      <c r="AP5" s="35">
+      <c r="AO5" s="34"/>
+      <c r="AP5" s="33">
         <v>0</v>
       </c>
       <c r="AQ5" s="18"/>
-      <c r="AR5" s="36"/>
+      <c r="AR5" s="34"/>
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B6" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="35"/>
+      <c r="C6" s="33"/>
       <c r="D6" s="18"/>
-      <c r="E6" s="36"/>
-      <c r="F6" s="35"/>
+      <c r="E6" s="34"/>
+      <c r="F6" s="33"/>
       <c r="G6" s="18"/>
-      <c r="H6" s="36"/>
-      <c r="I6" s="35"/>
+      <c r="H6" s="34"/>
+      <c r="I6" s="33"/>
       <c r="J6" s="18"/>
-      <c r="K6" s="36"/>
-      <c r="L6" s="35"/>
+      <c r="K6" s="34"/>
+      <c r="L6" s="33"/>
       <c r="M6" s="18"/>
-      <c r="N6" s="36"/>
-      <c r="O6" s="35"/>
+      <c r="N6" s="34"/>
+      <c r="O6" s="33"/>
       <c r="P6" s="18"/>
-      <c r="Q6" s="36"/>
-      <c r="R6" s="35"/>
+      <c r="Q6" s="34"/>
+      <c r="R6" s="33"/>
       <c r="S6" s="18"/>
-      <c r="T6" s="36"/>
-      <c r="U6" s="35"/>
+      <c r="T6" s="34"/>
+      <c r="U6" s="33"/>
       <c r="V6" s="18"/>
-      <c r="W6" s="36"/>
-      <c r="X6" s="35"/>
+      <c r="W6" s="34"/>
+      <c r="X6" s="33"/>
       <c r="Y6" s="18"/>
-      <c r="Z6" s="36"/>
-      <c r="AA6" s="35"/>
+      <c r="Z6" s="34"/>
+      <c r="AA6" s="33"/>
       <c r="AB6" s="18"/>
-      <c r="AC6" s="36"/>
-      <c r="AD6" s="35"/>
+      <c r="AC6" s="34"/>
+      <c r="AD6" s="33"/>
       <c r="AE6" s="18"/>
-      <c r="AF6" s="36"/>
-      <c r="AG6" s="35"/>
+      <c r="AF6" s="34"/>
+      <c r="AG6" s="33"/>
       <c r="AH6" s="18"/>
-      <c r="AI6" s="36"/>
-      <c r="AJ6" s="35"/>
+      <c r="AI6" s="34"/>
+      <c r="AJ6" s="33"/>
       <c r="AK6" s="18"/>
-      <c r="AL6" s="36"/>
-      <c r="AM6" s="35"/>
+      <c r="AL6" s="34"/>
+      <c r="AM6" s="33"/>
       <c r="AN6" s="18"/>
-      <c r="AO6" s="36"/>
-      <c r="AP6" s="35"/>
+      <c r="AO6" s="34"/>
+      <c r="AP6" s="33"/>
       <c r="AQ6" s="18"/>
-      <c r="AR6" s="36"/>
+      <c r="AR6" s="34"/>
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B7" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="35"/>
+      <c r="C7" s="33"/>
       <c r="D7" s="18"/>
-      <c r="E7" s="36"/>
-      <c r="F7" s="35"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="33"/>
       <c r="G7" s="18"/>
-      <c r="H7" s="36"/>
-      <c r="I7" s="35"/>
+      <c r="H7" s="34"/>
+      <c r="I7" s="33"/>
       <c r="J7" s="18"/>
-      <c r="K7" s="36"/>
-      <c r="L7" s="35"/>
+      <c r="K7" s="34"/>
+      <c r="L7" s="33"/>
       <c r="M7" s="18"/>
-      <c r="N7" s="36"/>
-      <c r="O7" s="35"/>
+      <c r="N7" s="34"/>
+      <c r="O7" s="33"/>
       <c r="P7" s="18"/>
-      <c r="Q7" s="36"/>
-      <c r="R7" s="35"/>
+      <c r="Q7" s="34"/>
+      <c r="R7" s="33"/>
       <c r="S7" s="18"/>
-      <c r="T7" s="36"/>
-      <c r="U7" s="35"/>
+      <c r="T7" s="34"/>
+      <c r="U7" s="33"/>
       <c r="V7" s="18"/>
-      <c r="W7" s="36"/>
-      <c r="X7" s="35"/>
+      <c r="W7" s="34"/>
+      <c r="X7" s="33"/>
       <c r="Y7" s="18"/>
-      <c r="Z7" s="36"/>
-      <c r="AA7" s="35"/>
+      <c r="Z7" s="34"/>
+      <c r="AA7" s="33"/>
       <c r="AB7" s="18"/>
-      <c r="AC7" s="36"/>
-      <c r="AD7" s="35"/>
+      <c r="AC7" s="34"/>
+      <c r="AD7" s="33"/>
       <c r="AE7" s="18"/>
-      <c r="AF7" s="36"/>
-      <c r="AG7" s="35"/>
+      <c r="AF7" s="34"/>
+      <c r="AG7" s="33"/>
       <c r="AH7" s="18"/>
-      <c r="AI7" s="36"/>
-      <c r="AJ7" s="35"/>
+      <c r="AI7" s="34"/>
+      <c r="AJ7" s="33"/>
       <c r="AK7" s="18"/>
-      <c r="AL7" s="36"/>
-      <c r="AM7" s="35"/>
+      <c r="AL7" s="34"/>
+      <c r="AM7" s="33"/>
       <c r="AN7" s="18"/>
-      <c r="AO7" s="36"/>
-      <c r="AP7" s="35"/>
+      <c r="AO7" s="34"/>
+      <c r="AP7" s="33"/>
       <c r="AQ7" s="18"/>
-      <c r="AR7" s="36"/>
+      <c r="AR7" s="34"/>
     </row>
     <row r="8" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B8" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="35"/>
-      <c r="D8" s="41">
+      <c r="C8" s="33"/>
+      <c r="D8" s="39">
         <f>D5-D6</f>
         <v>0</v>
       </c>
-      <c r="E8" s="36"/>
-      <c r="F8" s="35"/>
-      <c r="G8" s="41">
+      <c r="E8" s="34"/>
+      <c r="F8" s="33"/>
+      <c r="G8" s="39">
         <f>G5-G6</f>
         <v>0</v>
       </c>
-      <c r="H8" s="36"/>
-      <c r="I8" s="35"/>
-      <c r="J8" s="41">
+      <c r="H8" s="34"/>
+      <c r="I8" s="33"/>
+      <c r="J8" s="39">
         <f>J5-J6</f>
         <v>0</v>
       </c>
-      <c r="K8" s="36"/>
-      <c r="L8" s="35"/>
-      <c r="M8" s="41">
+      <c r="K8" s="34"/>
+      <c r="L8" s="33"/>
+      <c r="M8" s="39">
         <f>M5-M6</f>
         <v>0</v>
       </c>
-      <c r="N8" s="36"/>
-      <c r="O8" s="35"/>
-      <c r="P8" s="41">
+      <c r="N8" s="34"/>
+      <c r="O8" s="33"/>
+      <c r="P8" s="39">
         <f>P5-P6</f>
         <v>0</v>
       </c>
-      <c r="Q8" s="36"/>
-      <c r="R8" s="35"/>
-      <c r="S8" s="41">
+      <c r="Q8" s="34"/>
+      <c r="R8" s="33"/>
+      <c r="S8" s="39">
         <f>S5-S6</f>
         <v>0</v>
       </c>
-      <c r="T8" s="36"/>
-      <c r="U8" s="35"/>
-      <c r="V8" s="41">
+      <c r="T8" s="34"/>
+      <c r="U8" s="33"/>
+      <c r="V8" s="39">
         <f>V5-V6</f>
         <v>0</v>
       </c>
-      <c r="W8" s="36"/>
-      <c r="X8" s="35"/>
-      <c r="Y8" s="41">
+      <c r="W8" s="34"/>
+      <c r="X8" s="33"/>
+      <c r="Y8" s="39">
         <f>Y5-Y6</f>
         <v>0</v>
       </c>
-      <c r="Z8" s="36"/>
-      <c r="AA8" s="35"/>
-      <c r="AB8" s="41">
+      <c r="Z8" s="34"/>
+      <c r="AA8" s="33"/>
+      <c r="AB8" s="39">
         <f>AB5-AB6</f>
         <v>0</v>
       </c>
-      <c r="AC8" s="36"/>
-      <c r="AD8" s="35"/>
-      <c r="AE8" s="41">
+      <c r="AC8" s="34"/>
+      <c r="AD8" s="33"/>
+      <c r="AE8" s="39">
         <f>AE5-AE6</f>
         <v>0</v>
       </c>
-      <c r="AF8" s="36"/>
-      <c r="AG8" s="35"/>
-      <c r="AH8" s="41">
+      <c r="AF8" s="34"/>
+      <c r="AG8" s="33"/>
+      <c r="AH8" s="39">
         <f>AH5-AH6</f>
         <v>0</v>
       </c>
-      <c r="AI8" s="36"/>
-      <c r="AJ8" s="35"/>
-      <c r="AK8" s="41">
+      <c r="AI8" s="34"/>
+      <c r="AJ8" s="33"/>
+      <c r="AK8" s="39">
         <f>AK5-AK6</f>
         <v>0</v>
       </c>
-      <c r="AL8" s="36"/>
-      <c r="AM8" s="35"/>
-      <c r="AN8" s="41">
+      <c r="AL8" s="34"/>
+      <c r="AM8" s="33"/>
+      <c r="AN8" s="39">
         <f>AN5-AN6</f>
         <v>0</v>
       </c>
-      <c r="AO8" s="36"/>
-      <c r="AP8" s="35"/>
-      <c r="AQ8" s="41">
+      <c r="AO8" s="34"/>
+      <c r="AP8" s="33"/>
+      <c r="AQ8" s="39">
         <f>AQ5-AQ6</f>
         <v>0</v>
       </c>
-      <c r="AR8" s="36"/>
+      <c r="AR8" s="34"/>
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B9" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="C9" s="35"/>
+      <c r="C9" s="33"/>
       <c r="D9" s="18"/>
-      <c r="E9" s="36"/>
-      <c r="F9" s="35"/>
+      <c r="E9" s="34"/>
+      <c r="F9" s="33"/>
       <c r="G9" s="18"/>
-      <c r="H9" s="36"/>
-      <c r="I9" s="35"/>
+      <c r="H9" s="34"/>
+      <c r="I9" s="33"/>
       <c r="J9" s="18"/>
-      <c r="K9" s="36"/>
-      <c r="L9" s="35"/>
+      <c r="K9" s="34"/>
+      <c r="L9" s="33"/>
       <c r="M9" s="18"/>
-      <c r="N9" s="36"/>
-      <c r="O9" s="35"/>
+      <c r="N9" s="34"/>
+      <c r="O9" s="33"/>
       <c r="P9" s="18"/>
-      <c r="Q9" s="36"/>
-      <c r="R9" s="35"/>
+      <c r="Q9" s="34"/>
+      <c r="R9" s="33"/>
       <c r="S9" s="18"/>
-      <c r="T9" s="36"/>
-      <c r="U9" s="35"/>
+      <c r="T9" s="34"/>
+      <c r="U9" s="33"/>
       <c r="V9" s="18"/>
-      <c r="W9" s="36"/>
-      <c r="X9" s="35"/>
+      <c r="W9" s="34"/>
+      <c r="X9" s="33"/>
       <c r="Y9" s="18"/>
-      <c r="Z9" s="36"/>
-      <c r="AA9" s="35"/>
+      <c r="Z9" s="34"/>
+      <c r="AA9" s="33"/>
       <c r="AB9" s="18"/>
-      <c r="AC9" s="36"/>
-      <c r="AD9" s="35"/>
+      <c r="AC9" s="34"/>
+      <c r="AD9" s="33"/>
       <c r="AE9" s="18"/>
-      <c r="AF9" s="36"/>
-      <c r="AG9" s="35"/>
+      <c r="AF9" s="34"/>
+      <c r="AG9" s="33"/>
       <c r="AH9" s="18"/>
-      <c r="AI9" s="36"/>
-      <c r="AJ9" s="35"/>
+      <c r="AI9" s="34"/>
+      <c r="AJ9" s="33"/>
       <c r="AK9" s="18"/>
-      <c r="AL9" s="36"/>
-      <c r="AM9" s="35"/>
+      <c r="AL9" s="34"/>
+      <c r="AM9" s="33"/>
       <c r="AN9" s="18"/>
-      <c r="AO9" s="36"/>
-      <c r="AP9" s="35"/>
+      <c r="AO9" s="34"/>
+      <c r="AP9" s="33"/>
       <c r="AQ9" s="18"/>
-      <c r="AR9" s="36"/>
+      <c r="AR9" s="34"/>
     </row>
     <row r="10" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B10" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="35"/>
+      <c r="C10" s="33"/>
       <c r="D10" s="18"/>
-      <c r="E10" s="36"/>
-      <c r="F10" s="35"/>
+      <c r="E10" s="34"/>
+      <c r="F10" s="33"/>
       <c r="G10" s="18"/>
-      <c r="H10" s="36"/>
-      <c r="I10" s="35"/>
+      <c r="H10" s="34"/>
+      <c r="I10" s="33"/>
       <c r="J10" s="18"/>
-      <c r="K10" s="36"/>
-      <c r="L10" s="35"/>
+      <c r="K10" s="34"/>
+      <c r="L10" s="33"/>
       <c r="M10" s="18"/>
-      <c r="N10" s="36"/>
-      <c r="O10" s="35"/>
+      <c r="N10" s="34"/>
+      <c r="O10" s="33"/>
       <c r="P10" s="18"/>
-      <c r="Q10" s="36"/>
-      <c r="R10" s="35"/>
+      <c r="Q10" s="34"/>
+      <c r="R10" s="33"/>
       <c r="S10" s="18"/>
-      <c r="T10" s="36"/>
-      <c r="U10" s="35"/>
+      <c r="T10" s="34"/>
+      <c r="U10" s="33"/>
       <c r="V10" s="18"/>
-      <c r="W10" s="36"/>
-      <c r="X10" s="35"/>
+      <c r="W10" s="34"/>
+      <c r="X10" s="33"/>
       <c r="Y10" s="18"/>
-      <c r="Z10" s="36"/>
-      <c r="AA10" s="35"/>
+      <c r="Z10" s="34"/>
+      <c r="AA10" s="33"/>
       <c r="AB10" s="18"/>
-      <c r="AC10" s="36"/>
-      <c r="AD10" s="35"/>
+      <c r="AC10" s="34"/>
+      <c r="AD10" s="33"/>
       <c r="AE10" s="18"/>
-      <c r="AF10" s="36"/>
-      <c r="AG10" s="35"/>
+      <c r="AF10" s="34"/>
+      <c r="AG10" s="33"/>
       <c r="AH10" s="18"/>
-      <c r="AI10" s="36"/>
-      <c r="AJ10" s="35"/>
+      <c r="AI10" s="34"/>
+      <c r="AJ10" s="33"/>
       <c r="AK10" s="18"/>
-      <c r="AL10" s="36"/>
-      <c r="AM10" s="35"/>
+      <c r="AL10" s="34"/>
+      <c r="AM10" s="33"/>
       <c r="AN10" s="18"/>
-      <c r="AO10" s="36"/>
-      <c r="AP10" s="35"/>
+      <c r="AO10" s="34"/>
+      <c r="AP10" s="33"/>
       <c r="AQ10" s="18"/>
-      <c r="AR10" s="36"/>
+      <c r="AR10" s="34"/>
     </row>
     <row r="11" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B11" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="35"/>
-      <c r="D11" s="40" t="e">
+      <c r="C11" s="33"/>
+      <c r="D11" s="38" t="e">
         <f>D9/D10</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E11" s="36"/>
-      <c r="F11" s="35"/>
-      <c r="G11" s="40" t="e">
+      <c r="E11" s="34"/>
+      <c r="F11" s="33"/>
+      <c r="G11" s="38" t="e">
         <f>G9/G10</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H11" s="36"/>
-      <c r="I11" s="35"/>
-      <c r="J11" s="40" t="e">
+      <c r="H11" s="34"/>
+      <c r="I11" s="33"/>
+      <c r="J11" s="38" t="e">
         <f>J9/J10</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K11" s="36"/>
-      <c r="L11" s="35"/>
-      <c r="M11" s="40" t="e">
+      <c r="K11" s="34"/>
+      <c r="L11" s="33"/>
+      <c r="M11" s="38" t="e">
         <f>M9/M10</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="N11" s="36"/>
-      <c r="O11" s="35"/>
-      <c r="P11" s="40" t="e">
+      <c r="N11" s="34"/>
+      <c r="O11" s="33"/>
+      <c r="P11" s="38" t="e">
         <f>P9/P10</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q11" s="36"/>
-      <c r="R11" s="35"/>
-      <c r="S11" s="40" t="e">
+      <c r="Q11" s="34"/>
+      <c r="R11" s="33"/>
+      <c r="S11" s="38" t="e">
         <f>S9/S10</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="T11" s="36"/>
-      <c r="U11" s="35"/>
-      <c r="V11" s="40" t="e">
+      <c r="T11" s="34"/>
+      <c r="U11" s="33"/>
+      <c r="V11" s="38" t="e">
         <f>V9/V10</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="W11" s="36"/>
-      <c r="X11" s="35"/>
-      <c r="Y11" s="40" t="e">
+      <c r="W11" s="34"/>
+      <c r="X11" s="33"/>
+      <c r="Y11" s="38" t="e">
         <f>Y9/Y10</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z11" s="36"/>
-      <c r="AA11" s="35"/>
-      <c r="AB11" s="40" t="e">
+      <c r="Z11" s="34"/>
+      <c r="AA11" s="33"/>
+      <c r="AB11" s="38" t="e">
         <f>AB9/AB10</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC11" s="36"/>
-      <c r="AD11" s="35"/>
-      <c r="AE11" s="40" t="e">
+      <c r="AC11" s="34"/>
+      <c r="AD11" s="33"/>
+      <c r="AE11" s="38" t="e">
         <f>AE9/AE10</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF11" s="36"/>
-      <c r="AG11" s="35"/>
-      <c r="AH11" s="40" t="e">
+      <c r="AF11" s="34"/>
+      <c r="AG11" s="33"/>
+      <c r="AH11" s="38" t="e">
         <f>AH9/AH10</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AI11" s="36"/>
-      <c r="AJ11" s="35"/>
-      <c r="AK11" s="40" t="e">
+      <c r="AI11" s="34"/>
+      <c r="AJ11" s="33"/>
+      <c r="AK11" s="38" t="e">
         <f>AK9/AK10</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AL11" s="36"/>
-      <c r="AM11" s="35"/>
-      <c r="AN11" s="40" t="e">
+      <c r="AL11" s="34"/>
+      <c r="AM11" s="33"/>
+      <c r="AN11" s="38" t="e">
         <f>AN9/AN10</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AO11" s="36"/>
-      <c r="AP11" s="35"/>
-      <c r="AQ11" s="40" t="e">
+      <c r="AO11" s="34"/>
+      <c r="AP11" s="33"/>
+      <c r="AQ11" s="38" t="e">
         <f>AQ9/AQ10</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AR11" s="36"/>
+      <c r="AR11" s="34"/>
     </row>
     <row r="12" spans="1:44" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B12" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="35"/>
+      <c r="C12" s="33"/>
       <c r="D12" s="18"/>
-      <c r="E12" s="36"/>
-      <c r="F12" s="35"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="33"/>
       <c r="G12" s="18"/>
-      <c r="H12" s="36"/>
-      <c r="I12" s="35"/>
+      <c r="H12" s="34"/>
+      <c r="I12" s="33"/>
       <c r="J12" s="18"/>
-      <c r="K12" s="36"/>
-      <c r="L12" s="35"/>
+      <c r="K12" s="34"/>
+      <c r="L12" s="33"/>
       <c r="M12" s="18"/>
-      <c r="N12" s="36"/>
-      <c r="O12" s="35"/>
+      <c r="N12" s="34"/>
+      <c r="O12" s="33"/>
       <c r="P12" s="18"/>
-      <c r="Q12" s="36"/>
-      <c r="R12" s="35"/>
+      <c r="Q12" s="34"/>
+      <c r="R12" s="33"/>
       <c r="S12" s="18"/>
-      <c r="T12" s="36"/>
-      <c r="U12" s="35"/>
+      <c r="T12" s="34"/>
+      <c r="U12" s="33"/>
       <c r="V12" s="18"/>
-      <c r="W12" s="36"/>
-      <c r="X12" s="35"/>
+      <c r="W12" s="34"/>
+      <c r="X12" s="33"/>
       <c r="Y12" s="18"/>
-      <c r="Z12" s="36"/>
-      <c r="AA12" s="35"/>
+      <c r="Z12" s="34"/>
+      <c r="AA12" s="33"/>
       <c r="AB12" s="18"/>
-      <c r="AC12" s="36"/>
-      <c r="AD12" s="35"/>
+      <c r="AC12" s="34"/>
+      <c r="AD12" s="33"/>
       <c r="AE12" s="18"/>
-      <c r="AF12" s="36"/>
-      <c r="AG12" s="35"/>
+      <c r="AF12" s="34"/>
+      <c r="AG12" s="33"/>
       <c r="AH12" s="18"/>
-      <c r="AI12" s="36"/>
-      <c r="AJ12" s="35"/>
+      <c r="AI12" s="34"/>
+      <c r="AJ12" s="33"/>
       <c r="AK12" s="18"/>
-      <c r="AL12" s="36"/>
-      <c r="AM12" s="35"/>
+      <c r="AL12" s="34"/>
+      <c r="AM12" s="33"/>
       <c r="AN12" s="18"/>
-      <c r="AO12" s="36"/>
-      <c r="AP12" s="35"/>
+      <c r="AO12" s="34"/>
+      <c r="AP12" s="33"/>
       <c r="AQ12" s="18"/>
-      <c r="AR12" s="36"/>
+      <c r="AR12" s="34"/>
     </row>
     <row r="13" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B13" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="35"/>
+      <c r="C13" s="33"/>
       <c r="D13" s="18"/>
-      <c r="E13" s="36"/>
-      <c r="F13" s="35"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="33"/>
       <c r="G13" s="18"/>
-      <c r="H13" s="36"/>
-      <c r="I13" s="35"/>
+      <c r="H13" s="34"/>
+      <c r="I13" s="33"/>
       <c r="J13" s="18"/>
-      <c r="K13" s="36"/>
-      <c r="L13" s="35"/>
+      <c r="K13" s="34"/>
+      <c r="L13" s="33"/>
       <c r="M13" s="18"/>
-      <c r="N13" s="36"/>
-      <c r="O13" s="35"/>
+      <c r="N13" s="34"/>
+      <c r="O13" s="33"/>
       <c r="P13" s="18"/>
-      <c r="Q13" s="36"/>
-      <c r="R13" s="35"/>
+      <c r="Q13" s="34"/>
+      <c r="R13" s="33"/>
       <c r="S13" s="18"/>
-      <c r="T13" s="36"/>
-      <c r="U13" s="35"/>
+      <c r="T13" s="34"/>
+      <c r="U13" s="33"/>
       <c r="V13" s="18"/>
-      <c r="W13" s="36"/>
-      <c r="X13" s="35"/>
+      <c r="W13" s="34"/>
+      <c r="X13" s="33"/>
       <c r="Y13" s="18"/>
-      <c r="Z13" s="36"/>
-      <c r="AA13" s="35"/>
+      <c r="Z13" s="34"/>
+      <c r="AA13" s="33"/>
       <c r="AB13" s="18"/>
-      <c r="AC13" s="36"/>
-      <c r="AD13" s="35"/>
+      <c r="AC13" s="34"/>
+      <c r="AD13" s="33"/>
       <c r="AE13" s="18"/>
-      <c r="AF13" s="36"/>
-      <c r="AG13" s="35"/>
+      <c r="AF13" s="34"/>
+      <c r="AG13" s="33"/>
       <c r="AH13" s="18"/>
-      <c r="AI13" s="36"/>
-      <c r="AJ13" s="35"/>
+      <c r="AI13" s="34"/>
+      <c r="AJ13" s="33"/>
       <c r="AK13" s="18"/>
-      <c r="AL13" s="36"/>
-      <c r="AM13" s="35"/>
+      <c r="AL13" s="34"/>
+      <c r="AM13" s="33"/>
       <c r="AN13" s="18"/>
-      <c r="AO13" s="36"/>
-      <c r="AP13" s="35"/>
+      <c r="AO13" s="34"/>
+      <c r="AP13" s="33"/>
       <c r="AQ13" s="18"/>
-      <c r="AR13" s="36"/>
+      <c r="AR13" s="34"/>
     </row>
     <row r="14" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B14" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="35"/>
+      <c r="C14" s="33"/>
       <c r="D14" s="18"/>
-      <c r="E14" s="36"/>
-      <c r="F14" s="35"/>
+      <c r="E14" s="34"/>
+      <c r="F14" s="33"/>
       <c r="G14" s="18"/>
-      <c r="H14" s="36"/>
-      <c r="I14" s="35"/>
+      <c r="H14" s="34"/>
+      <c r="I14" s="33"/>
       <c r="J14" s="18"/>
-      <c r="K14" s="36"/>
-      <c r="L14" s="35"/>
+      <c r="K14" s="34"/>
+      <c r="L14" s="33"/>
       <c r="M14" s="18"/>
-      <c r="N14" s="36"/>
-      <c r="O14" s="35"/>
+      <c r="N14" s="34"/>
+      <c r="O14" s="33"/>
       <c r="P14" s="18"/>
-      <c r="Q14" s="36"/>
-      <c r="R14" s="35"/>
+      <c r="Q14" s="34"/>
+      <c r="R14" s="33"/>
       <c r="S14" s="18"/>
-      <c r="T14" s="36"/>
-      <c r="U14" s="35"/>
+      <c r="T14" s="34"/>
+      <c r="U14" s="33"/>
       <c r="V14" s="18"/>
-      <c r="W14" s="36"/>
-      <c r="X14" s="35"/>
+      <c r="W14" s="34"/>
+      <c r="X14" s="33"/>
       <c r="Y14" s="18"/>
-      <c r="Z14" s="36"/>
-      <c r="AA14" s="35"/>
+      <c r="Z14" s="34"/>
+      <c r="AA14" s="33"/>
       <c r="AB14" s="18"/>
-      <c r="AC14" s="36"/>
-      <c r="AD14" s="35"/>
+      <c r="AC14" s="34"/>
+      <c r="AD14" s="33"/>
       <c r="AE14" s="18"/>
-      <c r="AF14" s="36"/>
-      <c r="AG14" s="35"/>
+      <c r="AF14" s="34"/>
+      <c r="AG14" s="33"/>
       <c r="AH14" s="18"/>
-      <c r="AI14" s="36"/>
-      <c r="AJ14" s="35"/>
+      <c r="AI14" s="34"/>
+      <c r="AJ14" s="33"/>
       <c r="AK14" s="18"/>
-      <c r="AL14" s="36"/>
-      <c r="AM14" s="35"/>
+      <c r="AL14" s="34"/>
+      <c r="AM14" s="33"/>
       <c r="AN14" s="18"/>
-      <c r="AO14" s="36"/>
-      <c r="AP14" s="35"/>
+      <c r="AO14" s="34"/>
+      <c r="AP14" s="33"/>
       <c r="AQ14" s="18"/>
-      <c r="AR14" s="36"/>
+      <c r="AR14" s="34"/>
     </row>
     <row r="15" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B15" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="35"/>
+      <c r="C15" s="33"/>
       <c r="D15" s="19"/>
-      <c r="E15" s="36"/>
-      <c r="F15" s="35"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="33"/>
       <c r="G15" s="19"/>
-      <c r="H15" s="36"/>
-      <c r="I15" s="35"/>
+      <c r="H15" s="34"/>
+      <c r="I15" s="33"/>
       <c r="J15" s="19"/>
-      <c r="K15" s="36"/>
-      <c r="L15" s="35"/>
+      <c r="K15" s="34"/>
+      <c r="L15" s="33"/>
       <c r="M15" s="19"/>
-      <c r="N15" s="36"/>
-      <c r="O15" s="35"/>
+      <c r="N15" s="34"/>
+      <c r="O15" s="33"/>
       <c r="P15" s="19"/>
-      <c r="Q15" s="36"/>
-      <c r="R15" s="35"/>
+      <c r="Q15" s="34"/>
+      <c r="R15" s="33"/>
       <c r="S15" s="19"/>
-      <c r="T15" s="36"/>
-      <c r="U15" s="35"/>
+      <c r="T15" s="34"/>
+      <c r="U15" s="33"/>
       <c r="V15" s="19"/>
-      <c r="W15" s="36"/>
-      <c r="X15" s="35"/>
+      <c r="W15" s="34"/>
+      <c r="X15" s="33"/>
       <c r="Y15" s="19"/>
-      <c r="Z15" s="36"/>
-      <c r="AA15" s="35"/>
+      <c r="Z15" s="34"/>
+      <c r="AA15" s="33"/>
       <c r="AB15" s="19"/>
-      <c r="AC15" s="36"/>
-      <c r="AD15" s="35"/>
+      <c r="AC15" s="34"/>
+      <c r="AD15" s="33"/>
       <c r="AE15" s="19"/>
-      <c r="AF15" s="36"/>
-      <c r="AG15" s="35"/>
+      <c r="AF15" s="34"/>
+      <c r="AG15" s="33"/>
       <c r="AH15" s="19"/>
-      <c r="AI15" s="36"/>
-      <c r="AJ15" s="35"/>
+      <c r="AI15" s="34"/>
+      <c r="AJ15" s="33"/>
       <c r="AK15" s="19"/>
-      <c r="AL15" s="36"/>
-      <c r="AM15" s="35"/>
+      <c r="AL15" s="34"/>
+      <c r="AM15" s="33"/>
       <c r="AN15" s="19"/>
-      <c r="AO15" s="36"/>
-      <c r="AP15" s="35"/>
+      <c r="AO15" s="34"/>
+      <c r="AP15" s="33"/>
       <c r="AQ15" s="19"/>
-      <c r="AR15" s="36"/>
+      <c r="AR15" s="34"/>
     </row>
     <row r="16" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B16" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="35"/>
+      <c r="C16" s="33"/>
       <c r="D16" s="18"/>
-      <c r="E16" s="36"/>
-      <c r="F16" s="35"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="33"/>
       <c r="G16" s="18"/>
-      <c r="H16" s="36"/>
-      <c r="I16" s="35"/>
+      <c r="H16" s="34"/>
+      <c r="I16" s="33"/>
       <c r="J16" s="18"/>
-      <c r="K16" s="36"/>
-      <c r="L16" s="35"/>
+      <c r="K16" s="34"/>
+      <c r="L16" s="33"/>
       <c r="M16" s="18"/>
-      <c r="N16" s="36"/>
-      <c r="O16" s="35"/>
+      <c r="N16" s="34"/>
+      <c r="O16" s="33"/>
       <c r="P16" s="18"/>
-      <c r="Q16" s="36"/>
-      <c r="R16" s="35"/>
+      <c r="Q16" s="34"/>
+      <c r="R16" s="33"/>
       <c r="S16" s="18"/>
-      <c r="T16" s="36"/>
-      <c r="U16" s="35"/>
+      <c r="T16" s="34"/>
+      <c r="U16" s="33"/>
       <c r="V16" s="18"/>
-      <c r="W16" s="36"/>
-      <c r="X16" s="35"/>
+      <c r="W16" s="34"/>
+      <c r="X16" s="33"/>
       <c r="Y16" s="18"/>
-      <c r="Z16" s="36"/>
-      <c r="AA16" s="35"/>
+      <c r="Z16" s="34"/>
+      <c r="AA16" s="33"/>
       <c r="AB16" s="18"/>
-      <c r="AC16" s="36"/>
-      <c r="AD16" s="35"/>
+      <c r="AC16" s="34"/>
+      <c r="AD16" s="33"/>
       <c r="AE16" s="18"/>
-      <c r="AF16" s="36"/>
-      <c r="AG16" s="35"/>
+      <c r="AF16" s="34"/>
+      <c r="AG16" s="33"/>
       <c r="AH16" s="18"/>
-      <c r="AI16" s="36"/>
-      <c r="AJ16" s="35"/>
+      <c r="AI16" s="34"/>
+      <c r="AJ16" s="33"/>
       <c r="AK16" s="18"/>
-      <c r="AL16" s="36"/>
-      <c r="AM16" s="35"/>
+      <c r="AL16" s="34"/>
+      <c r="AM16" s="33"/>
       <c r="AN16" s="18"/>
-      <c r="AO16" s="36"/>
-      <c r="AP16" s="35"/>
+      <c r="AO16" s="34"/>
+      <c r="AP16" s="33"/>
       <c r="AQ16" s="18"/>
-      <c r="AR16" s="36"/>
+      <c r="AR16" s="34"/>
     </row>
     <row r="17" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B17" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C17" s="35"/>
+      <c r="C17" s="33"/>
       <c r="D17" s="18"/>
-      <c r="E17" s="36"/>
-      <c r="F17" s="35"/>
+      <c r="E17" s="34"/>
+      <c r="F17" s="33"/>
       <c r="G17" s="18"/>
-      <c r="H17" s="36"/>
-      <c r="I17" s="35"/>
+      <c r="H17" s="34"/>
+      <c r="I17" s="33"/>
       <c r="J17" s="18"/>
-      <c r="K17" s="36"/>
-      <c r="L17" s="35"/>
+      <c r="K17" s="34"/>
+      <c r="L17" s="33"/>
       <c r="M17" s="18"/>
-      <c r="N17" s="36"/>
-      <c r="O17" s="35"/>
+      <c r="N17" s="34"/>
+      <c r="O17" s="33"/>
       <c r="P17" s="18"/>
-      <c r="Q17" s="36"/>
-      <c r="R17" s="35"/>
+      <c r="Q17" s="34"/>
+      <c r="R17" s="33"/>
       <c r="S17" s="18"/>
-      <c r="T17" s="36"/>
-      <c r="U17" s="35"/>
+      <c r="T17" s="34"/>
+      <c r="U17" s="33"/>
       <c r="V17" s="18"/>
-      <c r="W17" s="36"/>
-      <c r="X17" s="35"/>
+      <c r="W17" s="34"/>
+      <c r="X17" s="33"/>
       <c r="Y17" s="18"/>
-      <c r="Z17" s="36"/>
-      <c r="AA17" s="35"/>
+      <c r="Z17" s="34"/>
+      <c r="AA17" s="33"/>
       <c r="AB17" s="18"/>
-      <c r="AC17" s="36"/>
-      <c r="AD17" s="35"/>
+      <c r="AC17" s="34"/>
+      <c r="AD17" s="33"/>
       <c r="AE17" s="18"/>
-      <c r="AF17" s="36"/>
-      <c r="AG17" s="35"/>
+      <c r="AF17" s="34"/>
+      <c r="AG17" s="33"/>
       <c r="AH17" s="18"/>
-      <c r="AI17" s="36"/>
-      <c r="AJ17" s="35"/>
+      <c r="AI17" s="34"/>
+      <c r="AJ17" s="33"/>
       <c r="AK17" s="18"/>
-      <c r="AL17" s="36"/>
-      <c r="AM17" s="35"/>
+      <c r="AL17" s="34"/>
+      <c r="AM17" s="33"/>
       <c r="AN17" s="18"/>
-      <c r="AO17" s="36"/>
-      <c r="AP17" s="35"/>
+      <c r="AO17" s="34"/>
+      <c r="AP17" s="33"/>
       <c r="AQ17" s="18"/>
-      <c r="AR17" s="36"/>
+      <c r="AR17" s="34"/>
     </row>
     <row r="18" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B18" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C18" s="35"/>
+      <c r="C18" s="33"/>
       <c r="D18" s="18"/>
-      <c r="E18" s="36"/>
-      <c r="F18" s="35"/>
+      <c r="E18" s="34"/>
+      <c r="F18" s="33"/>
       <c r="G18" s="18"/>
-      <c r="H18" s="36"/>
-      <c r="I18" s="35"/>
+      <c r="H18" s="34"/>
+      <c r="I18" s="33"/>
       <c r="J18" s="18"/>
-      <c r="K18" s="36"/>
-      <c r="L18" s="35"/>
+      <c r="K18" s="34"/>
+      <c r="L18" s="33"/>
       <c r="M18" s="18"/>
-      <c r="N18" s="36"/>
-      <c r="O18" s="35"/>
+      <c r="N18" s="34"/>
+      <c r="O18" s="33"/>
       <c r="P18" s="18"/>
-      <c r="Q18" s="36"/>
-      <c r="R18" s="35"/>
+      <c r="Q18" s="34"/>
+      <c r="R18" s="33"/>
       <c r="S18" s="18"/>
-      <c r="T18" s="36"/>
-      <c r="U18" s="35"/>
+      <c r="T18" s="34"/>
+      <c r="U18" s="33"/>
       <c r="V18" s="18"/>
-      <c r="W18" s="36"/>
-      <c r="X18" s="35"/>
+      <c r="W18" s="34"/>
+      <c r="X18" s="33"/>
       <c r="Y18" s="18"/>
-      <c r="Z18" s="36"/>
-      <c r="AA18" s="35"/>
+      <c r="Z18" s="34"/>
+      <c r="AA18" s="33"/>
       <c r="AB18" s="18"/>
-      <c r="AC18" s="36"/>
-      <c r="AD18" s="35"/>
+      <c r="AC18" s="34"/>
+      <c r="AD18" s="33"/>
       <c r="AE18" s="18"/>
-      <c r="AF18" s="36"/>
-      <c r="AG18" s="35"/>
+      <c r="AF18" s="34"/>
+      <c r="AG18" s="33"/>
       <c r="AH18" s="18"/>
-      <c r="AI18" s="36"/>
-      <c r="AJ18" s="35"/>
+      <c r="AI18" s="34"/>
+      <c r="AJ18" s="33"/>
       <c r="AK18" s="18"/>
-      <c r="AL18" s="36"/>
-      <c r="AM18" s="35"/>
+      <c r="AL18" s="34"/>
+      <c r="AM18" s="33"/>
       <c r="AN18" s="18"/>
-      <c r="AO18" s="36"/>
-      <c r="AP18" s="35"/>
+      <c r="AO18" s="34"/>
+      <c r="AP18" s="33"/>
       <c r="AQ18" s="18"/>
-      <c r="AR18" s="36"/>
+      <c r="AR18" s="34"/>
     </row>
     <row r="19" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B19" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="35"/>
+      <c r="C19" s="33"/>
       <c r="D19" s="18"/>
-      <c r="E19" s="36"/>
-      <c r="F19" s="35"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="33"/>
       <c r="G19" s="18"/>
-      <c r="H19" s="36"/>
-      <c r="I19" s="35"/>
+      <c r="H19" s="34"/>
+      <c r="I19" s="33"/>
       <c r="J19" s="18"/>
-      <c r="K19" s="36"/>
-      <c r="L19" s="35"/>
+      <c r="K19" s="34"/>
+      <c r="L19" s="33"/>
       <c r="M19" s="18"/>
-      <c r="N19" s="36"/>
-      <c r="O19" s="35"/>
+      <c r="N19" s="34"/>
+      <c r="O19" s="33"/>
       <c r="P19" s="18"/>
-      <c r="Q19" s="36"/>
-      <c r="R19" s="35"/>
+      <c r="Q19" s="34"/>
+      <c r="R19" s="33"/>
       <c r="S19" s="18"/>
-      <c r="T19" s="36"/>
-      <c r="U19" s="35"/>
+      <c r="T19" s="34"/>
+      <c r="U19" s="33"/>
       <c r="V19" s="18"/>
-      <c r="W19" s="36"/>
-      <c r="X19" s="35"/>
+      <c r="W19" s="34"/>
+      <c r="X19" s="33"/>
       <c r="Y19" s="18"/>
-      <c r="Z19" s="36"/>
-      <c r="AA19" s="35"/>
+      <c r="Z19" s="34"/>
+      <c r="AA19" s="33"/>
       <c r="AB19" s="18"/>
-      <c r="AC19" s="36"/>
-      <c r="AD19" s="35"/>
+      <c r="AC19" s="34"/>
+      <c r="AD19" s="33"/>
       <c r="AE19" s="18"/>
-      <c r="AF19" s="36"/>
-      <c r="AG19" s="35"/>
+      <c r="AF19" s="34"/>
+      <c r="AG19" s="33"/>
       <c r="AH19" s="18"/>
-      <c r="AI19" s="36"/>
-      <c r="AJ19" s="35"/>
+      <c r="AI19" s="34"/>
+      <c r="AJ19" s="33"/>
       <c r="AK19" s="18"/>
-      <c r="AL19" s="36"/>
-      <c r="AM19" s="35"/>
+      <c r="AL19" s="34"/>
+      <c r="AM19" s="33"/>
       <c r="AN19" s="18"/>
-      <c r="AO19" s="36"/>
-      <c r="AP19" s="35"/>
+      <c r="AO19" s="34"/>
+      <c r="AP19" s="33"/>
       <c r="AQ19" s="18"/>
-      <c r="AR19" s="36"/>
+      <c r="AR19" s="34"/>
     </row>
     <row r="20" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B20" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="C20" s="35"/>
-      <c r="D20" s="40" t="e">
+      <c r="C20" s="33"/>
+      <c r="D20" s="38" t="e">
         <f>D17/D19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E20" s="36"/>
-      <c r="F20" s="35"/>
-      <c r="G20" s="40" t="e">
+      <c r="E20" s="34"/>
+      <c r="F20" s="33"/>
+      <c r="G20" s="38" t="e">
         <f>G17/G19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H20" s="36"/>
-      <c r="I20" s="35"/>
-      <c r="J20" s="40" t="e">
+      <c r="H20" s="34"/>
+      <c r="I20" s="33"/>
+      <c r="J20" s="38" t="e">
         <f>J17/J19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K20" s="36"/>
-      <c r="L20" s="35"/>
-      <c r="M20" s="40" t="e">
+      <c r="K20" s="34"/>
+      <c r="L20" s="33"/>
+      <c r="M20" s="38" t="e">
         <f>M17/M19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="N20" s="36"/>
-      <c r="O20" s="35"/>
-      <c r="P20" s="40" t="e">
+      <c r="N20" s="34"/>
+      <c r="O20" s="33"/>
+      <c r="P20" s="38" t="e">
         <f>P17/P19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q20" s="36"/>
-      <c r="R20" s="35"/>
-      <c r="S20" s="40" t="e">
+      <c r="Q20" s="34"/>
+      <c r="R20" s="33"/>
+      <c r="S20" s="38" t="e">
         <f>S17/S19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="T20" s="36"/>
-      <c r="U20" s="35"/>
-      <c r="V20" s="40" t="e">
+      <c r="T20" s="34"/>
+      <c r="U20" s="33"/>
+      <c r="V20" s="38" t="e">
         <f>V17/V19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="W20" s="36"/>
-      <c r="X20" s="35"/>
-      <c r="Y20" s="40" t="e">
+      <c r="W20" s="34"/>
+      <c r="X20" s="33"/>
+      <c r="Y20" s="38" t="e">
         <f>Y17/Y19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z20" s="36"/>
-      <c r="AA20" s="35"/>
-      <c r="AB20" s="40" t="e">
+      <c r="Z20" s="34"/>
+      <c r="AA20" s="33"/>
+      <c r="AB20" s="38" t="e">
         <f>AB17/AB19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC20" s="36"/>
-      <c r="AD20" s="35"/>
-      <c r="AE20" s="40" t="e">
+      <c r="AC20" s="34"/>
+      <c r="AD20" s="33"/>
+      <c r="AE20" s="38" t="e">
         <f>AE17/AE19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF20" s="36"/>
-      <c r="AG20" s="35"/>
-      <c r="AH20" s="40" t="e">
+      <c r="AF20" s="34"/>
+      <c r="AG20" s="33"/>
+      <c r="AH20" s="38" t="e">
         <f>AH17/AH19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AI20" s="36"/>
-      <c r="AJ20" s="35"/>
-      <c r="AK20" s="40" t="e">
+      <c r="AI20" s="34"/>
+      <c r="AJ20" s="33"/>
+      <c r="AK20" s="38" t="e">
         <f>AK17/AK19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AL20" s="36"/>
-      <c r="AM20" s="35"/>
-      <c r="AN20" s="40" t="e">
+      <c r="AL20" s="34"/>
+      <c r="AM20" s="33"/>
+      <c r="AN20" s="38" t="e">
         <f>AN17/AN19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AO20" s="36"/>
-      <c r="AP20" s="35"/>
-      <c r="AQ20" s="40" t="e">
+      <c r="AO20" s="34"/>
+      <c r="AP20" s="33"/>
+      <c r="AQ20" s="38" t="e">
         <f>AQ17/AQ19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AR20" s="36"/>
+      <c r="AR20" s="34"/>
     </row>
     <row r="21" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B21" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="C21" s="35"/>
+      <c r="C21" s="33"/>
       <c r="D21" s="18"/>
-      <c r="E21" s="36"/>
-      <c r="F21" s="35"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="33"/>
       <c r="G21" s="18"/>
-      <c r="H21" s="36"/>
-      <c r="I21" s="35"/>
+      <c r="H21" s="34"/>
+      <c r="I21" s="33"/>
       <c r="J21" s="18"/>
-      <c r="K21" s="36"/>
-      <c r="L21" s="35"/>
+      <c r="K21" s="34"/>
+      <c r="L21" s="33"/>
       <c r="M21" s="18"/>
-      <c r="N21" s="36"/>
-      <c r="O21" s="35"/>
+      <c r="N21" s="34"/>
+      <c r="O21" s="33"/>
       <c r="P21" s="18"/>
-      <c r="Q21" s="36"/>
-      <c r="R21" s="35"/>
+      <c r="Q21" s="34"/>
+      <c r="R21" s="33"/>
       <c r="S21" s="18"/>
-      <c r="T21" s="36"/>
-      <c r="U21" s="35"/>
+      <c r="T21" s="34"/>
+      <c r="U21" s="33"/>
       <c r="V21" s="18"/>
-      <c r="W21" s="36"/>
-      <c r="X21" s="35"/>
+      <c r="W21" s="34"/>
+      <c r="X21" s="33"/>
       <c r="Y21" s="18"/>
-      <c r="Z21" s="36"/>
-      <c r="AA21" s="35"/>
+      <c r="Z21" s="34"/>
+      <c r="AA21" s="33"/>
       <c r="AB21" s="18"/>
-      <c r="AC21" s="36"/>
-      <c r="AD21" s="35"/>
+      <c r="AC21" s="34"/>
+      <c r="AD21" s="33"/>
       <c r="AE21" s="18"/>
-      <c r="AF21" s="36"/>
-      <c r="AG21" s="35"/>
+      <c r="AF21" s="34"/>
+      <c r="AG21" s="33"/>
       <c r="AH21" s="18"/>
-      <c r="AI21" s="36"/>
-      <c r="AJ21" s="35"/>
+      <c r="AI21" s="34"/>
+      <c r="AJ21" s="33"/>
       <c r="AK21" s="18"/>
-      <c r="AL21" s="36"/>
-      <c r="AM21" s="35"/>
+      <c r="AL21" s="34"/>
+      <c r="AM21" s="33"/>
       <c r="AN21" s="18"/>
-      <c r="AO21" s="36"/>
-      <c r="AP21" s="35"/>
+      <c r="AO21" s="34"/>
+      <c r="AP21" s="33"/>
       <c r="AQ21" s="18"/>
-      <c r="AR21" s="36"/>
+      <c r="AR21" s="34"/>
     </row>
     <row r="22" spans="1:44" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B22" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="35"/>
+      <c r="C22" s="33"/>
       <c r="D22" s="18"/>
-      <c r="E22" s="36"/>
-      <c r="F22" s="35"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="33"/>
       <c r="G22" s="18"/>
-      <c r="H22" s="36"/>
-      <c r="I22" s="35"/>
+      <c r="H22" s="34"/>
+      <c r="I22" s="33"/>
       <c r="J22" s="18"/>
-      <c r="K22" s="36"/>
-      <c r="L22" s="35"/>
+      <c r="K22" s="34"/>
+      <c r="L22" s="33"/>
       <c r="M22" s="18"/>
-      <c r="N22" s="36"/>
-      <c r="O22" s="35"/>
+      <c r="N22" s="34"/>
+      <c r="O22" s="33"/>
       <c r="P22" s="18"/>
-      <c r="Q22" s="36"/>
-      <c r="R22" s="35"/>
+      <c r="Q22" s="34"/>
+      <c r="R22" s="33"/>
       <c r="S22" s="18"/>
-      <c r="T22" s="36"/>
-      <c r="U22" s="35"/>
+      <c r="T22" s="34"/>
+      <c r="U22" s="33"/>
       <c r="V22" s="18"/>
-      <c r="W22" s="36"/>
-      <c r="X22" s="35"/>
+      <c r="W22" s="34"/>
+      <c r="X22" s="33"/>
       <c r="Y22" s="18"/>
-      <c r="Z22" s="36"/>
-      <c r="AA22" s="35"/>
+      <c r="Z22" s="34"/>
+      <c r="AA22" s="33"/>
       <c r="AB22" s="18"/>
-      <c r="AC22" s="36"/>
-      <c r="AD22" s="35"/>
+      <c r="AC22" s="34"/>
+      <c r="AD22" s="33"/>
       <c r="AE22" s="18"/>
-      <c r="AF22" s="36"/>
-      <c r="AG22" s="35"/>
+      <c r="AF22" s="34"/>
+      <c r="AG22" s="33"/>
       <c r="AH22" s="18"/>
-      <c r="AI22" s="36"/>
-      <c r="AJ22" s="35"/>
+      <c r="AI22" s="34"/>
+      <c r="AJ22" s="33"/>
       <c r="AK22" s="18"/>
-      <c r="AL22" s="36"/>
-      <c r="AM22" s="35"/>
+      <c r="AL22" s="34"/>
+      <c r="AM22" s="33"/>
       <c r="AN22" s="18"/>
-      <c r="AO22" s="36"/>
-      <c r="AP22" s="35"/>
+      <c r="AO22" s="34"/>
+      <c r="AP22" s="33"/>
       <c r="AQ22" s="18"/>
-      <c r="AR22" s="36"/>
+      <c r="AR22" s="34"/>
     </row>
     <row r="23" spans="1:44" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B23" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C23" s="35"/>
+      <c r="C23" s="33"/>
       <c r="D23" s="18"/>
-      <c r="E23" s="36"/>
-      <c r="F23" s="35"/>
+      <c r="E23" s="34"/>
+      <c r="F23" s="33"/>
       <c r="G23" s="18"/>
-      <c r="H23" s="36"/>
-      <c r="I23" s="35"/>
+      <c r="H23" s="34"/>
+      <c r="I23" s="33"/>
       <c r="J23" s="18"/>
-      <c r="K23" s="36"/>
-      <c r="L23" s="35"/>
+      <c r="K23" s="34"/>
+      <c r="L23" s="33"/>
       <c r="M23" s="18"/>
-      <c r="N23" s="36"/>
-      <c r="O23" s="35"/>
+      <c r="N23" s="34"/>
+      <c r="O23" s="33"/>
       <c r="P23" s="18"/>
-      <c r="Q23" s="36"/>
-      <c r="R23" s="35"/>
+      <c r="Q23" s="34"/>
+      <c r="R23" s="33"/>
       <c r="S23" s="18"/>
-      <c r="T23" s="36"/>
-      <c r="U23" s="35"/>
+      <c r="T23" s="34"/>
+      <c r="U23" s="33"/>
       <c r="V23" s="18"/>
-      <c r="W23" s="36"/>
-      <c r="X23" s="35"/>
+      <c r="W23" s="34"/>
+      <c r="X23" s="33"/>
       <c r="Y23" s="18"/>
-      <c r="Z23" s="36"/>
-      <c r="AA23" s="35"/>
+      <c r="Z23" s="34"/>
+      <c r="AA23" s="33"/>
       <c r="AB23" s="18"/>
-      <c r="AC23" s="36"/>
-      <c r="AD23" s="35"/>
+      <c r="AC23" s="34"/>
+      <c r="AD23" s="33"/>
       <c r="AE23" s="18"/>
-      <c r="AF23" s="36"/>
-      <c r="AG23" s="35"/>
+      <c r="AF23" s="34"/>
+      <c r="AG23" s="33"/>
       <c r="AH23" s="18"/>
-      <c r="AI23" s="36"/>
-      <c r="AJ23" s="35"/>
+      <c r="AI23" s="34"/>
+      <c r="AJ23" s="33"/>
       <c r="AK23" s="18"/>
-      <c r="AL23" s="36"/>
-      <c r="AM23" s="35"/>
+      <c r="AL23" s="34"/>
+      <c r="AM23" s="33"/>
       <c r="AN23" s="18"/>
-      <c r="AO23" s="36"/>
-      <c r="AP23" s="35"/>
+      <c r="AO23" s="34"/>
+      <c r="AP23" s="33"/>
       <c r="AQ23" s="18"/>
-      <c r="AR23" s="36"/>
+      <c r="AR23" s="34"/>
     </row>
     <row r="24" spans="1:44" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B24" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="35"/>
+      <c r="C24" s="33"/>
       <c r="D24" s="18"/>
-      <c r="E24" s="36"/>
-      <c r="F24" s="35"/>
+      <c r="E24" s="34"/>
+      <c r="F24" s="33"/>
       <c r="G24" s="18"/>
-      <c r="H24" s="36"/>
-      <c r="I24" s="35"/>
+      <c r="H24" s="34"/>
+      <c r="I24" s="33"/>
       <c r="J24" s="18"/>
-      <c r="K24" s="36"/>
-      <c r="L24" s="35"/>
+      <c r="K24" s="34"/>
+      <c r="L24" s="33"/>
       <c r="M24" s="18"/>
-      <c r="N24" s="36"/>
-      <c r="O24" s="35"/>
+      <c r="N24" s="34"/>
+      <c r="O24" s="33"/>
       <c r="P24" s="18"/>
-      <c r="Q24" s="36"/>
-      <c r="R24" s="35"/>
+      <c r="Q24" s="34"/>
+      <c r="R24" s="33"/>
       <c r="S24" s="18"/>
-      <c r="T24" s="36"/>
-      <c r="U24" s="35"/>
+      <c r="T24" s="34"/>
+      <c r="U24" s="33"/>
       <c r="V24" s="18"/>
-      <c r="W24" s="36"/>
-      <c r="X24" s="35"/>
+      <c r="W24" s="34"/>
+      <c r="X24" s="33"/>
       <c r="Y24" s="18"/>
-      <c r="Z24" s="36"/>
-      <c r="AA24" s="35"/>
+      <c r="Z24" s="34"/>
+      <c r="AA24" s="33"/>
       <c r="AB24" s="18"/>
-      <c r="AC24" s="36"/>
-      <c r="AD24" s="35"/>
+      <c r="AC24" s="34"/>
+      <c r="AD24" s="33"/>
       <c r="AE24" s="18"/>
-      <c r="AF24" s="36"/>
-      <c r="AG24" s="35"/>
+      <c r="AF24" s="34"/>
+      <c r="AG24" s="33"/>
       <c r="AH24" s="18"/>
-      <c r="AI24" s="36"/>
-      <c r="AJ24" s="35"/>
+      <c r="AI24" s="34"/>
+      <c r="AJ24" s="33"/>
       <c r="AK24" s="18"/>
-      <c r="AL24" s="36"/>
-      <c r="AM24" s="35"/>
+      <c r="AL24" s="34"/>
+      <c r="AM24" s="33"/>
       <c r="AN24" s="18"/>
-      <c r="AO24" s="36"/>
-      <c r="AP24" s="35"/>
+      <c r="AO24" s="34"/>
+      <c r="AP24" s="33"/>
       <c r="AQ24" s="18"/>
-      <c r="AR24" s="36"/>
+      <c r="AR24" s="34"/>
     </row>
     <row r="25" spans="1:44" ht="76.900000000000006" x14ac:dyDescent="0.45">
       <c r="B25" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="C25" s="35"/>
+      <c r="C25" s="33"/>
       <c r="D25" s="18"/>
-      <c r="E25" s="36"/>
-      <c r="F25" s="35"/>
+      <c r="E25" s="34"/>
+      <c r="F25" s="33"/>
       <c r="G25" s="18"/>
-      <c r="H25" s="36"/>
-      <c r="I25" s="35"/>
+      <c r="H25" s="34"/>
+      <c r="I25" s="33"/>
       <c r="J25" s="18"/>
-      <c r="K25" s="36"/>
-      <c r="L25" s="35"/>
+      <c r="K25" s="34"/>
+      <c r="L25" s="33"/>
       <c r="M25" s="18"/>
-      <c r="N25" s="36"/>
-      <c r="O25" s="35"/>
+      <c r="N25" s="34"/>
+      <c r="O25" s="33"/>
       <c r="P25" s="18"/>
-      <c r="Q25" s="36"/>
-      <c r="R25" s="35"/>
+      <c r="Q25" s="34"/>
+      <c r="R25" s="33"/>
       <c r="S25" s="18"/>
-      <c r="T25" s="36"/>
-      <c r="U25" s="35"/>
+      <c r="T25" s="34"/>
+      <c r="U25" s="33"/>
       <c r="V25" s="18"/>
-      <c r="W25" s="36"/>
-      <c r="X25" s="35"/>
+      <c r="W25" s="34"/>
+      <c r="X25" s="33"/>
       <c r="Y25" s="18"/>
-      <c r="Z25" s="36"/>
-      <c r="AA25" s="35"/>
+      <c r="Z25" s="34"/>
+      <c r="AA25" s="33"/>
       <c r="AB25" s="18"/>
-      <c r="AC25" s="36"/>
-      <c r="AD25" s="35"/>
+      <c r="AC25" s="34"/>
+      <c r="AD25" s="33"/>
       <c r="AE25" s="18"/>
-      <c r="AF25" s="36"/>
-      <c r="AG25" s="35"/>
+      <c r="AF25" s="34"/>
+      <c r="AG25" s="33"/>
       <c r="AH25" s="18"/>
-      <c r="AI25" s="36"/>
-      <c r="AJ25" s="35"/>
+      <c r="AI25" s="34"/>
+      <c r="AJ25" s="33"/>
       <c r="AK25" s="18"/>
-      <c r="AL25" s="36"/>
-      <c r="AM25" s="35"/>
+      <c r="AL25" s="34"/>
+      <c r="AM25" s="33"/>
       <c r="AN25" s="18"/>
-      <c r="AO25" s="36"/>
-      <c r="AP25" s="35"/>
+      <c r="AO25" s="34"/>
+      <c r="AP25" s="33"/>
       <c r="AQ25" s="18"/>
-      <c r="AR25" s="36"/>
+      <c r="AR25" s="34"/>
     </row>
     <row r="26" spans="1:44" x14ac:dyDescent="0.45">
-      <c r="B26" s="33"/>
-      <c r="C26" s="37"/>
-      <c r="D26" s="38"/>
-      <c r="E26" s="39"/>
-      <c r="F26" s="37"/>
-      <c r="G26" s="38"/>
-      <c r="H26" s="39"/>
-      <c r="I26" s="37"/>
-      <c r="J26" s="38"/>
-      <c r="K26" s="39"/>
-      <c r="L26" s="37"/>
-      <c r="M26" s="38"/>
-      <c r="N26" s="39"/>
-      <c r="O26" s="37"/>
-      <c r="P26" s="38"/>
-      <c r="Q26" s="39"/>
-      <c r="R26" s="37"/>
-      <c r="S26" s="38"/>
-      <c r="T26" s="39"/>
-      <c r="U26" s="37"/>
-      <c r="V26" s="38"/>
-      <c r="W26" s="39"/>
-      <c r="X26" s="37"/>
-      <c r="Y26" s="38"/>
-      <c r="Z26" s="39"/>
-      <c r="AA26" s="37"/>
-      <c r="AB26" s="38"/>
-      <c r="AC26" s="39"/>
-      <c r="AD26" s="37"/>
-      <c r="AE26" s="38"/>
-      <c r="AF26" s="39"/>
-      <c r="AG26" s="37"/>
-      <c r="AH26" s="38"/>
-      <c r="AI26" s="39"/>
-      <c r="AJ26" s="37"/>
-      <c r="AK26" s="38"/>
-      <c r="AL26" s="39"/>
-      <c r="AM26" s="37"/>
-      <c r="AN26" s="38"/>
-      <c r="AO26" s="39"/>
-      <c r="AP26" s="37"/>
-      <c r="AQ26" s="38"/>
-      <c r="AR26" s="39"/>
+      <c r="B26" s="31"/>
+      <c r="C26" s="35"/>
+      <c r="D26" s="36"/>
+      <c r="E26" s="37"/>
+      <c r="F26" s="35"/>
+      <c r="G26" s="36"/>
+      <c r="H26" s="37"/>
+      <c r="I26" s="35"/>
+      <c r="J26" s="36"/>
+      <c r="K26" s="37"/>
+      <c r="L26" s="35"/>
+      <c r="M26" s="36"/>
+      <c r="N26" s="37"/>
+      <c r="O26" s="35"/>
+      <c r="P26" s="36"/>
+      <c r="Q26" s="37"/>
+      <c r="R26" s="35"/>
+      <c r="S26" s="36"/>
+      <c r="T26" s="37"/>
+      <c r="U26" s="35"/>
+      <c r="V26" s="36"/>
+      <c r="W26" s="37"/>
+      <c r="X26" s="35"/>
+      <c r="Y26" s="36"/>
+      <c r="Z26" s="37"/>
+      <c r="AA26" s="35"/>
+      <c r="AB26" s="36"/>
+      <c r="AC26" s="37"/>
+      <c r="AD26" s="35"/>
+      <c r="AE26" s="36"/>
+      <c r="AF26" s="37"/>
+      <c r="AG26" s="35"/>
+      <c r="AH26" s="36"/>
+      <c r="AI26" s="37"/>
+      <c r="AJ26" s="35"/>
+      <c r="AK26" s="36"/>
+      <c r="AL26" s="37"/>
+      <c r="AM26" s="35"/>
+      <c r="AN26" s="36"/>
+      <c r="AO26" s="37"/>
+      <c r="AP26" s="35"/>
+      <c r="AQ26" s="36"/>
+      <c r="AR26" s="37"/>
     </row>
     <row r="27" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A27" s="1"/>
-      <c r="B27" s="34" t="s">
+      <c r="B27" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="C27" s="51">
+      <c r="C27" s="50">
         <f>AVERAGE(C4:C26)</f>
         <v>0</v>
       </c>
-      <c r="D27" s="51"/>
-      <c r="E27" s="52"/>
-      <c r="F27" s="51">
+      <c r="D27" s="50"/>
+      <c r="E27" s="51"/>
+      <c r="F27" s="50">
         <f>AVERAGE(F4:F26)</f>
         <v>0</v>
       </c>
-      <c r="G27" s="51"/>
-      <c r="H27" s="52"/>
-      <c r="I27" s="51">
+      <c r="G27" s="50"/>
+      <c r="H27" s="51"/>
+      <c r="I27" s="50">
         <f>AVERAGE(I4:I26)</f>
         <v>0</v>
       </c>
-      <c r="J27" s="51"/>
-      <c r="K27" s="52"/>
-      <c r="L27" s="51">
+      <c r="J27" s="50"/>
+      <c r="K27" s="51"/>
+      <c r="L27" s="50">
         <f>AVERAGE(L4:L26)</f>
         <v>0</v>
       </c>
-      <c r="M27" s="51"/>
-      <c r="N27" s="52"/>
-      <c r="O27" s="51">
+      <c r="M27" s="50"/>
+      <c r="N27" s="51"/>
+      <c r="O27" s="50">
         <f>AVERAGE(O4:O26)</f>
         <v>0</v>
       </c>
-      <c r="P27" s="51"/>
-      <c r="Q27" s="52"/>
-      <c r="R27" s="51">
+      <c r="P27" s="50"/>
+      <c r="Q27" s="51"/>
+      <c r="R27" s="50">
         <f>AVERAGE(R4:R26)</f>
         <v>0</v>
       </c>
-      <c r="S27" s="51"/>
-      <c r="T27" s="52"/>
-      <c r="U27" s="51">
+      <c r="S27" s="50"/>
+      <c r="T27" s="51"/>
+      <c r="U27" s="50">
         <f>AVERAGE(U4:U26)</f>
         <v>0</v>
       </c>
-      <c r="V27" s="51"/>
-      <c r="W27" s="52"/>
-      <c r="X27" s="51">
+      <c r="V27" s="50"/>
+      <c r="W27" s="51"/>
+      <c r="X27" s="50">
         <f>AVERAGE(X4:X26)</f>
         <v>0</v>
       </c>
-      <c r="Y27" s="51"/>
-      <c r="Z27" s="52"/>
-      <c r="AA27" s="51">
+      <c r="Y27" s="50"/>
+      <c r="Z27" s="51"/>
+      <c r="AA27" s="50">
         <f>AVERAGE(AA4:AA26)</f>
         <v>0</v>
       </c>
-      <c r="AB27" s="51"/>
-      <c r="AC27" s="52"/>
-      <c r="AD27" s="51">
+      <c r="AB27" s="50"/>
+      <c r="AC27" s="51"/>
+      <c r="AD27" s="50">
         <f>AVERAGE(AD4:AD26)</f>
         <v>0</v>
       </c>
-      <c r="AE27" s="51"/>
-      <c r="AF27" s="52"/>
-      <c r="AG27" s="51">
+      <c r="AE27" s="50"/>
+      <c r="AF27" s="51"/>
+      <c r="AG27" s="50">
         <f>AVERAGE(AG4:AG26)</f>
         <v>0</v>
       </c>
-      <c r="AH27" s="51"/>
-      <c r="AI27" s="52"/>
-      <c r="AJ27" s="51">
+      <c r="AH27" s="50"/>
+      <c r="AI27" s="51"/>
+      <c r="AJ27" s="50">
         <f>AVERAGE(AJ4:AJ26)</f>
         <v>0</v>
       </c>
-      <c r="AK27" s="51"/>
-      <c r="AL27" s="52"/>
-      <c r="AM27" s="51">
+      <c r="AK27" s="50"/>
+      <c r="AL27" s="51"/>
+      <c r="AM27" s="50">
         <f>AVERAGE(AM4:AM26)</f>
         <v>0</v>
       </c>
-      <c r="AN27" s="51"/>
-      <c r="AO27" s="52"/>
-      <c r="AP27" s="51">
+      <c r="AN27" s="50"/>
+      <c r="AO27" s="51"/>
+      <c r="AP27" s="50">
         <f>AVERAGE(AP4:AP26)</f>
         <v>0</v>
       </c>
-      <c r="AQ27" s="51"/>
-      <c r="AR27" s="52"/>
+      <c r="AQ27" s="50"/>
+      <c r="AR27" s="51"/>
     </row>
     <row r="28" spans="1:44" s="9" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B28" s="16"/>

--- a/activity/M01A07/M01A07_Pendiente.xlsx
+++ b/activity/M01A07/M01A07_Pendiente.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29309"/>
   <workbookPr updateLinks="never" codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.HCMC\activity\M01A07\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B57FBC16-9B45-48AF-8D6F-735B27E3384F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE37F889-5BAD-45A0-B685-0BD1893A98D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" tabRatio="762" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" tabRatio="762" activeTab="1" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
   </bookViews>
   <sheets>
     <sheet name="Calificacion" sheetId="12" r:id="rId1"/>
     <sheet name="Detalle" sheetId="10" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">Detalle!$B$1:$E$27</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">Detalle!$B$1:$E$25</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">Detalle!$1:$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="43">
   <si>
     <t>Observaciones</t>
   </si>
@@ -69,9 +69,6 @@
   </si>
   <si>
     <t>Justificar técnicamente la pendiente de diseño del cauce sinuoso artificial</t>
-  </si>
-  <si>
-    <t>Largo tramo natural a reemplazar, m</t>
   </si>
   <si>
     <t># secciones evaluadas</t>
@@ -663,6 +660,9 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -672,11 +672,11 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="2" fontId="6" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -687,14 +687,11 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -2101,51 +2098,51 @@
   <sheetData>
     <row r="1" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="F1" s="28" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="2:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B2" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
+      <c r="B2" s="43" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B3" s="43"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="43"/>
+      <c r="B3" s="44"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="44"/>
     </row>
     <row r="4" spans="2:6" ht="30.75" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="22" t="s">
         <v>2</v>
       </c>
       <c r="C4" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="21" t="s">
         <v>16</v>
-      </c>
-      <c r="D4" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" s="21" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="52">
+        <v>19</v>
+      </c>
+      <c r="C5" s="42">
         <v>5</v>
       </c>
       <c r="D5" s="23">
-        <f>Detalle!C27*C5/5</f>
+        <f>Detalle!C25*C5/5</f>
         <v>0</v>
       </c>
       <c r="E5" s="29"/>
@@ -2156,13 +2153,13 @@
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" s="52">
+        <v>20</v>
+      </c>
+      <c r="C6" s="42">
         <v>5</v>
       </c>
       <c r="D6" s="23">
-        <f>Detalle!F27*C6/5</f>
+        <f>Detalle!F25*C6/5</f>
         <v>0</v>
       </c>
       <c r="E6" s="29"/>
@@ -2173,13 +2170,13 @@
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="52">
+        <v>21</v>
+      </c>
+      <c r="C7" s="42">
         <v>5</v>
       </c>
       <c r="D7" s="23">
-        <f>Detalle!I27*C7/5</f>
+        <f>Detalle!I25*C7/5</f>
         <v>0</v>
       </c>
       <c r="E7" s="29"/>
@@ -2190,13 +2187,13 @@
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B8" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="52">
+        <v>22</v>
+      </c>
+      <c r="C8" s="42">
         <v>5</v>
       </c>
       <c r="D8" s="23">
-        <f>Detalle!L27*C8/5</f>
+        <f>Detalle!L25*C8/5</f>
         <v>0</v>
       </c>
       <c r="E8" s="29"/>
@@ -2207,13 +2204,13 @@
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B9" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="52">
+        <v>23</v>
+      </c>
+      <c r="C9" s="42">
         <v>5</v>
       </c>
       <c r="D9" s="23">
-        <f>Detalle!O27*C9/5</f>
+        <f>Detalle!O25*C9/5</f>
         <v>0</v>
       </c>
       <c r="E9" s="29"/>
@@ -2224,13 +2221,13 @@
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" s="52">
+        <v>26</v>
+      </c>
+      <c r="C10" s="42">
         <v>5</v>
       </c>
       <c r="D10" s="23">
-        <f>Detalle!R27*C10/5</f>
+        <f>Detalle!R25*C10/5</f>
         <v>0</v>
       </c>
       <c r="E10" s="29"/>
@@ -2241,13 +2238,13 @@
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B11" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" s="52">
+        <v>27</v>
+      </c>
+      <c r="C11" s="42">
         <v>5</v>
       </c>
       <c r="D11" s="23">
-        <f>Detalle!U27*C11/5</f>
+        <f>Detalle!U25*C11/5</f>
         <v>0</v>
       </c>
       <c r="E11" s="29"/>
@@ -2258,13 +2255,13 @@
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B12" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" s="52">
+        <v>28</v>
+      </c>
+      <c r="C12" s="42">
         <v>5</v>
       </c>
       <c r="D12" s="23">
-        <f>Detalle!X27*C12/5</f>
+        <f>Detalle!X25*C12/5</f>
         <v>0</v>
       </c>
       <c r="E12" s="29"/>
@@ -2275,13 +2272,13 @@
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B13" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C13" s="52">
+        <v>29</v>
+      </c>
+      <c r="C13" s="42">
         <v>5</v>
       </c>
       <c r="D13" s="23">
-        <f>Detalle!AA27*C13/5</f>
+        <f>Detalle!AA25*C13/5</f>
         <v>0</v>
       </c>
       <c r="E13" s="29"/>
@@ -2292,13 +2289,13 @@
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B14" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" s="52">
+        <v>30</v>
+      </c>
+      <c r="C14" s="42">
         <v>5</v>
       </c>
       <c r="D14" s="23">
-        <f>Detalle!AD27*C14/5</f>
+        <f>Detalle!AD25*C14/5</f>
         <v>0</v>
       </c>
       <c r="E14" s="29"/>
@@ -2309,13 +2306,13 @@
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B15" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C15" s="52">
+        <v>31</v>
+      </c>
+      <c r="C15" s="42">
         <v>5</v>
       </c>
       <c r="D15" s="23">
-        <f>Detalle!AG27*C15/5</f>
+        <f>Detalle!AG25*C15/5</f>
         <v>0</v>
       </c>
       <c r="E15" s="29"/>
@@ -2326,13 +2323,13 @@
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B16" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C16" s="52">
+        <v>32</v>
+      </c>
+      <c r="C16" s="42">
         <v>5</v>
       </c>
       <c r="D16" s="23">
-        <f>Detalle!AJ27*C16/5</f>
+        <f>Detalle!AJ25*C16/5</f>
         <v>0</v>
       </c>
       <c r="E16" s="29"/>
@@ -2343,13 +2340,13 @@
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B17" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C17" s="52">
+        <v>33</v>
+      </c>
+      <c r="C17" s="42">
         <v>5</v>
       </c>
       <c r="D17" s="23">
-        <f>Detalle!AM27*C17/5</f>
+        <f>Detalle!AM25*C17/5</f>
         <v>0</v>
       </c>
       <c r="E17" s="29"/>
@@ -2360,13 +2357,13 @@
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B18" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C18" s="30">
         <v>5</v>
       </c>
       <c r="D18" s="24">
-        <f>Detalle!AP27*C18/5</f>
+        <f>Detalle!AP25*C18/5</f>
         <v>0</v>
       </c>
       <c r="E18" s="30"/>
@@ -2376,21 +2373,21 @@
       </c>
     </row>
     <row r="19" spans="2:6" ht="15.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B19" s="44" t="str">
+      <c r="B19" s="45" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.HCMC/blob/main/activity/",F1,"/Readme.md"),_xlfn.CONCAT("Ir a actividad ",F1," en GitHub."))</f>
         <v>Ir a actividad M01A07 en GitHub.</v>
       </c>
-      <c r="C19" s="44"/>
-      <c r="D19" s="44"/>
-      <c r="E19" s="44"/>
-      <c r="F19" s="44"/>
+      <c r="C19" s="45"/>
+      <c r="D19" s="45"/>
+      <c r="E19" s="45"/>
+      <c r="F19" s="45"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B20" s="44"/>
-      <c r="C20" s="44"/>
-      <c r="D20" s="44"/>
-      <c r="E20" s="44"/>
-      <c r="F20" s="44"/>
+      <c r="B20" s="45"/>
+      <c r="C20" s="45"/>
+      <c r="D20" s="45"/>
+      <c r="E20" s="45"/>
+      <c r="F20" s="45"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B21" s="27"/>
@@ -2415,7 +2412,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A17987CE-896A-4E26-83D1-1610B3259376}">
   <sheetPr codeName="Hoja1"/>
-  <dimension ref="A1:AR63"/>
+  <dimension ref="A1:AR61"/>
   <sheetFormatPr defaultColWidth="11.3984375" defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="9" customWidth="1"/>
@@ -2488,96 +2485,96 @@
     </row>
     <row r="2" spans="1:44" s="41" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A2" s="40"/>
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="47" t="str">
+      <c r="C2" s="48" t="str">
         <f>Calificacion!B5</f>
         <v>Grupo 1</v>
       </c>
-      <c r="D2" s="48"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="47" t="str">
+      <c r="D2" s="49"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="48" t="str">
         <f>Calificacion!B6</f>
         <v>Grupo 2</v>
       </c>
-      <c r="G2" s="48"/>
-      <c r="H2" s="49"/>
-      <c r="I2" s="47" t="str">
+      <c r="G2" s="49"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="48" t="str">
         <f>Calificacion!B7</f>
         <v>Grupo 3</v>
       </c>
-      <c r="J2" s="48"/>
-      <c r="K2" s="49"/>
-      <c r="L2" s="47" t="str">
+      <c r="J2" s="49"/>
+      <c r="K2" s="50"/>
+      <c r="L2" s="48" t="str">
         <f>Calificacion!B8</f>
         <v>Grupo 4</v>
       </c>
-      <c r="M2" s="48"/>
-      <c r="N2" s="49"/>
-      <c r="O2" s="47" t="str">
+      <c r="M2" s="49"/>
+      <c r="N2" s="50"/>
+      <c r="O2" s="48" t="str">
         <f>Calificacion!B9</f>
         <v>Grupo 5</v>
       </c>
-      <c r="P2" s="48"/>
-      <c r="Q2" s="49"/>
-      <c r="R2" s="47" t="str">
+      <c r="P2" s="49"/>
+      <c r="Q2" s="50"/>
+      <c r="R2" s="48" t="str">
         <f>Calificacion!B10</f>
         <v>Grupo 6</v>
       </c>
-      <c r="S2" s="48"/>
-      <c r="T2" s="49"/>
-      <c r="U2" s="47" t="str">
+      <c r="S2" s="49"/>
+      <c r="T2" s="50"/>
+      <c r="U2" s="48" t="str">
         <f>Calificacion!B11</f>
         <v>Grupo 7</v>
       </c>
-      <c r="V2" s="48"/>
-      <c r="W2" s="49"/>
-      <c r="X2" s="47" t="str">
+      <c r="V2" s="49"/>
+      <c r="W2" s="50"/>
+      <c r="X2" s="48" t="str">
         <f>Calificacion!B12</f>
         <v>Grupo 8</v>
       </c>
-      <c r="Y2" s="48"/>
-      <c r="Z2" s="49"/>
-      <c r="AA2" s="47" t="str">
+      <c r="Y2" s="49"/>
+      <c r="Z2" s="50"/>
+      <c r="AA2" s="48" t="str">
         <f>Calificacion!B13</f>
         <v>Grupo 9</v>
       </c>
-      <c r="AB2" s="48"/>
-      <c r="AC2" s="49"/>
-      <c r="AD2" s="47" t="str">
+      <c r="AB2" s="49"/>
+      <c r="AC2" s="50"/>
+      <c r="AD2" s="48" t="str">
         <f>Calificacion!B14</f>
         <v>Grupo 10</v>
       </c>
-      <c r="AE2" s="48"/>
-      <c r="AF2" s="49"/>
-      <c r="AG2" s="47" t="str">
+      <c r="AE2" s="49"/>
+      <c r="AF2" s="50"/>
+      <c r="AG2" s="48" t="str">
         <f>Calificacion!B15</f>
         <v>Grupo 11</v>
       </c>
-      <c r="AH2" s="48"/>
-      <c r="AI2" s="49"/>
-      <c r="AJ2" s="47" t="str">
+      <c r="AH2" s="49"/>
+      <c r="AI2" s="50"/>
+      <c r="AJ2" s="48" t="str">
         <f>Calificacion!B16</f>
         <v>Grupo 12</v>
       </c>
-      <c r="AK2" s="48"/>
-      <c r="AL2" s="49"/>
-      <c r="AM2" s="47" t="str">
+      <c r="AK2" s="49"/>
+      <c r="AL2" s="50"/>
+      <c r="AM2" s="48" t="str">
         <f>Calificacion!B17</f>
         <v>Grupo 13</v>
       </c>
-      <c r="AN2" s="48"/>
-      <c r="AO2" s="49"/>
-      <c r="AP2" s="47" t="str">
+      <c r="AN2" s="49"/>
+      <c r="AO2" s="50"/>
+      <c r="AP2" s="48" t="str">
         <f>Calificacion!B18</f>
         <v>Grupo 14</v>
       </c>
-      <c r="AQ2" s="48"/>
-      <c r="AR2" s="49"/>
+      <c r="AQ2" s="49"/>
+      <c r="AR2" s="50"/>
     </row>
     <row r="3" spans="1:44" x14ac:dyDescent="0.45">
-      <c r="B3" s="46"/>
+      <c r="B3" s="52"/>
       <c r="C3" s="12" t="s">
         <v>1</v>
       </c>
@@ -2754,7 +2751,7 @@
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B5" s="14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C5" s="33">
         <v>0</v>
@@ -2829,7 +2826,7 @@
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B6" s="14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C6" s="33"/>
       <c r="D6" s="18"/>
@@ -2876,7 +2873,7 @@
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B7" s="14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C7" s="33"/>
       <c r="D7" s="18"/>
@@ -2923,7 +2920,7 @@
     </row>
     <row r="8" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B8" s="14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C8" s="33"/>
       <c r="D8" s="39">
@@ -3012,54 +3009,96 @@
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B9" s="14" t="s">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="C9" s="33"/>
-      <c r="D9" s="18"/>
+      <c r="D9" s="38" t="e">
+        <f>D8/D7</f>
+        <v>#DIV/0!</v>
+      </c>
       <c r="E9" s="34"/>
       <c r="F9" s="33"/>
-      <c r="G9" s="18"/>
+      <c r="G9" s="38" t="e">
+        <f>G8/G7</f>
+        <v>#DIV/0!</v>
+      </c>
       <c r="H9" s="34"/>
       <c r="I9" s="33"/>
-      <c r="J9" s="18"/>
+      <c r="J9" s="38" t="e">
+        <f>J8/J7</f>
+        <v>#DIV/0!</v>
+      </c>
       <c r="K9" s="34"/>
       <c r="L9" s="33"/>
-      <c r="M9" s="18"/>
+      <c r="M9" s="38" t="e">
+        <f>M8/M7</f>
+        <v>#DIV/0!</v>
+      </c>
       <c r="N9" s="34"/>
       <c r="O9" s="33"/>
-      <c r="P9" s="18"/>
+      <c r="P9" s="38" t="e">
+        <f>P8/P7</f>
+        <v>#DIV/0!</v>
+      </c>
       <c r="Q9" s="34"/>
       <c r="R9" s="33"/>
-      <c r="S9" s="18"/>
+      <c r="S9" s="38" t="e">
+        <f>S8/S7</f>
+        <v>#DIV/0!</v>
+      </c>
       <c r="T9" s="34"/>
       <c r="U9" s="33"/>
-      <c r="V9" s="18"/>
+      <c r="V9" s="38" t="e">
+        <f>V8/V7</f>
+        <v>#DIV/0!</v>
+      </c>
       <c r="W9" s="34"/>
       <c r="X9" s="33"/>
-      <c r="Y9" s="18"/>
+      <c r="Y9" s="38" t="e">
+        <f>Y8/Y7</f>
+        <v>#DIV/0!</v>
+      </c>
       <c r="Z9" s="34"/>
       <c r="AA9" s="33"/>
-      <c r="AB9" s="18"/>
+      <c r="AB9" s="38" t="e">
+        <f>AB8/AB7</f>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AC9" s="34"/>
       <c r="AD9" s="33"/>
-      <c r="AE9" s="18"/>
+      <c r="AE9" s="38" t="e">
+        <f>AE8/AE7</f>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AF9" s="34"/>
       <c r="AG9" s="33"/>
-      <c r="AH9" s="18"/>
+      <c r="AH9" s="38" t="e">
+        <f>AH8/AH7</f>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AI9" s="34"/>
       <c r="AJ9" s="33"/>
-      <c r="AK9" s="18"/>
+      <c r="AK9" s="38" t="e">
+        <f>AK8/AK7</f>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AL9" s="34"/>
       <c r="AM9" s="33"/>
-      <c r="AN9" s="18"/>
+      <c r="AN9" s="38" t="e">
+        <f>AN8/AN7</f>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AO9" s="34"/>
       <c r="AP9" s="33"/>
-      <c r="AQ9" s="18"/>
+      <c r="AQ9" s="38" t="e">
+        <f>AQ8/AQ7</f>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AR9" s="34"/>
     </row>
-    <row r="10" spans="1:44" x14ac:dyDescent="0.45">
-      <c r="B10" s="14" t="s">
-        <v>10</v>
+    <row r="10" spans="1:44" ht="30.75" x14ac:dyDescent="0.45">
+      <c r="B10" s="11" t="s">
+        <v>8</v>
       </c>
       <c r="C10" s="33"/>
       <c r="D10" s="18"/>
@@ -3106,96 +3145,54 @@
     </row>
     <row r="11" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B11" s="14" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C11" s="33"/>
-      <c r="D11" s="38" t="e">
-        <f>D9/D10</f>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="D11" s="18"/>
       <c r="E11" s="34"/>
       <c r="F11" s="33"/>
-      <c r="G11" s="38" t="e">
-        <f>G9/G10</f>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="G11" s="18"/>
       <c r="H11" s="34"/>
       <c r="I11" s="33"/>
-      <c r="J11" s="38" t="e">
-        <f>J9/J10</f>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="J11" s="18"/>
       <c r="K11" s="34"/>
       <c r="L11" s="33"/>
-      <c r="M11" s="38" t="e">
-        <f>M9/M10</f>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="M11" s="18"/>
       <c r="N11" s="34"/>
       <c r="O11" s="33"/>
-      <c r="P11" s="38" t="e">
-        <f>P9/P10</f>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="P11" s="18"/>
       <c r="Q11" s="34"/>
       <c r="R11" s="33"/>
-      <c r="S11" s="38" t="e">
-        <f>S9/S10</f>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="S11" s="18"/>
       <c r="T11" s="34"/>
       <c r="U11" s="33"/>
-      <c r="V11" s="38" t="e">
-        <f>V9/V10</f>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="V11" s="18"/>
       <c r="W11" s="34"/>
       <c r="X11" s="33"/>
-      <c r="Y11" s="38" t="e">
-        <f>Y9/Y10</f>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="Y11" s="18"/>
       <c r="Z11" s="34"/>
       <c r="AA11" s="33"/>
-      <c r="AB11" s="38" t="e">
-        <f>AB9/AB10</f>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="AB11" s="18"/>
       <c r="AC11" s="34"/>
       <c r="AD11" s="33"/>
-      <c r="AE11" s="38" t="e">
-        <f>AE9/AE10</f>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="AE11" s="18"/>
       <c r="AF11" s="34"/>
       <c r="AG11" s="33"/>
-      <c r="AH11" s="38" t="e">
-        <f>AH9/AH10</f>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="AH11" s="18"/>
       <c r="AI11" s="34"/>
       <c r="AJ11" s="33"/>
-      <c r="AK11" s="38" t="e">
-        <f>AK9/AK10</f>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="AK11" s="18"/>
       <c r="AL11" s="34"/>
       <c r="AM11" s="33"/>
-      <c r="AN11" s="38" t="e">
-        <f>AN9/AN10</f>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="AN11" s="18"/>
       <c r="AO11" s="34"/>
       <c r="AP11" s="33"/>
-      <c r="AQ11" s="38" t="e">
-        <f>AQ9/AQ10</f>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="AQ11" s="18"/>
       <c r="AR11" s="34"/>
     </row>
-    <row r="12" spans="1:44" ht="30.75" x14ac:dyDescent="0.45">
-      <c r="B12" s="11" t="s">
-        <v>8</v>
+    <row r="12" spans="1:44" x14ac:dyDescent="0.45">
+      <c r="B12" s="14" t="s">
+        <v>12</v>
       </c>
       <c r="C12" s="33"/>
       <c r="D12" s="18"/>
@@ -3245,51 +3242,51 @@
         <v>11</v>
       </c>
       <c r="C13" s="33"/>
-      <c r="D13" s="18"/>
+      <c r="D13" s="19"/>
       <c r="E13" s="34"/>
       <c r="F13" s="33"/>
-      <c r="G13" s="18"/>
+      <c r="G13" s="19"/>
       <c r="H13" s="34"/>
       <c r="I13" s="33"/>
-      <c r="J13" s="18"/>
+      <c r="J13" s="19"/>
       <c r="K13" s="34"/>
       <c r="L13" s="33"/>
-      <c r="M13" s="18"/>
+      <c r="M13" s="19"/>
       <c r="N13" s="34"/>
       <c r="O13" s="33"/>
-      <c r="P13" s="18"/>
+      <c r="P13" s="19"/>
       <c r="Q13" s="34"/>
       <c r="R13" s="33"/>
-      <c r="S13" s="18"/>
+      <c r="S13" s="19"/>
       <c r="T13" s="34"/>
       <c r="U13" s="33"/>
-      <c r="V13" s="18"/>
+      <c r="V13" s="19"/>
       <c r="W13" s="34"/>
       <c r="X13" s="33"/>
-      <c r="Y13" s="18"/>
+      <c r="Y13" s="19"/>
       <c r="Z13" s="34"/>
       <c r="AA13" s="33"/>
-      <c r="AB13" s="18"/>
+      <c r="AB13" s="19"/>
       <c r="AC13" s="34"/>
       <c r="AD13" s="33"/>
-      <c r="AE13" s="18"/>
+      <c r="AE13" s="19"/>
       <c r="AF13" s="34"/>
       <c r="AG13" s="33"/>
-      <c r="AH13" s="18"/>
+      <c r="AH13" s="19"/>
       <c r="AI13" s="34"/>
       <c r="AJ13" s="33"/>
-      <c r="AK13" s="18"/>
+      <c r="AK13" s="19"/>
       <c r="AL13" s="34"/>
       <c r="AM13" s="33"/>
-      <c r="AN13" s="18"/>
+      <c r="AN13" s="19"/>
       <c r="AO13" s="34"/>
       <c r="AP13" s="33"/>
-      <c r="AQ13" s="18"/>
+      <c r="AQ13" s="19"/>
       <c r="AR13" s="34"/>
     </row>
     <row r="14" spans="1:44" x14ac:dyDescent="0.45">
-      <c r="B14" s="14" t="s">
-        <v>13</v>
+      <c r="B14" s="11" t="s">
+        <v>7</v>
       </c>
       <c r="C14" s="33"/>
       <c r="D14" s="18"/>
@@ -3336,54 +3333,54 @@
     </row>
     <row r="15" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B15" s="14" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="C15" s="33"/>
-      <c r="D15" s="19"/>
+      <c r="D15" s="18"/>
       <c r="E15" s="34"/>
       <c r="F15" s="33"/>
-      <c r="G15" s="19"/>
+      <c r="G15" s="18"/>
       <c r="H15" s="34"/>
       <c r="I15" s="33"/>
-      <c r="J15" s="19"/>
+      <c r="J15" s="18"/>
       <c r="K15" s="34"/>
       <c r="L15" s="33"/>
-      <c r="M15" s="19"/>
+      <c r="M15" s="18"/>
       <c r="N15" s="34"/>
       <c r="O15" s="33"/>
-      <c r="P15" s="19"/>
+      <c r="P15" s="18"/>
       <c r="Q15" s="34"/>
       <c r="R15" s="33"/>
-      <c r="S15" s="19"/>
+      <c r="S15" s="18"/>
       <c r="T15" s="34"/>
       <c r="U15" s="33"/>
-      <c r="V15" s="19"/>
+      <c r="V15" s="18"/>
       <c r="W15" s="34"/>
       <c r="X15" s="33"/>
-      <c r="Y15" s="19"/>
+      <c r="Y15" s="18"/>
       <c r="Z15" s="34"/>
       <c r="AA15" s="33"/>
-      <c r="AB15" s="19"/>
+      <c r="AB15" s="18"/>
       <c r="AC15" s="34"/>
       <c r="AD15" s="33"/>
-      <c r="AE15" s="19"/>
+      <c r="AE15" s="18"/>
       <c r="AF15" s="34"/>
       <c r="AG15" s="33"/>
-      <c r="AH15" s="19"/>
+      <c r="AH15" s="18"/>
       <c r="AI15" s="34"/>
       <c r="AJ15" s="33"/>
-      <c r="AK15" s="19"/>
+      <c r="AK15" s="18"/>
       <c r="AL15" s="34"/>
       <c r="AM15" s="33"/>
-      <c r="AN15" s="19"/>
+      <c r="AN15" s="18"/>
       <c r="AO15" s="34"/>
       <c r="AP15" s="33"/>
-      <c r="AQ15" s="19"/>
+      <c r="AQ15" s="18"/>
       <c r="AR15" s="34"/>
     </row>
     <row r="16" spans="1:44" x14ac:dyDescent="0.45">
-      <c r="B16" s="11" t="s">
-        <v>7</v>
+      <c r="B16" s="14" t="s">
+        <v>42</v>
       </c>
       <c r="C16" s="33"/>
       <c r="D16" s="18"/>
@@ -3430,7 +3427,7 @@
     </row>
     <row r="17" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B17" s="14" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="C17" s="33"/>
       <c r="D17" s="18"/>
@@ -3477,54 +3474,96 @@
     </row>
     <row r="18" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B18" s="14" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="C18" s="33"/>
-      <c r="D18" s="18"/>
+      <c r="D18" s="38" t="e">
+        <f>D15/D17</f>
+        <v>#DIV/0!</v>
+      </c>
       <c r="E18" s="34"/>
       <c r="F18" s="33"/>
-      <c r="G18" s="18"/>
+      <c r="G18" s="38" t="e">
+        <f>G15/G17</f>
+        <v>#DIV/0!</v>
+      </c>
       <c r="H18" s="34"/>
       <c r="I18" s="33"/>
-      <c r="J18" s="18"/>
+      <c r="J18" s="38" t="e">
+        <f>J15/J17</f>
+        <v>#DIV/0!</v>
+      </c>
       <c r="K18" s="34"/>
       <c r="L18" s="33"/>
-      <c r="M18" s="18"/>
+      <c r="M18" s="38" t="e">
+        <f>M15/M17</f>
+        <v>#DIV/0!</v>
+      </c>
       <c r="N18" s="34"/>
       <c r="O18" s="33"/>
-      <c r="P18" s="18"/>
+      <c r="P18" s="38" t="e">
+        <f>P15/P17</f>
+        <v>#DIV/0!</v>
+      </c>
       <c r="Q18" s="34"/>
       <c r="R18" s="33"/>
-      <c r="S18" s="18"/>
+      <c r="S18" s="38" t="e">
+        <f>S15/S17</f>
+        <v>#DIV/0!</v>
+      </c>
       <c r="T18" s="34"/>
       <c r="U18" s="33"/>
-      <c r="V18" s="18"/>
+      <c r="V18" s="38" t="e">
+        <f>V15/V17</f>
+        <v>#DIV/0!</v>
+      </c>
       <c r="W18" s="34"/>
       <c r="X18" s="33"/>
-      <c r="Y18" s="18"/>
+      <c r="Y18" s="38" t="e">
+        <f>Y15/Y17</f>
+        <v>#DIV/0!</v>
+      </c>
       <c r="Z18" s="34"/>
       <c r="AA18" s="33"/>
-      <c r="AB18" s="18"/>
+      <c r="AB18" s="38" t="e">
+        <f>AB15/AB17</f>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AC18" s="34"/>
       <c r="AD18" s="33"/>
-      <c r="AE18" s="18"/>
+      <c r="AE18" s="38" t="e">
+        <f>AE15/AE17</f>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AF18" s="34"/>
       <c r="AG18" s="33"/>
-      <c r="AH18" s="18"/>
+      <c r="AH18" s="38" t="e">
+        <f>AH15/AH17</f>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AI18" s="34"/>
       <c r="AJ18" s="33"/>
-      <c r="AK18" s="18"/>
+      <c r="AK18" s="38" t="e">
+        <f>AK15/AK17</f>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AL18" s="34"/>
       <c r="AM18" s="33"/>
-      <c r="AN18" s="18"/>
+      <c r="AN18" s="38" t="e">
+        <f>AN15/AN17</f>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AO18" s="34"/>
       <c r="AP18" s="33"/>
-      <c r="AQ18" s="18"/>
+      <c r="AQ18" s="38" t="e">
+        <f>AQ15/AQ17</f>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AR18" s="34"/>
     </row>
     <row r="19" spans="1:44" x14ac:dyDescent="0.45">
-      <c r="B19" s="14" t="s">
-        <v>14</v>
+      <c r="B19" s="11" t="s">
+        <v>4</v>
       </c>
       <c r="C19" s="33"/>
       <c r="D19" s="18"/>
@@ -3569,98 +3608,56 @@
       <c r="AQ19" s="18"/>
       <c r="AR19" s="34"/>
     </row>
-    <row r="20" spans="1:44" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:44" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B20" s="14" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C20" s="33"/>
-      <c r="D20" s="38" t="e">
-        <f>D17/D19</f>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="D20" s="18"/>
       <c r="E20" s="34"/>
       <c r="F20" s="33"/>
-      <c r="G20" s="38" t="e">
-        <f>G17/G19</f>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="G20" s="18"/>
       <c r="H20" s="34"/>
       <c r="I20" s="33"/>
-      <c r="J20" s="38" t="e">
-        <f>J17/J19</f>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="J20" s="18"/>
       <c r="K20" s="34"/>
       <c r="L20" s="33"/>
-      <c r="M20" s="38" t="e">
-        <f>M17/M19</f>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="M20" s="18"/>
       <c r="N20" s="34"/>
       <c r="O20" s="33"/>
-      <c r="P20" s="38" t="e">
-        <f>P17/P19</f>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="P20" s="18"/>
       <c r="Q20" s="34"/>
       <c r="R20" s="33"/>
-      <c r="S20" s="38" t="e">
-        <f>S17/S19</f>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="S20" s="18"/>
       <c r="T20" s="34"/>
       <c r="U20" s="33"/>
-      <c r="V20" s="38" t="e">
-        <f>V17/V19</f>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="V20" s="18"/>
       <c r="W20" s="34"/>
       <c r="X20" s="33"/>
-      <c r="Y20" s="38" t="e">
-        <f>Y17/Y19</f>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="Y20" s="18"/>
       <c r="Z20" s="34"/>
       <c r="AA20" s="33"/>
-      <c r="AB20" s="38" t="e">
-        <f>AB17/AB19</f>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="AB20" s="18"/>
       <c r="AC20" s="34"/>
       <c r="AD20" s="33"/>
-      <c r="AE20" s="38" t="e">
-        <f>AE17/AE19</f>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="AE20" s="18"/>
       <c r="AF20" s="34"/>
       <c r="AG20" s="33"/>
-      <c r="AH20" s="38" t="e">
-        <f>AH17/AH19</f>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="AH20" s="18"/>
       <c r="AI20" s="34"/>
       <c r="AJ20" s="33"/>
-      <c r="AK20" s="38" t="e">
-        <f>AK17/AK19</f>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="AK20" s="18"/>
       <c r="AL20" s="34"/>
       <c r="AM20" s="33"/>
-      <c r="AN20" s="38" t="e">
-        <f>AN17/AN19</f>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="AN20" s="18"/>
       <c r="AO20" s="34"/>
       <c r="AP20" s="33"/>
-      <c r="AQ20" s="38" t="e">
-        <f>AQ17/AQ19</f>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="AQ20" s="18"/>
       <c r="AR20" s="34"/>
     </row>
-    <row r="21" spans="1:44" x14ac:dyDescent="0.45">
-      <c r="B21" s="11" t="s">
-        <v>4</v>
+    <row r="21" spans="1:44" ht="30.75" x14ac:dyDescent="0.45">
+      <c r="B21" s="14" t="s">
+        <v>14</v>
       </c>
       <c r="C21" s="33"/>
       <c r="D21" s="18"/>
@@ -3707,7 +3704,7 @@
     </row>
     <row r="22" spans="1:44" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B22" s="14" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="C22" s="33"/>
       <c r="D22" s="18"/>
@@ -3752,9 +3749,9 @@
       <c r="AQ22" s="18"/>
       <c r="AR22" s="34"/>
     </row>
-    <row r="23" spans="1:44" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:44" ht="76.900000000000006" x14ac:dyDescent="0.45">
       <c r="B23" s="14" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="C23" s="33"/>
       <c r="D23" s="18"/>
@@ -3799,237 +3796,233 @@
       <c r="AQ23" s="18"/>
       <c r="AR23" s="34"/>
     </row>
-    <row r="24" spans="1:44" ht="30.75" x14ac:dyDescent="0.45">
-      <c r="B24" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="C24" s="33"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="34"/>
-      <c r="F24" s="33"/>
-      <c r="G24" s="18"/>
-      <c r="H24" s="34"/>
-      <c r="I24" s="33"/>
-      <c r="J24" s="18"/>
-      <c r="K24" s="34"/>
-      <c r="L24" s="33"/>
-      <c r="M24" s="18"/>
-      <c r="N24" s="34"/>
-      <c r="O24" s="33"/>
-      <c r="P24" s="18"/>
-      <c r="Q24" s="34"/>
-      <c r="R24" s="33"/>
-      <c r="S24" s="18"/>
-      <c r="T24" s="34"/>
-      <c r="U24" s="33"/>
-      <c r="V24" s="18"/>
-      <c r="W24" s="34"/>
-      <c r="X24" s="33"/>
-      <c r="Y24" s="18"/>
-      <c r="Z24" s="34"/>
-      <c r="AA24" s="33"/>
-      <c r="AB24" s="18"/>
-      <c r="AC24" s="34"/>
-      <c r="AD24" s="33"/>
-      <c r="AE24" s="18"/>
-      <c r="AF24" s="34"/>
-      <c r="AG24" s="33"/>
-      <c r="AH24" s="18"/>
-      <c r="AI24" s="34"/>
-      <c r="AJ24" s="33"/>
-      <c r="AK24" s="18"/>
-      <c r="AL24" s="34"/>
-      <c r="AM24" s="33"/>
-      <c r="AN24" s="18"/>
-      <c r="AO24" s="34"/>
-      <c r="AP24" s="33"/>
-      <c r="AQ24" s="18"/>
-      <c r="AR24" s="34"/>
-    </row>
-    <row r="25" spans="1:44" ht="76.900000000000006" x14ac:dyDescent="0.45">
-      <c r="B25" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="C25" s="33"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="34"/>
-      <c r="F25" s="33"/>
-      <c r="G25" s="18"/>
-      <c r="H25" s="34"/>
-      <c r="I25" s="33"/>
-      <c r="J25" s="18"/>
-      <c r="K25" s="34"/>
-      <c r="L25" s="33"/>
-      <c r="M25" s="18"/>
-      <c r="N25" s="34"/>
-      <c r="O25" s="33"/>
-      <c r="P25" s="18"/>
-      <c r="Q25" s="34"/>
-      <c r="R25" s="33"/>
-      <c r="S25" s="18"/>
-      <c r="T25" s="34"/>
-      <c r="U25" s="33"/>
-      <c r="V25" s="18"/>
-      <c r="W25" s="34"/>
-      <c r="X25" s="33"/>
-      <c r="Y25" s="18"/>
-      <c r="Z25" s="34"/>
-      <c r="AA25" s="33"/>
-      <c r="AB25" s="18"/>
-      <c r="AC25" s="34"/>
-      <c r="AD25" s="33"/>
-      <c r="AE25" s="18"/>
-      <c r="AF25" s="34"/>
-      <c r="AG25" s="33"/>
-      <c r="AH25" s="18"/>
-      <c r="AI25" s="34"/>
-      <c r="AJ25" s="33"/>
-      <c r="AK25" s="18"/>
-      <c r="AL25" s="34"/>
-      <c r="AM25" s="33"/>
-      <c r="AN25" s="18"/>
-      <c r="AO25" s="34"/>
-      <c r="AP25" s="33"/>
-      <c r="AQ25" s="18"/>
-      <c r="AR25" s="34"/>
-    </row>
-    <row r="26" spans="1:44" x14ac:dyDescent="0.45">
-      <c r="B26" s="31"/>
-      <c r="C26" s="35"/>
-      <c r="D26" s="36"/>
-      <c r="E26" s="37"/>
-      <c r="F26" s="35"/>
-      <c r="G26" s="36"/>
-      <c r="H26" s="37"/>
-      <c r="I26" s="35"/>
-      <c r="J26" s="36"/>
-      <c r="K26" s="37"/>
-      <c r="L26" s="35"/>
-      <c r="M26" s="36"/>
-      <c r="N26" s="37"/>
-      <c r="O26" s="35"/>
-      <c r="P26" s="36"/>
-      <c r="Q26" s="37"/>
-      <c r="R26" s="35"/>
-      <c r="S26" s="36"/>
-      <c r="T26" s="37"/>
-      <c r="U26" s="35"/>
-      <c r="V26" s="36"/>
-      <c r="W26" s="37"/>
-      <c r="X26" s="35"/>
-      <c r="Y26" s="36"/>
-      <c r="Z26" s="37"/>
-      <c r="AA26" s="35"/>
-      <c r="AB26" s="36"/>
-      <c r="AC26" s="37"/>
-      <c r="AD26" s="35"/>
-      <c r="AE26" s="36"/>
-      <c r="AF26" s="37"/>
-      <c r="AG26" s="35"/>
-      <c r="AH26" s="36"/>
-      <c r="AI26" s="37"/>
-      <c r="AJ26" s="35"/>
-      <c r="AK26" s="36"/>
-      <c r="AL26" s="37"/>
-      <c r="AM26" s="35"/>
-      <c r="AN26" s="36"/>
-      <c r="AO26" s="37"/>
-      <c r="AP26" s="35"/>
-      <c r="AQ26" s="36"/>
-      <c r="AR26" s="37"/>
-    </row>
-    <row r="27" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A27" s="1"/>
-      <c r="B27" s="32" t="s">
+    <row r="24" spans="1:44" x14ac:dyDescent="0.45">
+      <c r="B24" s="31"/>
+      <c r="C24" s="35"/>
+      <c r="D24" s="36"/>
+      <c r="E24" s="37"/>
+      <c r="F24" s="35"/>
+      <c r="G24" s="36"/>
+      <c r="H24" s="37"/>
+      <c r="I24" s="35"/>
+      <c r="J24" s="36"/>
+      <c r="K24" s="37"/>
+      <c r="L24" s="35"/>
+      <c r="M24" s="36"/>
+      <c r="N24" s="37"/>
+      <c r="O24" s="35"/>
+      <c r="P24" s="36"/>
+      <c r="Q24" s="37"/>
+      <c r="R24" s="35"/>
+      <c r="S24" s="36"/>
+      <c r="T24" s="37"/>
+      <c r="U24" s="35"/>
+      <c r="V24" s="36"/>
+      <c r="W24" s="37"/>
+      <c r="X24" s="35"/>
+      <c r="Y24" s="36"/>
+      <c r="Z24" s="37"/>
+      <c r="AA24" s="35"/>
+      <c r="AB24" s="36"/>
+      <c r="AC24" s="37"/>
+      <c r="AD24" s="35"/>
+      <c r="AE24" s="36"/>
+      <c r="AF24" s="37"/>
+      <c r="AG24" s="35"/>
+      <c r="AH24" s="36"/>
+      <c r="AI24" s="37"/>
+      <c r="AJ24" s="35"/>
+      <c r="AK24" s="36"/>
+      <c r="AL24" s="37"/>
+      <c r="AM24" s="35"/>
+      <c r="AN24" s="36"/>
+      <c r="AO24" s="37"/>
+      <c r="AP24" s="35"/>
+      <c r="AQ24" s="36"/>
+      <c r="AR24" s="37"/>
+    </row>
+    <row r="25" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="1"/>
+      <c r="B25" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="C27" s="50">
-        <f>AVERAGE(C4:C26)</f>
-        <v>0</v>
-      </c>
-      <c r="D27" s="50"/>
-      <c r="E27" s="51"/>
-      <c r="F27" s="50">
-        <f>AVERAGE(F4:F26)</f>
-        <v>0</v>
-      </c>
-      <c r="G27" s="50"/>
-      <c r="H27" s="51"/>
-      <c r="I27" s="50">
-        <f>AVERAGE(I4:I26)</f>
-        <v>0</v>
-      </c>
-      <c r="J27" s="50"/>
-      <c r="K27" s="51"/>
-      <c r="L27" s="50">
-        <f>AVERAGE(L4:L26)</f>
-        <v>0</v>
-      </c>
-      <c r="M27" s="50"/>
-      <c r="N27" s="51"/>
-      <c r="O27" s="50">
-        <f>AVERAGE(O4:O26)</f>
-        <v>0</v>
-      </c>
-      <c r="P27" s="50"/>
-      <c r="Q27" s="51"/>
-      <c r="R27" s="50">
-        <f>AVERAGE(R4:R26)</f>
-        <v>0</v>
-      </c>
-      <c r="S27" s="50"/>
-      <c r="T27" s="51"/>
-      <c r="U27" s="50">
-        <f>AVERAGE(U4:U26)</f>
-        <v>0</v>
-      </c>
-      <c r="V27" s="50"/>
-      <c r="W27" s="51"/>
-      <c r="X27" s="50">
-        <f>AVERAGE(X4:X26)</f>
-        <v>0</v>
-      </c>
-      <c r="Y27" s="50"/>
-      <c r="Z27" s="51"/>
-      <c r="AA27" s="50">
-        <f>AVERAGE(AA4:AA26)</f>
-        <v>0</v>
-      </c>
-      <c r="AB27" s="50"/>
-      <c r="AC27" s="51"/>
-      <c r="AD27" s="50">
-        <f>AVERAGE(AD4:AD26)</f>
-        <v>0</v>
-      </c>
-      <c r="AE27" s="50"/>
-      <c r="AF27" s="51"/>
-      <c r="AG27" s="50">
-        <f>AVERAGE(AG4:AG26)</f>
-        <v>0</v>
-      </c>
-      <c r="AH27" s="50"/>
-      <c r="AI27" s="51"/>
-      <c r="AJ27" s="50">
-        <f>AVERAGE(AJ4:AJ26)</f>
-        <v>0</v>
-      </c>
-      <c r="AK27" s="50"/>
-      <c r="AL27" s="51"/>
-      <c r="AM27" s="50">
-        <f>AVERAGE(AM4:AM26)</f>
-        <v>0</v>
-      </c>
-      <c r="AN27" s="50"/>
-      <c r="AO27" s="51"/>
-      <c r="AP27" s="50">
-        <f>AVERAGE(AP4:AP26)</f>
-        <v>0</v>
-      </c>
-      <c r="AQ27" s="50"/>
-      <c r="AR27" s="51"/>
+      <c r="C25" s="46">
+        <f>AVERAGE(C4:C24)</f>
+        <v>0</v>
+      </c>
+      <c r="D25" s="46"/>
+      <c r="E25" s="47"/>
+      <c r="F25" s="46">
+        <f>AVERAGE(F4:F24)</f>
+        <v>0</v>
+      </c>
+      <c r="G25" s="46"/>
+      <c r="H25" s="47"/>
+      <c r="I25" s="46">
+        <f>AVERAGE(I4:I24)</f>
+        <v>0</v>
+      </c>
+      <c r="J25" s="46"/>
+      <c r="K25" s="47"/>
+      <c r="L25" s="46">
+        <f>AVERAGE(L4:L24)</f>
+        <v>0</v>
+      </c>
+      <c r="M25" s="46"/>
+      <c r="N25" s="47"/>
+      <c r="O25" s="46">
+        <f>AVERAGE(O4:O24)</f>
+        <v>0</v>
+      </c>
+      <c r="P25" s="46"/>
+      <c r="Q25" s="47"/>
+      <c r="R25" s="46">
+        <f>AVERAGE(R4:R24)</f>
+        <v>0</v>
+      </c>
+      <c r="S25" s="46"/>
+      <c r="T25" s="47"/>
+      <c r="U25" s="46">
+        <f>AVERAGE(U4:U24)</f>
+        <v>0</v>
+      </c>
+      <c r="V25" s="46"/>
+      <c r="W25" s="47"/>
+      <c r="X25" s="46">
+        <f>AVERAGE(X4:X24)</f>
+        <v>0</v>
+      </c>
+      <c r="Y25" s="46"/>
+      <c r="Z25" s="47"/>
+      <c r="AA25" s="46">
+        <f>AVERAGE(AA4:AA24)</f>
+        <v>0</v>
+      </c>
+      <c r="AB25" s="46"/>
+      <c r="AC25" s="47"/>
+      <c r="AD25" s="46">
+        <f>AVERAGE(AD4:AD24)</f>
+        <v>0</v>
+      </c>
+      <c r="AE25" s="46"/>
+      <c r="AF25" s="47"/>
+      <c r="AG25" s="46">
+        <f>AVERAGE(AG4:AG24)</f>
+        <v>0</v>
+      </c>
+      <c r="AH25" s="46"/>
+      <c r="AI25" s="47"/>
+      <c r="AJ25" s="46">
+        <f>AVERAGE(AJ4:AJ24)</f>
+        <v>0</v>
+      </c>
+      <c r="AK25" s="46"/>
+      <c r="AL25" s="47"/>
+      <c r="AM25" s="46">
+        <f>AVERAGE(AM4:AM24)</f>
+        <v>0</v>
+      </c>
+      <c r="AN25" s="46"/>
+      <c r="AO25" s="47"/>
+      <c r="AP25" s="46">
+        <f>AVERAGE(AP4:AP24)</f>
+        <v>0</v>
+      </c>
+      <c r="AQ25" s="46"/>
+      <c r="AR25" s="47"/>
+    </row>
+    <row r="26" spans="1:44" s="9" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="B26" s="16"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="7"/>
+      <c r="H26" s="7"/>
+      <c r="I26" s="7"/>
+      <c r="J26" s="7"/>
+      <c r="K26" s="7"/>
+      <c r="L26" s="7"/>
+      <c r="M26" s="7"/>
+      <c r="N26" s="7"/>
+      <c r="O26" s="7"/>
+      <c r="P26" s="7"/>
+      <c r="Q26" s="7"/>
+      <c r="R26" s="7"/>
+      <c r="S26" s="7"/>
+      <c r="T26" s="7"/>
+      <c r="U26" s="7"/>
+      <c r="V26" s="7"/>
+      <c r="W26" s="7"/>
+      <c r="X26" s="7"/>
+      <c r="Y26" s="7"/>
+      <c r="Z26" s="7"/>
+      <c r="AA26" s="7"/>
+      <c r="AB26" s="7"/>
+      <c r="AC26" s="7"/>
+      <c r="AD26" s="7"/>
+      <c r="AE26" s="7"/>
+      <c r="AF26" s="7"/>
+      <c r="AG26" s="7"/>
+      <c r="AH26" s="7"/>
+      <c r="AI26" s="7"/>
+      <c r="AJ26" s="7"/>
+      <c r="AK26" s="7"/>
+      <c r="AL26" s="7"/>
+      <c r="AM26" s="7"/>
+      <c r="AN26" s="7"/>
+      <c r="AO26" s="7"/>
+      <c r="AP26" s="7"/>
+      <c r="AQ26" s="7"/>
+      <c r="AR26" s="7"/>
+    </row>
+    <row r="27" spans="1:44" s="9" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="B27" s="8"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="7"/>
+      <c r="G27" s="7"/>
+      <c r="H27" s="7"/>
+      <c r="I27" s="7"/>
+      <c r="J27" s="7"/>
+      <c r="K27" s="7"/>
+      <c r="L27" s="7"/>
+      <c r="M27" s="7"/>
+      <c r="N27" s="7"/>
+      <c r="O27" s="7"/>
+      <c r="P27" s="7"/>
+      <c r="Q27" s="7"/>
+      <c r="R27" s="7"/>
+      <c r="S27" s="7"/>
+      <c r="T27" s="7"/>
+      <c r="U27" s="7"/>
+      <c r="V27" s="7"/>
+      <c r="W27" s="7"/>
+      <c r="X27" s="7"/>
+      <c r="Y27" s="7"/>
+      <c r="Z27" s="7"/>
+      <c r="AA27" s="7"/>
+      <c r="AB27" s="7"/>
+      <c r="AC27" s="7"/>
+      <c r="AD27" s="7"/>
+      <c r="AE27" s="7"/>
+      <c r="AF27" s="7"/>
+      <c r="AG27" s="7"/>
+      <c r="AH27" s="7"/>
+      <c r="AI27" s="7"/>
+      <c r="AJ27" s="7"/>
+      <c r="AK27" s="7"/>
+      <c r="AL27" s="7"/>
+      <c r="AM27" s="7"/>
+      <c r="AN27" s="7"/>
+      <c r="AO27" s="7"/>
+      <c r="AP27" s="7"/>
+      <c r="AQ27" s="7"/>
+      <c r="AR27" s="7"/>
     </row>
     <row r="28" spans="1:44" s="9" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="B28" s="16"/>
+      <c r="B28" s="8"/>
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
       <c r="E28" s="7"/>
@@ -5558,117 +5551,14 @@
       <c r="AQ61" s="7"/>
       <c r="AR61" s="7"/>
     </row>
-    <row r="62" spans="2:44" s="9" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="B62" s="8"/>
-      <c r="C62" s="7"/>
-      <c r="D62" s="7"/>
-      <c r="E62" s="7"/>
-      <c r="F62" s="7"/>
-      <c r="G62" s="7"/>
-      <c r="H62" s="7"/>
-      <c r="I62" s="7"/>
-      <c r="J62" s="7"/>
-      <c r="K62" s="7"/>
-      <c r="L62" s="7"/>
-      <c r="M62" s="7"/>
-      <c r="N62" s="7"/>
-      <c r="O62" s="7"/>
-      <c r="P62" s="7"/>
-      <c r="Q62" s="7"/>
-      <c r="R62" s="7"/>
-      <c r="S62" s="7"/>
-      <c r="T62" s="7"/>
-      <c r="U62" s="7"/>
-      <c r="V62" s="7"/>
-      <c r="W62" s="7"/>
-      <c r="X62" s="7"/>
-      <c r="Y62" s="7"/>
-      <c r="Z62" s="7"/>
-      <c r="AA62" s="7"/>
-      <c r="AB62" s="7"/>
-      <c r="AC62" s="7"/>
-      <c r="AD62" s="7"/>
-      <c r="AE62" s="7"/>
-      <c r="AF62" s="7"/>
-      <c r="AG62" s="7"/>
-      <c r="AH62" s="7"/>
-      <c r="AI62" s="7"/>
-      <c r="AJ62" s="7"/>
-      <c r="AK62" s="7"/>
-      <c r="AL62" s="7"/>
-      <c r="AM62" s="7"/>
-      <c r="AN62" s="7"/>
-      <c r="AO62" s="7"/>
-      <c r="AP62" s="7"/>
-      <c r="AQ62" s="7"/>
-      <c r="AR62" s="7"/>
-    </row>
-    <row r="63" spans="2:44" s="9" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="B63" s="8"/>
-      <c r="C63" s="7"/>
-      <c r="D63" s="7"/>
-      <c r="E63" s="7"/>
-      <c r="F63" s="7"/>
-      <c r="G63" s="7"/>
-      <c r="H63" s="7"/>
-      <c r="I63" s="7"/>
-      <c r="J63" s="7"/>
-      <c r="K63" s="7"/>
-      <c r="L63" s="7"/>
-      <c r="M63" s="7"/>
-      <c r="N63" s="7"/>
-      <c r="O63" s="7"/>
-      <c r="P63" s="7"/>
-      <c r="Q63" s="7"/>
-      <c r="R63" s="7"/>
-      <c r="S63" s="7"/>
-      <c r="T63" s="7"/>
-      <c r="U63" s="7"/>
-      <c r="V63" s="7"/>
-      <c r="W63" s="7"/>
-      <c r="X63" s="7"/>
-      <c r="Y63" s="7"/>
-      <c r="Z63" s="7"/>
-      <c r="AA63" s="7"/>
-      <c r="AB63" s="7"/>
-      <c r="AC63" s="7"/>
-      <c r="AD63" s="7"/>
-      <c r="AE63" s="7"/>
-      <c r="AF63" s="7"/>
-      <c r="AG63" s="7"/>
-      <c r="AH63" s="7"/>
-      <c r="AI63" s="7"/>
-      <c r="AJ63" s="7"/>
-      <c r="AK63" s="7"/>
-      <c r="AL63" s="7"/>
-      <c r="AM63" s="7"/>
-      <c r="AN63" s="7"/>
-      <c r="AO63" s="7"/>
-      <c r="AP63" s="7"/>
-      <c r="AQ63" s="7"/>
-      <c r="AR63" s="7"/>
-    </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="R27:T27"/>
-    <mergeCell ref="U27:W27"/>
-    <mergeCell ref="AM27:AO27"/>
-    <mergeCell ref="X27:Z27"/>
-    <mergeCell ref="AA27:AC27"/>
-    <mergeCell ref="AD27:AF27"/>
-    <mergeCell ref="AG27:AI27"/>
-    <mergeCell ref="AJ27:AL27"/>
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="I27:K27"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="O27:Q27"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="AP2:AR2"/>
-    <mergeCell ref="AP27:AR27"/>
+    <mergeCell ref="AP25:AR25"/>
     <mergeCell ref="C2:E2"/>
-    <mergeCell ref="C27:E27"/>
-    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="F25:H25"/>
     <mergeCell ref="AJ2:AL2"/>
     <mergeCell ref="AM2:AO2"/>
     <mergeCell ref="AG2:AI2"/>
@@ -5679,6 +5569,19 @@
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="U2:W2"/>
     <mergeCell ref="R2:T2"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="I25:K25"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="R25:T25"/>
+    <mergeCell ref="U25:W25"/>
+    <mergeCell ref="AM25:AO25"/>
+    <mergeCell ref="X25:Z25"/>
+    <mergeCell ref="AA25:AC25"/>
+    <mergeCell ref="AD25:AF25"/>
+    <mergeCell ref="AG25:AI25"/>
+    <mergeCell ref="AJ25:AL25"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
